--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="226">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -521,6 +521,12 @@
   </si>
   <si>
     <t>['12', '42']</t>
+  </si>
+  <si>
+    <t>['44']</t>
+  </si>
+  <si>
+    <t>['22', '13', '86']</t>
   </si>
   <si>
     <t>['75']</t>
@@ -1047,7 +1053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP131"/>
+  <dimension ref="A1:BP135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1509,7 +1515,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Q3">
         <v>3.1</v>
@@ -1715,7 +1721,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="Q4">
         <v>2.3</v>
@@ -2205,7 +2211,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ6">
         <v>0.43</v>
@@ -2333,7 +2339,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q7">
         <v>3.68</v>
@@ -2414,7 +2420,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2539,7 +2545,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -2617,7 +2623,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ8">
         <v>1</v>
@@ -2826,7 +2832,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ9">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3235,10 +3241,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ11">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3775,7 +3781,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3981,7 +3987,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="Q15">
         <v>2.7</v>
@@ -4393,7 +4399,7 @@
         <v>90</v>
       </c>
       <c r="P17" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q17">
         <v>4.4</v>
@@ -4471,7 +4477,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ17">
         <v>1.67</v>
@@ -5011,7 +5017,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="Q20">
         <v>2.8</v>
@@ -5217,7 +5223,7 @@
         <v>104</v>
       </c>
       <c r="P21" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q21">
         <v>2.65</v>
@@ -5298,7 +5304,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ21">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -5423,7 +5429,7 @@
         <v>105</v>
       </c>
       <c r="P22" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Q22">
         <v>2.82</v>
@@ -5501,7 +5507,7 @@
         <v>3</v>
       </c>
       <c r="AP22">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ22">
         <v>1</v>
@@ -5629,7 +5635,7 @@
         <v>106</v>
       </c>
       <c r="P23" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Q23">
         <v>2.9</v>
@@ -5835,7 +5841,7 @@
         <v>107</v>
       </c>
       <c r="P24" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -5913,7 +5919,7 @@
         <v>0</v>
       </c>
       <c r="AP24">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ24">
         <v>0.86</v>
@@ -6041,7 +6047,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q25">
         <v>2.56</v>
@@ -6122,7 +6128,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ25">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR25">
         <v>2.01</v>
@@ -6740,7 +6746,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ28">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR28">
         <v>1.01</v>
@@ -6946,7 +6952,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ29">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR29">
         <v>1.06</v>
@@ -7483,7 +7489,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7689,7 +7695,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="Q33">
         <v>1.95</v>
@@ -8388,7 +8394,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ36">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR36">
         <v>1.34</v>
@@ -8591,7 +8597,7 @@
         <v>0</v>
       </c>
       <c r="AP37">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ37">
         <v>0.57</v>
@@ -8925,7 +8931,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9003,7 +9009,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ39">
         <v>0.83</v>
@@ -9337,7 +9343,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Q41">
         <v>2.74</v>
@@ -9827,7 +9833,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ43">
         <v>1.57</v>
@@ -9955,7 +9961,7 @@
         <v>90</v>
       </c>
       <c r="P44" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="Q44">
         <v>2.55</v>
@@ -10036,7 +10042,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ44">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR44">
         <v>1.07</v>
@@ -10242,7 +10248,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ45">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR45">
         <v>1.63</v>
@@ -10367,7 +10373,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Q46">
         <v>2.25</v>
@@ -10779,7 +10785,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="Q48">
         <v>3.1</v>
@@ -11063,7 +11069,7 @@
         <v>0.5</v>
       </c>
       <c r="AP49">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ49">
         <v>0.43</v>
@@ -11684,7 +11690,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ52">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR52">
         <v>1.71</v>
@@ -11887,7 +11893,7 @@
         <v>0</v>
       </c>
       <c r="AP53">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ53">
         <v>0.83</v>
@@ -12015,7 +12021,7 @@
         <v>90</v>
       </c>
       <c r="P54" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q54">
         <v>2.69</v>
@@ -12096,7 +12102,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ54">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR54">
         <v>1.35</v>
@@ -12221,7 +12227,7 @@
         <v>101</v>
       </c>
       <c r="P55" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="Q55">
         <v>2.41</v>
@@ -12633,7 +12639,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q57">
         <v>2.49</v>
@@ -12917,7 +12923,7 @@
         <v>0</v>
       </c>
       <c r="AP58">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ58">
         <v>0</v>
@@ -13251,7 +13257,7 @@
         <v>90</v>
       </c>
       <c r="P60" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q60">
         <v>3</v>
@@ -13457,7 +13463,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Q61">
         <v>2.45</v>
@@ -13869,7 +13875,7 @@
         <v>90</v>
       </c>
       <c r="P63" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -14075,7 +14081,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="Q64">
         <v>3.32</v>
@@ -14281,7 +14287,7 @@
         <v>131</v>
       </c>
       <c r="P65" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Q65">
         <v>2.44</v>
@@ -14359,10 +14365,10 @@
         <v>1.67</v>
       </c>
       <c r="AP65">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ65">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR65">
         <v>1.95</v>
@@ -15105,7 +15111,7 @@
         <v>95</v>
       </c>
       <c r="P69" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15595,7 +15601,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ71">
         <v>0.86</v>
@@ -15804,7 +15810,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ72">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR72">
         <v>1.92</v>
@@ -15929,7 +15935,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Q73">
         <v>2.94</v>
@@ -16007,7 +16013,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ73">
         <v>0.83</v>
@@ -16135,7 +16141,7 @@
         <v>135</v>
       </c>
       <c r="P74" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q74">
         <v>3.05</v>
@@ -16419,7 +16425,7 @@
         <v>0</v>
       </c>
       <c r="AP75">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ75">
         <v>0</v>
@@ -16547,7 +16553,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -16959,7 +16965,7 @@
         <v>95</v>
       </c>
       <c r="P78" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Q78">
         <v>2.21</v>
@@ -17371,7 +17377,7 @@
         <v>90</v>
       </c>
       <c r="P80" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q80">
         <v>2.13</v>
@@ -17452,7 +17458,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ80">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR80">
         <v>1.49</v>
@@ -17577,7 +17583,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="Q81">
         <v>2.45</v>
@@ -17658,7 +17664,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ81">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR81">
         <v>1.7</v>
@@ -17864,7 +17870,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ82">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR82">
         <v>1.51</v>
@@ -17989,7 +17995,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q83">
         <v>3.45</v>
@@ -18401,7 +18407,7 @@
         <v>141</v>
       </c>
       <c r="P85" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="Q85">
         <v>2.55</v>
@@ -18607,7 +18613,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -18685,7 +18691,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ86">
         <v>0.86</v>
@@ -19225,7 +19231,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19303,7 +19309,7 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ89">
         <v>0</v>
@@ -19637,7 +19643,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -19921,10 +19927,10 @@
         <v>1.25</v>
       </c>
       <c r="AP92">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ92">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR92">
         <v>1.79</v>
@@ -20049,7 +20055,7 @@
         <v>90</v>
       </c>
       <c r="P93" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="Q93">
         <v>3.04</v>
@@ -20127,7 +20133,7 @@
         <v>1.75</v>
       </c>
       <c r="AP93">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ93">
         <v>1.67</v>
@@ -20255,7 +20261,7 @@
         <v>90</v>
       </c>
       <c r="P94" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q94">
         <v>2.85</v>
@@ -20667,7 +20673,7 @@
         <v>149</v>
       </c>
       <c r="P96" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Q96">
         <v>2.4</v>
@@ -20873,7 +20879,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Q97">
         <v>2.5</v>
@@ -20954,7 +20960,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ97">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR97">
         <v>1.89</v>
@@ -21079,7 +21085,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21160,7 +21166,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ98">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR98">
         <v>1.47</v>
@@ -21285,7 +21291,7 @@
         <v>150</v>
       </c>
       <c r="P99" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="Q99">
         <v>2.3</v>
@@ -21569,7 +21575,7 @@
         <v>1.25</v>
       </c>
       <c r="AP100">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ100">
         <v>1.33</v>
@@ -22315,7 +22321,7 @@
         <v>153</v>
       </c>
       <c r="P104" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="Q104">
         <v>2.51</v>
@@ -22521,7 +22527,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="Q105">
         <v>3.32</v>
@@ -22602,7 +22608,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ105">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR105">
         <v>2.41</v>
@@ -22805,7 +22811,7 @@
         <v>1</v>
       </c>
       <c r="AP106">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ106">
         <v>0.83</v>
@@ -23345,7 +23351,7 @@
         <v>90</v>
       </c>
       <c r="P109" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q109">
         <v>4.1</v>
@@ -23757,7 +23763,7 @@
         <v>156</v>
       </c>
       <c r="P111" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Q111">
         <v>3.1</v>
@@ -24375,7 +24381,7 @@
         <v>158</v>
       </c>
       <c r="P114" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q114">
         <v>3.3</v>
@@ -24453,10 +24459,10 @@
         <v>1.4</v>
       </c>
       <c r="AP114">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AQ114">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AR114">
         <v>1.65</v>
@@ -24581,7 +24587,7 @@
         <v>159</v>
       </c>
       <c r="P115" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="Q115">
         <v>3.2</v>
@@ -24662,7 +24668,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ115">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AR115">
         <v>1.49</v>
@@ -25071,7 +25077,7 @@
         <v>1.4</v>
       </c>
       <c r="AP117">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ117">
         <v>1.33</v>
@@ -25486,7 +25492,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ119">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR119">
         <v>1.9</v>
@@ -25689,10 +25695,10 @@
         <v>1</v>
       </c>
       <c r="AP120">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ120">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AR120">
         <v>1.42</v>
@@ -25817,7 +25823,7 @@
         <v>90</v>
       </c>
       <c r="P121" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="Q121">
         <v>2.44</v>
@@ -26023,7 +26029,7 @@
         <v>161</v>
       </c>
       <c r="P122" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q122">
         <v>2.83</v>
@@ -26229,7 +26235,7 @@
         <v>90</v>
       </c>
       <c r="P123" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Q123">
         <v>2.6</v>
@@ -26435,7 +26441,7 @@
         <v>162</v>
       </c>
       <c r="P124" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q124">
         <v>2.25</v>
@@ -26719,7 +26725,7 @@
         <v>0</v>
       </c>
       <c r="AP125">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ125">
         <v>0</v>
@@ -26847,7 +26853,7 @@
         <v>164</v>
       </c>
       <c r="P126" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q126">
         <v>2.7</v>
@@ -27053,7 +27059,7 @@
         <v>165</v>
       </c>
       <c r="P127" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="Q127">
         <v>2.86</v>
@@ -27259,7 +27265,7 @@
         <v>90</v>
       </c>
       <c r="P128" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27465,7 +27471,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="Q129">
         <v>2.68</v>
@@ -28034,6 +28040,830 @@
       </c>
       <c r="BP131">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="132" spans="1:68">
+      <c r="A132" s="1">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>7845473</v>
+      </c>
+      <c r="C132" t="s">
+        <v>68</v>
+      </c>
+      <c r="D132" t="s">
+        <v>69</v>
+      </c>
+      <c r="E132" s="2">
+        <v>45864.70833333334</v>
+      </c>
+      <c r="F132">
+        <v>14</v>
+      </c>
+      <c r="G132" t="s">
+        <v>76</v>
+      </c>
+      <c r="H132" t="s">
+        <v>81</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>1</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>1</v>
+      </c>
+      <c r="N132">
+        <v>1</v>
+      </c>
+      <c r="O132" t="s">
+        <v>90</v>
+      </c>
+      <c r="P132" t="s">
+        <v>203</v>
+      </c>
+      <c r="Q132">
+        <v>2.7</v>
+      </c>
+      <c r="R132">
+        <v>1.93</v>
+      </c>
+      <c r="S132">
+        <v>5.02</v>
+      </c>
+      <c r="T132">
+        <v>1.51</v>
+      </c>
+      <c r="U132">
+        <v>2.45</v>
+      </c>
+      <c r="V132">
+        <v>3.3</v>
+      </c>
+      <c r="W132">
+        <v>1.29</v>
+      </c>
+      <c r="X132">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y132">
+        <v>1.03</v>
+      </c>
+      <c r="Z132">
+        <v>2</v>
+      </c>
+      <c r="AA132">
+        <v>3.05</v>
+      </c>
+      <c r="AB132">
+        <v>3.5</v>
+      </c>
+      <c r="AC132">
+        <v>1.09</v>
+      </c>
+      <c r="AD132">
+        <v>6.15</v>
+      </c>
+      <c r="AE132">
+        <v>1.44</v>
+      </c>
+      <c r="AF132">
+        <v>2.6</v>
+      </c>
+      <c r="AG132">
+        <v>2.28</v>
+      </c>
+      <c r="AH132">
+        <v>1.5</v>
+      </c>
+      <c r="AI132">
+        <v>2.1</v>
+      </c>
+      <c r="AJ132">
+        <v>1.69</v>
+      </c>
+      <c r="AK132">
+        <v>1.37</v>
+      </c>
+      <c r="AL132">
+        <v>1.28</v>
+      </c>
+      <c r="AM132">
+        <v>1.67</v>
+      </c>
+      <c r="AN132">
+        <v>1.57</v>
+      </c>
+      <c r="AO132">
+        <v>1.33</v>
+      </c>
+      <c r="AP132">
+        <v>1.38</v>
+      </c>
+      <c r="AQ132">
+        <v>1.57</v>
+      </c>
+      <c r="AR132">
+        <v>1.71</v>
+      </c>
+      <c r="AS132">
+        <v>1.29</v>
+      </c>
+      <c r="AT132">
+        <v>3</v>
+      </c>
+      <c r="AU132">
+        <v>3</v>
+      </c>
+      <c r="AV132">
+        <v>5</v>
+      </c>
+      <c r="AW132">
+        <v>9</v>
+      </c>
+      <c r="AX132">
+        <v>5</v>
+      </c>
+      <c r="AY132">
+        <v>12</v>
+      </c>
+      <c r="AZ132">
+        <v>10</v>
+      </c>
+      <c r="BA132">
+        <v>5</v>
+      </c>
+      <c r="BB132">
+        <v>4</v>
+      </c>
+      <c r="BC132">
+        <v>9</v>
+      </c>
+      <c r="BD132">
+        <v>1.59</v>
+      </c>
+      <c r="BE132">
+        <v>8</v>
+      </c>
+      <c r="BF132">
+        <v>2.95</v>
+      </c>
+      <c r="BG132">
+        <v>1.25</v>
+      </c>
+      <c r="BH132">
+        <v>3.86</v>
+      </c>
+      <c r="BI132">
+        <v>1.38</v>
+      </c>
+      <c r="BJ132">
+        <v>2.7</v>
+      </c>
+      <c r="BK132">
+        <v>1.88</v>
+      </c>
+      <c r="BL132">
+        <v>2.05</v>
+      </c>
+      <c r="BM132">
+        <v>2.1</v>
+      </c>
+      <c r="BN132">
+        <v>1.65</v>
+      </c>
+      <c r="BO132">
+        <v>2.74</v>
+      </c>
+      <c r="BP132">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="133" spans="1:68">
+      <c r="A133" s="1">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>7845479</v>
+      </c>
+      <c r="C133" t="s">
+        <v>68</v>
+      </c>
+      <c r="D133" t="s">
+        <v>69</v>
+      </c>
+      <c r="E133" s="2">
+        <v>45864.70833333334</v>
+      </c>
+      <c r="F133">
+        <v>14</v>
+      </c>
+      <c r="G133" t="s">
+        <v>85</v>
+      </c>
+      <c r="H133" t="s">
+        <v>89</v>
+      </c>
+      <c r="I133">
+        <v>1</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+      <c r="L133">
+        <v>1</v>
+      </c>
+      <c r="M133">
+        <v>1</v>
+      </c>
+      <c r="N133">
+        <v>2</v>
+      </c>
+      <c r="O133" t="s">
+        <v>169</v>
+      </c>
+      <c r="P133" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q133">
+        <v>3.08</v>
+      </c>
+      <c r="R133">
+        <v>1.71</v>
+      </c>
+      <c r="S133">
+        <v>4.11</v>
+      </c>
+      <c r="T133">
+        <v>1.72</v>
+      </c>
+      <c r="U133">
+        <v>2.01</v>
+      </c>
+      <c r="V133">
+        <v>4.33</v>
+      </c>
+      <c r="W133">
+        <v>1.16</v>
+      </c>
+      <c r="X133">
+        <v>13.5</v>
+      </c>
+      <c r="Y133">
+        <v>1.03</v>
+      </c>
+      <c r="Z133">
+        <v>2.31</v>
+      </c>
+      <c r="AA133">
+        <v>2.78</v>
+      </c>
+      <c r="AB133">
+        <v>3.5</v>
+      </c>
+      <c r="AC133">
+        <v>1.11</v>
+      </c>
+      <c r="AD133">
+        <v>5.3</v>
+      </c>
+      <c r="AE133">
+        <v>1.62</v>
+      </c>
+      <c r="AF133">
+        <v>2.03</v>
+      </c>
+      <c r="AG133">
+        <v>3</v>
+      </c>
+      <c r="AH133">
+        <v>1.33</v>
+      </c>
+      <c r="AI133">
+        <v>2.38</v>
+      </c>
+      <c r="AJ133">
+        <v>1.46</v>
+      </c>
+      <c r="AK133">
+        <v>1.34</v>
+      </c>
+      <c r="AL133">
+        <v>1.29</v>
+      </c>
+      <c r="AM133">
+        <v>1.6</v>
+      </c>
+      <c r="AN133">
+        <v>2.17</v>
+      </c>
+      <c r="AO133">
+        <v>1.57</v>
+      </c>
+      <c r="AP133">
+        <v>2</v>
+      </c>
+      <c r="AQ133">
+        <v>1.5</v>
+      </c>
+      <c r="AR133">
+        <v>1.62</v>
+      </c>
+      <c r="AS133">
+        <v>1.64</v>
+      </c>
+      <c r="AT133">
+        <v>3.26</v>
+      </c>
+      <c r="AU133">
+        <v>3</v>
+      </c>
+      <c r="AV133">
+        <v>2</v>
+      </c>
+      <c r="AW133">
+        <v>5</v>
+      </c>
+      <c r="AX133">
+        <v>9</v>
+      </c>
+      <c r="AY133">
+        <v>8</v>
+      </c>
+      <c r="AZ133">
+        <v>11</v>
+      </c>
+      <c r="BA133">
+        <v>2</v>
+      </c>
+      <c r="BB133">
+        <v>2</v>
+      </c>
+      <c r="BC133">
+        <v>4</v>
+      </c>
+      <c r="BD133">
+        <v>2.15</v>
+      </c>
+      <c r="BE133">
+        <v>6.25</v>
+      </c>
+      <c r="BF133">
+        <v>2.03</v>
+      </c>
+      <c r="BG133">
+        <v>1.21</v>
+      </c>
+      <c r="BH133">
+        <v>3.58</v>
+      </c>
+      <c r="BI133">
+        <v>1.46</v>
+      </c>
+      <c r="BJ133">
+        <v>2.56</v>
+      </c>
+      <c r="BK133">
+        <v>1.8</v>
+      </c>
+      <c r="BL133">
+        <v>1.96</v>
+      </c>
+      <c r="BM133">
+        <v>2.2</v>
+      </c>
+      <c r="BN133">
+        <v>1.59</v>
+      </c>
+      <c r="BO133">
+        <v>2.88</v>
+      </c>
+      <c r="BP133">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="134" spans="1:68">
+      <c r="A134" s="1">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>7845471</v>
+      </c>
+      <c r="C134" t="s">
+        <v>68</v>
+      </c>
+      <c r="D134" t="s">
+        <v>69</v>
+      </c>
+      <c r="E134" s="2">
+        <v>45864.8125</v>
+      </c>
+      <c r="F134">
+        <v>14</v>
+      </c>
+      <c r="G134" t="s">
+        <v>74</v>
+      </c>
+      <c r="H134" t="s">
+        <v>83</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134" t="s">
+        <v>90</v>
+      </c>
+      <c r="P134" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q134">
+        <v>2.6</v>
+      </c>
+      <c r="R134">
+        <v>1.98</v>
+      </c>
+      <c r="S134">
+        <v>5</v>
+      </c>
+      <c r="T134">
+        <v>1.56</v>
+      </c>
+      <c r="U134">
+        <v>2.28</v>
+      </c>
+      <c r="V134">
+        <v>3.6</v>
+      </c>
+      <c r="W134">
+        <v>1.25</v>
+      </c>
+      <c r="X134">
+        <v>10</v>
+      </c>
+      <c r="Y134">
+        <v>1.02</v>
+      </c>
+      <c r="Z134">
+        <v>1.9</v>
+      </c>
+      <c r="AA134">
+        <v>3</v>
+      </c>
+      <c r="AB134">
+        <v>4.6</v>
+      </c>
+      <c r="AC134">
+        <v>1.06</v>
+      </c>
+      <c r="AD134">
+        <v>6.5</v>
+      </c>
+      <c r="AE134">
+        <v>1.53</v>
+      </c>
+      <c r="AF134">
+        <v>2.39</v>
+      </c>
+      <c r="AG134">
+        <v>2.49</v>
+      </c>
+      <c r="AH134">
+        <v>1.49</v>
+      </c>
+      <c r="AI134">
+        <v>2.35</v>
+      </c>
+      <c r="AJ134">
+        <v>1.55</v>
+      </c>
+      <c r="AK134">
+        <v>1.33</v>
+      </c>
+      <c r="AL134">
+        <v>1.3</v>
+      </c>
+      <c r="AM134">
+        <v>1.95</v>
+      </c>
+      <c r="AN134">
+        <v>1.33</v>
+      </c>
+      <c r="AO134">
+        <v>1.17</v>
+      </c>
+      <c r="AP134">
+        <v>1.29</v>
+      </c>
+      <c r="AQ134">
+        <v>1.14</v>
+      </c>
+      <c r="AR134">
+        <v>1.36</v>
+      </c>
+      <c r="AS134">
+        <v>1.19</v>
+      </c>
+      <c r="AT134">
+        <v>2.55</v>
+      </c>
+      <c r="AU134">
+        <v>4</v>
+      </c>
+      <c r="AV134">
+        <v>5</v>
+      </c>
+      <c r="AW134">
+        <v>8</v>
+      </c>
+      <c r="AX134">
+        <v>10</v>
+      </c>
+      <c r="AY134">
+        <v>12</v>
+      </c>
+      <c r="AZ134">
+        <v>15</v>
+      </c>
+      <c r="BA134">
+        <v>7</v>
+      </c>
+      <c r="BB134">
+        <v>7</v>
+      </c>
+      <c r="BC134">
+        <v>14</v>
+      </c>
+      <c r="BD134">
+        <v>1.6</v>
+      </c>
+      <c r="BE134">
+        <v>7.75</v>
+      </c>
+      <c r="BF134">
+        <v>3</v>
+      </c>
+      <c r="BG134">
+        <v>1.2</v>
+      </c>
+      <c r="BH134">
+        <v>4</v>
+      </c>
+      <c r="BI134">
+        <v>1.35</v>
+      </c>
+      <c r="BJ134">
+        <v>2.79</v>
+      </c>
+      <c r="BK134">
+        <v>1.72</v>
+      </c>
+      <c r="BL134">
+        <v>1.93</v>
+      </c>
+      <c r="BM134">
+        <v>2.04</v>
+      </c>
+      <c r="BN134">
+        <v>1.53</v>
+      </c>
+      <c r="BO134">
+        <v>2.38</v>
+      </c>
+      <c r="BP134">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="135" spans="1:68">
+      <c r="A135" s="1">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>7845476</v>
+      </c>
+      <c r="C135" t="s">
+        <v>68</v>
+      </c>
+      <c r="D135" t="s">
+        <v>69</v>
+      </c>
+      <c r="E135" s="2">
+        <v>45864.8125</v>
+      </c>
+      <c r="F135">
+        <v>14</v>
+      </c>
+      <c r="G135" t="s">
+        <v>79</v>
+      </c>
+      <c r="H135" t="s">
+        <v>72</v>
+      </c>
+      <c r="I135">
+        <v>2</v>
+      </c>
+      <c r="J135">
+        <v>1</v>
+      </c>
+      <c r="K135">
+        <v>3</v>
+      </c>
+      <c r="L135">
+        <v>3</v>
+      </c>
+      <c r="M135">
+        <v>1</v>
+      </c>
+      <c r="N135">
+        <v>4</v>
+      </c>
+      <c r="O135" t="s">
+        <v>170</v>
+      </c>
+      <c r="P135" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q135">
+        <v>2.8</v>
+      </c>
+      <c r="R135">
+        <v>1.95</v>
+      </c>
+      <c r="S135">
+        <v>4.4</v>
+      </c>
+      <c r="T135">
+        <v>1.48</v>
+      </c>
+      <c r="U135">
+        <v>2.4</v>
+      </c>
+      <c r="V135">
+        <v>3.65</v>
+      </c>
+      <c r="W135">
+        <v>1.25</v>
+      </c>
+      <c r="X135">
+        <v>10</v>
+      </c>
+      <c r="Y135">
+        <v>1.03</v>
+      </c>
+      <c r="Z135">
+        <v>2.06</v>
+      </c>
+      <c r="AA135">
+        <v>3.17</v>
+      </c>
+      <c r="AB135">
+        <v>3.6</v>
+      </c>
+      <c r="AC135">
+        <v>1.09</v>
+      </c>
+      <c r="AD135">
+        <v>7.4</v>
+      </c>
+      <c r="AE135">
+        <v>1.57</v>
+      </c>
+      <c r="AF135">
+        <v>2.6</v>
+      </c>
+      <c r="AG135">
+        <v>2.5</v>
+      </c>
+      <c r="AH135">
+        <v>1.5</v>
+      </c>
+      <c r="AI135">
+        <v>1.9</v>
+      </c>
+      <c r="AJ135">
+        <v>1.65</v>
+      </c>
+      <c r="AK135">
+        <v>1.3</v>
+      </c>
+      <c r="AL135">
+        <v>1.25</v>
+      </c>
+      <c r="AM135">
+        <v>1.74</v>
+      </c>
+      <c r="AN135">
+        <v>1.86</v>
+      </c>
+      <c r="AO135">
+        <v>1</v>
+      </c>
+      <c r="AP135">
+        <v>2</v>
+      </c>
+      <c r="AQ135">
+        <v>0.86</v>
+      </c>
+      <c r="AR135">
+        <v>1.84</v>
+      </c>
+      <c r="AS135">
+        <v>1.18</v>
+      </c>
+      <c r="AT135">
+        <v>3.02</v>
+      </c>
+      <c r="AU135">
+        <v>8</v>
+      </c>
+      <c r="AV135">
+        <v>3</v>
+      </c>
+      <c r="AW135">
+        <v>6</v>
+      </c>
+      <c r="AX135">
+        <v>5</v>
+      </c>
+      <c r="AY135">
+        <v>14</v>
+      </c>
+      <c r="AZ135">
+        <v>8</v>
+      </c>
+      <c r="BA135">
+        <v>6</v>
+      </c>
+      <c r="BB135">
+        <v>4</v>
+      </c>
+      <c r="BC135">
+        <v>10</v>
+      </c>
+      <c r="BD135">
+        <v>1.53</v>
+      </c>
+      <c r="BE135">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF135">
+        <v>3.48</v>
+      </c>
+      <c r="BG135">
+        <v>1.12</v>
+      </c>
+      <c r="BH135">
+        <v>4.53</v>
+      </c>
+      <c r="BI135">
+        <v>1.3</v>
+      </c>
+      <c r="BJ135">
+        <v>2.9</v>
+      </c>
+      <c r="BK135">
+        <v>1.54</v>
+      </c>
+      <c r="BL135">
+        <v>2.2</v>
+      </c>
+      <c r="BM135">
+        <v>1.91</v>
+      </c>
+      <c r="BN135">
+        <v>1.68</v>
+      </c>
+      <c r="BO135">
+        <v>2.38</v>
+      </c>
+      <c r="BP135">
+        <v>1.51</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="235">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -460,7 +460,7 @@
     <t>['30']</t>
   </si>
   <si>
-    <t>['17', '12', '31']</t>
+    <t>['12', '17', '31']</t>
   </si>
   <si>
     <t>['2']</t>
@@ -490,10 +490,10 @@
     <t>['11', '66']</t>
   </si>
   <si>
-    <t>['2', '43']</t>
+    <t>['24']</t>
   </si>
   <si>
-    <t>['24']</t>
+    <t>['2', '43']</t>
   </si>
   <si>
     <t>['10', '45+2']</t>
@@ -508,16 +508,16 @@
     <t>['19', '30']</t>
   </si>
   <si>
-    <t>['13', '53', '90+4']</t>
+    <t>['82']</t>
   </si>
   <si>
-    <t>['82']</t>
+    <t>['13', '53', '90+4']</t>
   </si>
   <si>
     <t>['54']</t>
   </si>
   <si>
-    <t>['83', '60']</t>
+    <t>['60', '83']</t>
   </si>
   <si>
     <t>['12', '42']</t>
@@ -526,7 +526,19 @@
     <t>['44']</t>
   </si>
   <si>
-    <t>['22', '13', '86']</t>
+    <t>['13', '22', '86']</t>
+  </si>
+  <si>
+    <t>['20', '90+8']</t>
+  </si>
+  <si>
+    <t>['16', '49', '54']</t>
+  </si>
+  <si>
+    <t>['84']</t>
+  </si>
+  <si>
+    <t>['9']</t>
   </si>
   <si>
     <t>['75']</t>
@@ -655,7 +667,7 @@
     <t>['26', '64']</t>
   </si>
   <si>
-    <t>['11', '8', '41']</t>
+    <t>['8', '11', '41']</t>
   </si>
   <si>
     <t>['38', '56']</t>
@@ -664,34 +676,49 @@
     <t>['56']</t>
   </si>
   <si>
+    <t>['90', '90+5']</t>
+  </si>
+  <si>
     <t>['35']</t>
   </si>
   <si>
-    <t>['90', '90+5']</t>
+    <t>['45', '63']</t>
   </si>
   <si>
-    <t>['63', '45']</t>
+    <t>['42', '78', '88']</t>
   </si>
   <si>
-    <t>['90+5', '63', '83']</t>
-  </si>
-  <si>
-    <t>['78', '88', '42']</t>
+    <t>['63', '83', '90+5']</t>
   </si>
   <si>
     <t>['52']</t>
   </si>
   <si>
-    <t>['35', '23']</t>
+    <t>['28']</t>
   </si>
   <si>
-    <t>['28']</t>
+    <t>['23', '35']</t>
   </si>
   <si>
     <t>['26', '90+7']</t>
   </si>
   <si>
     <t>['32', '58']</t>
+  </si>
+  <si>
+    <t>['10']</t>
+  </si>
+  <si>
+    <t>['30', '90+3']</t>
+  </si>
+  <si>
+    <t>['41']</t>
+  </si>
+  <si>
+    <t>['43']</t>
+  </si>
+  <si>
+    <t>['35', '41', '90+6']</t>
   </si>
 </sst>
 </file>
@@ -1053,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP135"/>
+  <dimension ref="A1:BP141"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1390,7 +1417,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ2">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1515,7 +1542,7 @@
         <v>91</v>
       </c>
       <c r="P3" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Q3">
         <v>3.1</v>
@@ -1593,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ3">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -1721,7 +1748,7 @@
         <v>90</v>
       </c>
       <c r="P4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Q4">
         <v>2.3</v>
@@ -1802,7 +1829,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ4">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2005,10 +2032,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ5">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2339,7 +2366,7 @@
         <v>93</v>
       </c>
       <c r="P7" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q7">
         <v>3.68</v>
@@ -2417,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ7">
         <v>1.57</v>
@@ -2545,7 +2572,7 @@
         <v>94</v>
       </c>
       <c r="P8" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q8">
         <v>2.88</v>
@@ -2829,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ9">
         <v>1.5</v>
@@ -3781,7 +3808,7 @@
         <v>90</v>
       </c>
       <c r="P14" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q14">
         <v>3.1</v>
@@ -3862,7 +3889,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ14">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -3987,7 +4014,7 @@
         <v>99</v>
       </c>
       <c r="P15" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="Q15">
         <v>2.7</v>
@@ -4399,7 +4426,7 @@
         <v>90</v>
       </c>
       <c r="P17" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Q17">
         <v>4.4</v>
@@ -5017,7 +5044,7 @@
         <v>103</v>
       </c>
       <c r="P20" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Q20">
         <v>2.8</v>
@@ -5095,7 +5122,7 @@
         <v>0</v>
       </c>
       <c r="AP20">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ20">
         <v>0.86</v>
@@ -5223,7 +5250,7 @@
         <v>104</v>
       </c>
       <c r="P21" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q21">
         <v>2.65</v>
@@ -5429,7 +5456,7 @@
         <v>105</v>
       </c>
       <c r="P22" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Q22">
         <v>2.82</v>
@@ -5635,7 +5662,7 @@
         <v>106</v>
       </c>
       <c r="P23" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Q23">
         <v>2.9</v>
@@ -5716,7 +5743,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ23">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR23">
         <v>2.74</v>
@@ -5841,7 +5868,7 @@
         <v>107</v>
       </c>
       <c r="P24" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="Q24">
         <v>2.62</v>
@@ -6047,7 +6074,7 @@
         <v>108</v>
       </c>
       <c r="P25" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="Q25">
         <v>2.56</v>
@@ -6537,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ27">
         <v>1.57</v>
@@ -6949,7 +6976,7 @@
         <v>1</v>
       </c>
       <c r="AP29">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ29">
         <v>1.5</v>
@@ -7489,7 +7516,7 @@
         <v>112</v>
       </c>
       <c r="P32" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="Q32">
         <v>3</v>
@@ -7570,7 +7597,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ32">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR32">
         <v>1.8</v>
@@ -7695,7 +7722,7 @@
         <v>113</v>
       </c>
       <c r="P33" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="Q33">
         <v>1.95</v>
@@ -7776,7 +7803,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ33">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR33">
         <v>2.62</v>
@@ -7979,7 +8006,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ34">
         <v>0</v>
@@ -8188,7 +8215,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ35">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR35">
         <v>1.46</v>
@@ -8806,7 +8833,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ38">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR38">
         <v>1.58</v>
@@ -8931,7 +8958,7 @@
         <v>118</v>
       </c>
       <c r="P39" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="Q39">
         <v>2.5</v>
@@ -9215,7 +9242,7 @@
         <v>3</v>
       </c>
       <c r="AP40">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ40">
         <v>1.67</v>
@@ -9343,7 +9370,7 @@
         <v>119</v>
       </c>
       <c r="P41" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q41">
         <v>2.74</v>
@@ -9421,7 +9448,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ41">
         <v>1.29</v>
@@ -9630,7 +9657,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ42">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR42">
         <v>1.37</v>
@@ -9961,7 +9988,7 @@
         <v>90</v>
       </c>
       <c r="P44" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="Q44">
         <v>2.55</v>
@@ -10373,7 +10400,7 @@
         <v>121</v>
       </c>
       <c r="P46" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="Q46">
         <v>2.25</v>
@@ -10451,7 +10478,7 @@
         <v>0.5</v>
       </c>
       <c r="AP46">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ46">
         <v>0.86</v>
@@ -10579,7 +10606,7 @@
         <v>122</v>
       </c>
       <c r="P47" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q47">
         <v>2.71</v>
@@ -10785,7 +10812,7 @@
         <v>123</v>
       </c>
       <c r="P48" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="Q48">
         <v>3.1</v>
@@ -11278,7 +11305,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ50">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR50">
         <v>1.81</v>
@@ -11481,7 +11508,7 @@
         <v>0</v>
       </c>
       <c r="AP51">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ51">
         <v>0.86</v>
@@ -11687,7 +11714,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ52">
         <v>0.86</v>
@@ -12021,7 +12048,7 @@
         <v>90</v>
       </c>
       <c r="P54" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="Q54">
         <v>2.69</v>
@@ -12227,7 +12254,7 @@
         <v>101</v>
       </c>
       <c r="P55" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="Q55">
         <v>2.41</v>
@@ -12308,7 +12335,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ55">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR55">
         <v>1.36</v>
@@ -12511,7 +12538,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ56">
         <v>1.29</v>
@@ -12639,7 +12666,7 @@
         <v>126</v>
       </c>
       <c r="P57" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q57">
         <v>2.49</v>
@@ -13129,10 +13156,10 @@
         <v>3</v>
       </c>
       <c r="AP59">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ59">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR59">
         <v>1.85</v>
@@ -13257,7 +13284,7 @@
         <v>90</v>
       </c>
       <c r="P60" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Q60">
         <v>3</v>
@@ -13463,7 +13490,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Q61">
         <v>2.45</v>
@@ -13544,7 +13571,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ61">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR61">
         <v>2.01</v>
@@ -13750,7 +13777,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ62">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR62">
         <v>1.93</v>
@@ -13875,7 +13902,7 @@
         <v>90</v>
       </c>
       <c r="P63" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="Q63">
         <v>3</v>
@@ -13956,7 +13983,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ63">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR63">
         <v>1.56</v>
@@ -14081,7 +14108,7 @@
         <v>130</v>
       </c>
       <c r="P64" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="Q64">
         <v>3.32</v>
@@ -14159,7 +14186,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ64">
         <v>1.29</v>
@@ -14287,7 +14314,7 @@
         <v>131</v>
       </c>
       <c r="P65" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="Q65">
         <v>2.44</v>
@@ -14571,7 +14598,7 @@
         <v>0</v>
       </c>
       <c r="AP66">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ66">
         <v>0.57</v>
@@ -15111,7 +15138,7 @@
         <v>95</v>
       </c>
       <c r="P69" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="Q69">
         <v>4</v>
@@ -15935,7 +15962,7 @@
         <v>90</v>
       </c>
       <c r="P73" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="Q73">
         <v>2.94</v>
@@ -16141,7 +16168,7 @@
         <v>135</v>
       </c>
       <c r="P74" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Q74">
         <v>3.05</v>
@@ -16553,7 +16580,7 @@
         <v>137</v>
       </c>
       <c r="P76" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Q76">
         <v>2.95</v>
@@ -16634,7 +16661,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ76">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR76">
         <v>2.43</v>
@@ -16837,10 +16864,10 @@
         <v>1.33</v>
       </c>
       <c r="AP77">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ77">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR77">
         <v>1.38</v>
@@ -16965,7 +16992,7 @@
         <v>95</v>
       </c>
       <c r="P78" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="Q78">
         <v>2.21</v>
@@ -17046,7 +17073,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ78">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR78">
         <v>2.46</v>
@@ -17249,7 +17276,7 @@
         <v>0.67</v>
       </c>
       <c r="AP79">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ79">
         <v>0.83</v>
@@ -17377,7 +17404,7 @@
         <v>90</v>
       </c>
       <c r="P80" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q80">
         <v>2.13</v>
@@ -17583,7 +17610,7 @@
         <v>139</v>
       </c>
       <c r="P81" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="Q81">
         <v>2.45</v>
@@ -17661,7 +17688,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ81">
         <v>0.86</v>
@@ -17995,7 +18022,7 @@
         <v>140</v>
       </c>
       <c r="P83" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q83">
         <v>3.45</v>
@@ -18407,7 +18434,7 @@
         <v>141</v>
       </c>
       <c r="P85" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Q85">
         <v>2.55</v>
@@ -18485,7 +18512,7 @@
         <v>0.75</v>
       </c>
       <c r="AP85">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ85">
         <v>1.29</v>
@@ -18613,7 +18640,7 @@
         <v>142</v>
       </c>
       <c r="P86" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -19106,7 +19133,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ88">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR88">
         <v>1.4</v>
@@ -19231,7 +19258,7 @@
         <v>144</v>
       </c>
       <c r="P89" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q89">
         <v>2.05</v>
@@ -19643,7 +19670,7 @@
         <v>146</v>
       </c>
       <c r="P91" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Q91">
         <v>3</v>
@@ -20055,7 +20082,7 @@
         <v>90</v>
       </c>
       <c r="P93" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="Q93">
         <v>3.04</v>
@@ -20261,7 +20288,7 @@
         <v>90</v>
       </c>
       <c r="P94" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Q94">
         <v>2.85</v>
@@ -20342,7 +20369,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ94">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR94">
         <v>2.68</v>
@@ -20545,10 +20572,10 @@
         <v>1.25</v>
       </c>
       <c r="AP95">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ95">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="AR95">
         <v>1.83</v>
@@ -20673,7 +20700,7 @@
         <v>149</v>
       </c>
       <c r="P96" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q96">
         <v>2.4</v>
@@ -20751,10 +20778,10 @@
         <v>0.2</v>
       </c>
       <c r="AP96">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ96">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR96">
         <v>1.91</v>
@@ -20879,7 +20906,7 @@
         <v>90</v>
       </c>
       <c r="P97" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q97">
         <v>2.5</v>
@@ -21085,7 +21112,7 @@
         <v>90</v>
       </c>
       <c r="P98" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="Q98">
         <v>2.75</v>
@@ -21163,7 +21190,7 @@
         <v>1</v>
       </c>
       <c r="AP98">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ98">
         <v>1.57</v>
@@ -21291,7 +21318,7 @@
         <v>150</v>
       </c>
       <c r="P99" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="Q99">
         <v>2.3</v>
@@ -21372,7 +21399,7 @@
         <v>3</v>
       </c>
       <c r="AQ99">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR99">
         <v>1.36</v>
@@ -21578,7 +21605,7 @@
         <v>2</v>
       </c>
       <c r="AQ100">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AR100">
         <v>1.52</v>
@@ -21781,7 +21808,7 @@
         <v>0.5</v>
       </c>
       <c r="AP101">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ101">
         <v>0.83</v>
@@ -22321,7 +22348,7 @@
         <v>153</v>
       </c>
       <c r="P104" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q104">
         <v>2.51</v>
@@ -22527,7 +22554,7 @@
         <v>125</v>
       </c>
       <c r="P105" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="Q105">
         <v>3.32</v>
@@ -23351,7 +23378,7 @@
         <v>90</v>
       </c>
       <c r="P109" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="Q109">
         <v>4.1</v>
@@ -23763,7 +23790,7 @@
         <v>156</v>
       </c>
       <c r="P111" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="Q111">
         <v>3.1</v>
@@ -23841,7 +23868,7 @@
         <v>1.4</v>
       </c>
       <c r="AP111">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ111">
         <v>1.57</v>
@@ -24047,10 +24074,10 @@
         <v>0.33</v>
       </c>
       <c r="AP112">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ112">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AR112">
         <v>1.59</v>
@@ -24253,10 +24280,10 @@
         <v>2.6</v>
       </c>
       <c r="AP113">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AQ113">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AR113">
         <v>2</v>
@@ -24339,7 +24366,7 @@
         <v>113</v>
       </c>
       <c r="B114">
-        <v>7845459</v>
+        <v>7845454</v>
       </c>
       <c r="C114" t="s">
         <v>68</v>
@@ -24354,25 +24381,25 @@
         <v>0</v>
       </c>
       <c r="G114" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H114" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K114">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N114">
         <v>3</v>
@@ -24381,55 +24408,55 @@
         <v>158</v>
       </c>
       <c r="P114" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="Q114">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R114">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="S114">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T114">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="U114">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="V114">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="W114">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X114">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y114">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Z114">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AA114">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AB114">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="AC114">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AD114">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AE114">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AF114">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AG114">
         <v>3</v>
@@ -24438,40 +24465,40 @@
         <v>1.36</v>
       </c>
       <c r="AI114">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="AJ114">
+        <v>1.6</v>
+      </c>
+      <c r="AK114">
+        <v>1.28</v>
+      </c>
+      <c r="AL114">
+        <v>1.35</v>
+      </c>
+      <c r="AM114">
+        <v>1.46</v>
+      </c>
+      <c r="AN114">
+        <v>1.6</v>
+      </c>
+      <c r="AO114">
+        <v>1.33</v>
+      </c>
+      <c r="AP114">
+        <v>1.29</v>
+      </c>
+      <c r="AQ114">
         <v>1.5</v>
       </c>
-      <c r="AK114">
-        <v>1.44</v>
-      </c>
-      <c r="AL114">
-        <v>1.37</v>
-      </c>
-      <c r="AM114">
-        <v>1.5</v>
-      </c>
-      <c r="AN114">
-        <v>2</v>
-      </c>
-      <c r="AO114">
-        <v>1.4</v>
-      </c>
-      <c r="AP114">
-        <v>2</v>
-      </c>
-      <c r="AQ114">
-        <v>1.14</v>
-      </c>
       <c r="AR114">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="AS114">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="AT114">
-        <v>2.75</v>
+        <v>3.03</v>
       </c>
       <c r="AU114">
         <v>4</v>
@@ -24480,64 +24507,64 @@
         <v>6</v>
       </c>
       <c r="AW114">
+        <v>5</v>
+      </c>
+      <c r="AX114">
+        <v>12</v>
+      </c>
+      <c r="AY114">
         <v>9</v>
       </c>
-      <c r="AX114">
-        <v>6</v>
-      </c>
-      <c r="AY114">
-        <v>13</v>
-      </c>
       <c r="AZ114">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BA114">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BB114">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="BC114">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BD114">
+        <v>2</v>
+      </c>
+      <c r="BE114">
+        <v>8</v>
+      </c>
+      <c r="BF114">
+        <v>2</v>
+      </c>
+      <c r="BG114">
+        <v>1.1</v>
+      </c>
+      <c r="BH114">
+        <v>4.85</v>
+      </c>
+      <c r="BI114">
+        <v>1.26</v>
+      </c>
+      <c r="BJ114">
+        <v>3.2</v>
+      </c>
+      <c r="BK114">
+        <v>1.73</v>
+      </c>
+      <c r="BL114">
+        <v>2.12</v>
+      </c>
+      <c r="BM114">
+        <v>1.85</v>
+      </c>
+      <c r="BN114">
         <v>1.8</v>
       </c>
-      <c r="BE114">
-        <v>6.4</v>
-      </c>
-      <c r="BF114">
-        <v>2.23</v>
-      </c>
-      <c r="BG114">
-        <v>1.29</v>
-      </c>
-      <c r="BH114">
-        <v>3.45</v>
-      </c>
-      <c r="BI114">
-        <v>1.48</v>
-      </c>
-      <c r="BJ114">
-        <v>2.89</v>
-      </c>
-      <c r="BK114">
-        <v>1.61</v>
-      </c>
-      <c r="BL114">
-        <v>1.98</v>
-      </c>
-      <c r="BM114">
-        <v>2.15</v>
-      </c>
-      <c r="BN114">
-        <v>1.61</v>
-      </c>
       <c r="BO114">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="BP114">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="115" spans="1:68">
@@ -24545,7 +24572,7 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>7845454</v>
+        <v>7845459</v>
       </c>
       <c r="C115" t="s">
         <v>68</v>
@@ -24560,25 +24587,25 @@
         <v>0</v>
       </c>
       <c r="G115" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H115" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="I115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K115">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N115">
         <v>3</v>
@@ -24587,55 +24614,55 @@
         <v>159</v>
       </c>
       <c r="P115" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="Q115">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R115">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S115">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T115">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U115">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="V115">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="W115">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X115">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y115">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Z115">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AA115">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AB115">
-        <v>3</v>
+        <v>3.26</v>
       </c>
       <c r="AC115">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AD115">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="AE115">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AF115">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AG115">
         <v>3</v>
@@ -24644,40 +24671,40 @@
         <v>1.36</v>
       </c>
       <c r="AI115">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AJ115">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AK115">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AL115">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AM115">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AN115">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AO115">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AP115">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AQ115">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AR115">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="AS115">
-        <v>1.54</v>
+        <v>1.1</v>
       </c>
       <c r="AT115">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="AU115">
         <v>4</v>
@@ -24686,64 +24713,64 @@
         <v>6</v>
       </c>
       <c r="AW115">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX115">
+        <v>6</v>
+      </c>
+      <c r="AY115">
+        <v>13</v>
+      </c>
+      <c r="AZ115">
         <v>12</v>
       </c>
-      <c r="AY115">
-        <v>9</v>
-      </c>
-      <c r="AZ115">
-        <v>18</v>
-      </c>
       <c r="BA115">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BB115">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="BC115">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BD115">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BE115">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="BF115">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="BG115">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="BH115">
-        <v>4.85</v>
+        <v>3.45</v>
       </c>
       <c r="BI115">
-        <v>1.26</v>
+        <v>1.48</v>
       </c>
       <c r="BJ115">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="BK115">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="BL115">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="BM115">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="BN115">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="BO115">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="BP115">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="116" spans="1:68">
@@ -24871,7 +24898,7 @@
         <v>2</v>
       </c>
       <c r="AP116">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ116">
         <v>1.67</v>
@@ -25080,7 +25107,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ117">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AR117">
         <v>1.73</v>
@@ -25163,7 +25190,7 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>7845457</v>
+        <v>7845458</v>
       </c>
       <c r="C118" t="s">
         <v>68</v>
@@ -25178,10 +25205,10 @@
         <v>0</v>
       </c>
       <c r="G118" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H118" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I118">
         <v>0</v>
@@ -25193,175 +25220,175 @@
         <v>0</v>
       </c>
       <c r="L118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M118">
         <v>0</v>
       </c>
       <c r="N118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O118" t="s">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="P118" t="s">
         <v>90</v>
       </c>
       <c r="Q118">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="R118">
         <v>1.95</v>
       </c>
       <c r="S118">
-        <v>5.75</v>
+        <v>5.88</v>
       </c>
       <c r="T118">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="U118">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V118">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="W118">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X118">
-        <v>11</v>
+        <v>9.25</v>
       </c>
       <c r="Y118">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Z118">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AA118">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="AB118">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="AC118">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AD118">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AE118">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AF118">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="AG118">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH118">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AI118">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AJ118">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AK118">
         <v>1.33</v>
       </c>
       <c r="AL118">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AM118">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AN118">
+        <v>1.6</v>
+      </c>
+      <c r="AO118">
+        <v>1.4</v>
+      </c>
+      <c r="AP118">
+        <v>1.29</v>
+      </c>
+      <c r="AQ118">
+        <v>1.57</v>
+      </c>
+      <c r="AR118">
+        <v>1.9</v>
+      </c>
+      <c r="AS118">
+        <v>1.34</v>
+      </c>
+      <c r="AT118">
+        <v>3.24</v>
+      </c>
+      <c r="AU118">
+        <v>7</v>
+      </c>
+      <c r="AV118">
         <v>3</v>
       </c>
-      <c r="AO118">
-        <v>1</v>
-      </c>
-      <c r="AP118">
-        <v>3</v>
-      </c>
-      <c r="AQ118">
-        <v>0.83</v>
-      </c>
-      <c r="AR118">
-        <v>1.5</v>
-      </c>
-      <c r="AS118">
-        <v>1.36</v>
-      </c>
-      <c r="AT118">
-        <v>2.86</v>
-      </c>
-      <c r="AU118">
-        <v>5</v>
-      </c>
-      <c r="AV118">
-        <v>0</v>
-      </c>
       <c r="AW118">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX118">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AY118">
         <v>14</v>
       </c>
       <c r="AZ118">
+        <v>5</v>
+      </c>
+      <c r="BA118">
+        <v>6</v>
+      </c>
+      <c r="BB118">
         <v>8</v>
       </c>
-      <c r="BA118">
-        <v>10</v>
-      </c>
-      <c r="BB118">
-        <v>1</v>
-      </c>
       <c r="BC118">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BD118">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BE118">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BF118">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="BG118">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="BH118">
-        <v>5.3</v>
+        <v>4.96</v>
       </c>
       <c r="BI118">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="BJ118">
-        <v>5.87</v>
+        <v>3.25</v>
       </c>
       <c r="BK118">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="BL118">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="BM118">
-        <v>1.49</v>
+        <v>1.88</v>
       </c>
       <c r="BN118">
-        <v>2.73</v>
+        <v>1.92</v>
       </c>
       <c r="BO118">
-        <v>1.64</v>
+        <v>2.65</v>
       </c>
       <c r="BP118">
-        <v>2.12</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="119" spans="1:68">
@@ -25369,7 +25396,7 @@
         <v>118</v>
       </c>
       <c r="B119">
-        <v>7845458</v>
+        <v>7845457</v>
       </c>
       <c r="C119" t="s">
         <v>68</v>
@@ -25384,10 +25411,10 @@
         <v>0</v>
       </c>
       <c r="G119" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H119" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -25399,175 +25426,175 @@
         <v>0</v>
       </c>
       <c r="L119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119">
         <v>0</v>
       </c>
       <c r="N119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O119" t="s">
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="P119" t="s">
         <v>90</v>
       </c>
       <c r="Q119">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="R119">
         <v>1.95</v>
       </c>
       <c r="S119">
-        <v>5.88</v>
+        <v>5.75</v>
       </c>
       <c r="T119">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="U119">
+        <v>2.4</v>
+      </c>
+      <c r="V119">
+        <v>3.6</v>
+      </c>
+      <c r="W119">
+        <v>1.25</v>
+      </c>
+      <c r="X119">
+        <v>11</v>
+      </c>
+      <c r="Y119">
+        <v>1.04</v>
+      </c>
+      <c r="Z119">
+        <v>1.68</v>
+      </c>
+      <c r="AA119">
+        <v>3.06</v>
+      </c>
+      <c r="AB119">
+        <v>4.9</v>
+      </c>
+      <c r="AC119">
+        <v>1.06</v>
+      </c>
+      <c r="AD119">
+        <v>6</v>
+      </c>
+      <c r="AE119">
+        <v>1.46</v>
+      </c>
+      <c r="AF119">
+        <v>2.4</v>
+      </c>
+      <c r="AG119">
         <v>2.5</v>
       </c>
-      <c r="V119">
-        <v>3.3</v>
-      </c>
-      <c r="W119">
-        <v>1.3</v>
-      </c>
-      <c r="X119">
-        <v>9.25</v>
-      </c>
-      <c r="Y119">
-        <v>1.03</v>
-      </c>
-      <c r="Z119">
-        <v>1.85</v>
-      </c>
-      <c r="AA119">
-        <v>2.98</v>
-      </c>
-      <c r="AB119">
-        <v>4.5</v>
-      </c>
-      <c r="AC119">
-        <v>1.1</v>
-      </c>
-      <c r="AD119">
-        <v>6.5</v>
-      </c>
-      <c r="AE119">
-        <v>1.43</v>
-      </c>
-      <c r="AF119">
-        <v>2.46</v>
-      </c>
-      <c r="AG119">
-        <v>2.38</v>
-      </c>
       <c r="AH119">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AI119">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="AJ119">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AK119">
         <v>1.33</v>
       </c>
       <c r="AL119">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AM119">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AN119">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="AO119">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AP119">
+        <v>3</v>
+      </c>
+      <c r="AQ119">
+        <v>1.14</v>
+      </c>
+      <c r="AR119">
         <v>1.5</v>
       </c>
-      <c r="AQ119">
-        <v>1.57</v>
-      </c>
-      <c r="AR119">
-        <v>1.9</v>
-      </c>
       <c r="AS119">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AT119">
-        <v>3.24</v>
+        <v>2.86</v>
       </c>
       <c r="AU119">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV119">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AW119">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX119">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AY119">
         <v>14</v>
       </c>
       <c r="AZ119">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BA119">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BB119">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BC119">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BD119">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="BE119">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BF119">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="BG119">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BH119">
-        <v>4.96</v>
+        <v>5.3</v>
       </c>
       <c r="BI119">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="BJ119">
-        <v>3.25</v>
+        <v>5.87</v>
       </c>
       <c r="BK119">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="BL119">
+        <v>2.4</v>
+      </c>
+      <c r="BM119">
+        <v>1.49</v>
+      </c>
+      <c r="BN119">
+        <v>2.73</v>
+      </c>
+      <c r="BO119">
+        <v>1.64</v>
+      </c>
+      <c r="BP119">
         <v>2.12</v>
-      </c>
-      <c r="BM119">
-        <v>1.88</v>
-      </c>
-      <c r="BN119">
-        <v>1.92</v>
-      </c>
-      <c r="BO119">
-        <v>2.65</v>
-      </c>
-      <c r="BP119">
-        <v>1.54</v>
       </c>
     </row>
     <row r="120" spans="1:68">
@@ -25575,7 +25602,7 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>7845451</v>
+        <v>7845456</v>
       </c>
       <c r="C120" t="s">
         <v>68</v>
@@ -25590,152 +25617,152 @@
         <v>0</v>
       </c>
       <c r="G120" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="H120" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="I120">
         <v>0</v>
       </c>
       <c r="J120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120">
         <v>0</v>
       </c>
       <c r="M120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O120" t="s">
         <v>90</v>
       </c>
       <c r="P120" t="s">
-        <v>90</v>
+        <v>222</v>
       </c>
       <c r="Q120">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="R120">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="S120">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="T120">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="U120">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="V120">
         <v>3.6</v>
       </c>
       <c r="W120">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="X120">
-        <v>10</v>
+        <v>9.25</v>
       </c>
       <c r="Y120">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Z120">
-        <v>2.81</v>
+        <v>1.75</v>
       </c>
       <c r="AA120">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="AB120">
-        <v>2.59</v>
+        <v>4.5</v>
       </c>
       <c r="AC120">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="AD120">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AE120">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AF120">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AG120">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="AH120">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AI120">
         <v>2.15</v>
       </c>
       <c r="AJ120">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AK120">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL120">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AM120">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AN120">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AO120">
         <v>1</v>
       </c>
       <c r="AP120">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AQ120">
-        <v>0.86</v>
+        <v>1.57</v>
       </c>
       <c r="AR120">
-        <v>1.42</v>
+        <v>2.56</v>
       </c>
       <c r="AS120">
-        <v>1.15</v>
+        <v>1.68</v>
       </c>
       <c r="AT120">
-        <v>2.57</v>
+        <v>4.24</v>
       </c>
       <c r="AU120">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV120">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW120">
+        <v>8</v>
+      </c>
+      <c r="AX120">
+        <v>2</v>
+      </c>
+      <c r="AY120">
+        <v>17</v>
+      </c>
+      <c r="AZ120">
+        <v>5</v>
+      </c>
+      <c r="BA120">
+        <v>7</v>
+      </c>
+      <c r="BB120">
+        <v>2</v>
+      </c>
+      <c r="BC120">
         <v>9</v>
       </c>
-      <c r="AX120">
-        <v>8</v>
-      </c>
-      <c r="AY120">
-        <v>9</v>
-      </c>
-      <c r="AZ120">
-        <v>10</v>
-      </c>
-      <c r="BA120">
-        <v>4</v>
-      </c>
-      <c r="BB120">
-        <v>4</v>
-      </c>
-      <c r="BC120">
-        <v>8</v>
-      </c>
       <c r="BD120">
         <v>0</v>
       </c>
@@ -25746,34 +25773,34 @@
         <v>0</v>
       </c>
       <c r="BG120">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BH120">
-        <v>4.85</v>
+        <v>4.96</v>
       </c>
       <c r="BI120">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BJ120">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BK120">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="BL120">
-        <v>2.17</v>
+        <v>2.37</v>
       </c>
       <c r="BM120">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="BN120">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="BO120">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="BP120">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="121" spans="1:68">
@@ -25781,7 +25808,7 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>7845456</v>
+        <v>7845451</v>
       </c>
       <c r="C121" t="s">
         <v>68</v>
@@ -25796,151 +25823,151 @@
         <v>0</v>
       </c>
       <c r="G121" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="H121" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="I121">
         <v>0</v>
       </c>
       <c r="J121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121">
         <v>0</v>
       </c>
       <c r="M121">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N121">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O121" t="s">
         <v>90</v>
       </c>
       <c r="P121" t="s">
-        <v>218</v>
+        <v>90</v>
       </c>
       <c r="Q121">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="R121">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="S121">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="T121">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="U121">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="V121">
         <v>3.6</v>
       </c>
       <c r="W121">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="X121">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="Y121">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Z121">
-        <v>1.75</v>
+        <v>2.81</v>
       </c>
       <c r="AA121">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="AB121">
-        <v>4.5</v>
+        <v>2.59</v>
       </c>
       <c r="AC121">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="AD121">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AE121">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AF121">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AG121">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AH121">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AI121">
         <v>2.15</v>
       </c>
       <c r="AJ121">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AK121">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AL121">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AM121">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="AN121">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AO121">
         <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ121">
-        <v>1.33</v>
+        <v>0.86</v>
       </c>
       <c r="AR121">
-        <v>2.56</v>
+        <v>1.42</v>
       </c>
       <c r="AS121">
-        <v>1.68</v>
+        <v>1.15</v>
       </c>
       <c r="AT121">
-        <v>4.24</v>
+        <v>2.57</v>
       </c>
       <c r="AU121">
+        <v>0</v>
+      </c>
+      <c r="AV121">
+        <v>2</v>
+      </c>
+      <c r="AW121">
         <v>9</v>
       </c>
-      <c r="AV121">
-        <v>3</v>
-      </c>
-      <c r="AW121">
+      <c r="AX121">
         <v>8</v>
       </c>
-      <c r="AX121">
-        <v>2</v>
-      </c>
       <c r="AY121">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AZ121">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BA121">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BB121">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BC121">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD121">
         <v>0</v>
@@ -25952,34 +25979,34 @@
         <v>0</v>
       </c>
       <c r="BG121">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="BH121">
-        <v>4.96</v>
+        <v>4.85</v>
       </c>
       <c r="BI121">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BJ121">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BK121">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="BL121">
-        <v>2.37</v>
+        <v>2.17</v>
       </c>
       <c r="BM121">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="BN121">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="BO121">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="BP121">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="122" spans="1:68">
@@ -25987,7 +26014,7 @@
         <v>121</v>
       </c>
       <c r="B122">
-        <v>7845470</v>
+        <v>7845464</v>
       </c>
       <c r="C122" t="s">
         <v>68</v>
@@ -26002,190 +26029,190 @@
         <v>0</v>
       </c>
       <c r="G122" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H122" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
       <c r="I122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K122">
         <v>1</v>
       </c>
       <c r="L122">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M122">
         <v>3</v>
       </c>
       <c r="N122">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O122" t="s">
-        <v>161</v>
+        <v>90</v>
       </c>
       <c r="P122" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="Q122">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="R122">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="S122">
-        <v>4</v>
+        <v>5.92</v>
       </c>
       <c r="T122">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="U122">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V122">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="W122">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="X122">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y122">
         <v>1.03</v>
       </c>
       <c r="Z122">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AA122">
+        <v>2.9</v>
+      </c>
+      <c r="AB122">
+        <v>5.09</v>
+      </c>
+      <c r="AC122">
+        <v>1.08</v>
+      </c>
+      <c r="AD122">
+        <v>5.5</v>
+      </c>
+      <c r="AE122">
+        <v>1.57</v>
+      </c>
+      <c r="AF122">
+        <v>2.26</v>
+      </c>
+      <c r="AG122">
+        <v>2.86</v>
+      </c>
+      <c r="AH122">
+        <v>1.44</v>
+      </c>
+      <c r="AI122">
+        <v>2.47</v>
+      </c>
+      <c r="AJ122">
+        <v>1.51</v>
+      </c>
+      <c r="AK122">
+        <v>1.28</v>
+      </c>
+      <c r="AL122">
+        <v>1.31</v>
+      </c>
+      <c r="AM122">
+        <v>1.88</v>
+      </c>
+      <c r="AN122">
+        <v>1.5</v>
+      </c>
+      <c r="AO122">
+        <v>0.4</v>
+      </c>
+      <c r="AP122">
+        <v>1.29</v>
+      </c>
+      <c r="AQ122">
+        <v>0.83</v>
+      </c>
+      <c r="AR122">
+        <v>1.6</v>
+      </c>
+      <c r="AS122">
+        <v>1.15</v>
+      </c>
+      <c r="AT122">
+        <v>2.75</v>
+      </c>
+      <c r="AU122">
         <v>3</v>
       </c>
-      <c r="AB122">
-        <v>3.3</v>
-      </c>
-      <c r="AC122">
-        <v>1.07</v>
-      </c>
-      <c r="AD122">
+      <c r="AV122">
         <v>7</v>
       </c>
-      <c r="AE122">
-        <v>1.39</v>
-      </c>
-      <c r="AF122">
-        <v>2.59</v>
-      </c>
-      <c r="AG122">
-        <v>2.37</v>
-      </c>
-      <c r="AH122">
-        <v>1.57</v>
-      </c>
-      <c r="AI122">
-        <v>2</v>
-      </c>
-      <c r="AJ122">
-        <v>1.72</v>
-      </c>
-      <c r="AK122">
-        <v>1.29</v>
-      </c>
-      <c r="AL122">
-        <v>1.36</v>
-      </c>
-      <c r="AM122">
-        <v>1.6</v>
-      </c>
-      <c r="AN122">
-        <v>0.6</v>
-      </c>
-      <c r="AO122">
-        <v>1</v>
-      </c>
-      <c r="AP122">
-        <v>0.67</v>
-      </c>
-      <c r="AQ122">
-        <v>1</v>
-      </c>
-      <c r="AR122">
-        <v>2.02</v>
-      </c>
-      <c r="AS122">
-        <v>1.8</v>
-      </c>
-      <c r="AT122">
-        <v>3.82</v>
-      </c>
-      <c r="AU122">
-        <v>7</v>
-      </c>
-      <c r="AV122">
+      <c r="AW122">
+        <v>9</v>
+      </c>
+      <c r="AX122">
         <v>5</v>
       </c>
-      <c r="AW122">
-        <v>6</v>
-      </c>
-      <c r="AX122">
-        <v>6</v>
-      </c>
       <c r="AY122">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ122">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA122">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB122">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC122">
         <v>8</v>
       </c>
       <c r="BD122">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="BE122">
-        <v>9</v>
+        <v>7.85</v>
       </c>
       <c r="BF122">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="BG122">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="BH122">
-        <v>4.62</v>
+        <v>4.28</v>
       </c>
       <c r="BI122">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="BJ122">
-        <v>3.07</v>
+        <v>2.48</v>
       </c>
       <c r="BK122">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="BL122">
-        <v>2.27</v>
+        <v>1.92</v>
       </c>
       <c r="BM122">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="BN122">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="BO122">
-        <v>2.4</v>
+        <v>2.53</v>
       </c>
       <c r="BP122">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="123" spans="1:68">
@@ -26193,7 +26220,7 @@
         <v>122</v>
       </c>
       <c r="B123">
-        <v>7845464</v>
+        <v>7845470</v>
       </c>
       <c r="C123" t="s">
         <v>68</v>
@@ -26208,190 +26235,190 @@
         <v>0</v>
       </c>
       <c r="G123" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H123" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="I123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K123">
         <v>1</v>
       </c>
       <c r="L123">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M123">
         <v>3</v>
       </c>
       <c r="N123">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O123" t="s">
-        <v>90</v>
+        <v>161</v>
       </c>
       <c r="P123" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="Q123">
-        <v>2.6</v>
+        <v>2.83</v>
       </c>
       <c r="R123">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="S123">
-        <v>5.92</v>
+        <v>4</v>
       </c>
       <c r="T123">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="U123">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V123">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="W123">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="X123">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y123">
         <v>1.03</v>
       </c>
       <c r="Z123">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AA123">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AB123">
-        <v>5.09</v>
+        <v>3.3</v>
       </c>
       <c r="AC123">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AD123">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AE123">
+        <v>1.39</v>
+      </c>
+      <c r="AF123">
+        <v>2.59</v>
+      </c>
+      <c r="AG123">
+        <v>2.37</v>
+      </c>
+      <c r="AH123">
         <v>1.57</v>
       </c>
-      <c r="AF123">
-        <v>2.26</v>
-      </c>
-      <c r="AG123">
-        <v>2.86</v>
-      </c>
-      <c r="AH123">
-        <v>1.44</v>
-      </c>
       <c r="AI123">
-        <v>2.47</v>
+        <v>2</v>
       </c>
       <c r="AJ123">
-        <v>1.51</v>
+        <v>1.72</v>
       </c>
       <c r="AK123">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL123">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AM123">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AN123">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="AO123">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="AP123">
-        <v>1.29</v>
+        <v>0.67</v>
       </c>
       <c r="AQ123">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AR123">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="AS123">
-        <v>1.15</v>
+        <v>1.8</v>
       </c>
       <c r="AT123">
-        <v>2.75</v>
+        <v>3.82</v>
       </c>
       <c r="AU123">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV123">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW123">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX123">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY123">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ123">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA123">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB123">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC123">
         <v>8</v>
       </c>
       <c r="BD123">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="BE123">
-        <v>7.85</v>
+        <v>9</v>
       </c>
       <c r="BF123">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="BG123">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="BH123">
-        <v>4.28</v>
+        <v>4.62</v>
       </c>
       <c r="BI123">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BJ123">
-        <v>2.48</v>
+        <v>3.07</v>
       </c>
       <c r="BK123">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="BL123">
-        <v>1.92</v>
+        <v>2.27</v>
       </c>
       <c r="BM123">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="BN123">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="BO123">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="BP123">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="124" spans="1:68">
@@ -26441,7 +26468,7 @@
         <v>162</v>
       </c>
       <c r="P124" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="Q124">
         <v>2.25</v>
@@ -26811,7 +26838,7 @@
         <v>125</v>
       </c>
       <c r="B126">
-        <v>7845463</v>
+        <v>7845469</v>
       </c>
       <c r="C126" t="s">
         <v>68</v>
@@ -26826,190 +26853,190 @@
         <v>13</v>
       </c>
       <c r="G126" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="H126" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="I126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K126">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L126">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N126">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O126" t="s">
         <v>164</v>
       </c>
       <c r="P126" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Q126">
-        <v>2.7</v>
+        <v>2.86</v>
       </c>
       <c r="R126">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="S126">
-        <v>5.25</v>
+        <v>5.36</v>
       </c>
       <c r="T126">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="U126">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="V126">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="W126">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X126">
         <v>10</v>
       </c>
       <c r="Y126">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Z126">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="AA126">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AB126">
-        <v>4.6</v>
+        <v>3.94</v>
       </c>
       <c r="AC126">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AD126">
-        <v>6.1</v>
+        <v>5.55</v>
       </c>
       <c r="AE126">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="AF126">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AG126">
-        <v>2.91</v>
+        <v>2.85</v>
       </c>
       <c r="AH126">
         <v>1.36</v>
       </c>
       <c r="AI126">
+        <v>2.4</v>
+      </c>
+      <c r="AJ126">
+        <v>1.54</v>
+      </c>
+      <c r="AK126">
+        <v>1.13</v>
+      </c>
+      <c r="AL126">
+        <v>1.34</v>
+      </c>
+      <c r="AM126">
+        <v>1.7</v>
+      </c>
+      <c r="AN126">
+        <v>1.67</v>
+      </c>
+      <c r="AO126">
+        <v>0.83</v>
+      </c>
+      <c r="AP126">
+        <v>1.57</v>
+      </c>
+      <c r="AQ126">
+        <v>0.86</v>
+      </c>
+      <c r="AR126">
+        <v>1.92</v>
+      </c>
+      <c r="AS126">
+        <v>1.4</v>
+      </c>
+      <c r="AT126">
+        <v>3.32</v>
+      </c>
+      <c r="AU126">
+        <v>7</v>
+      </c>
+      <c r="AV126">
+        <v>3</v>
+      </c>
+      <c r="AW126">
+        <v>15</v>
+      </c>
+      <c r="AX126">
+        <v>5</v>
+      </c>
+      <c r="AY126">
+        <v>22</v>
+      </c>
+      <c r="AZ126">
+        <v>8</v>
+      </c>
+      <c r="BA126">
+        <v>10</v>
+      </c>
+      <c r="BB126">
+        <v>4</v>
+      </c>
+      <c r="BC126">
+        <v>14</v>
+      </c>
+      <c r="BD126">
+        <v>1.71</v>
+      </c>
+      <c r="BE126">
+        <v>8.6</v>
+      </c>
+      <c r="BF126">
         <v>2.5</v>
       </c>
-      <c r="AJ126">
-        <v>1.48</v>
-      </c>
-      <c r="AK126">
-        <v>1.38</v>
-      </c>
-      <c r="AL126">
+      <c r="BG126">
+        <v>1.22</v>
+      </c>
+      <c r="BH126">
+        <v>3.8</v>
+      </c>
+      <c r="BI126">
         <v>1.32</v>
       </c>
-      <c r="AM126">
-        <v>1.81</v>
-      </c>
-      <c r="AN126">
-        <v>1.4</v>
-      </c>
-      <c r="AO126">
-        <v>0.5</v>
-      </c>
-      <c r="AP126">
-        <v>1.67</v>
-      </c>
-      <c r="AQ126">
-        <v>0.43</v>
-      </c>
-      <c r="AR126">
-        <v>2.28</v>
-      </c>
-      <c r="AS126">
-        <v>1.08</v>
-      </c>
-      <c r="AT126">
-        <v>3.36</v>
-      </c>
-      <c r="AU126">
-        <v>12</v>
-      </c>
-      <c r="AV126">
-        <v>7</v>
-      </c>
-      <c r="AW126">
-        <v>6</v>
-      </c>
-      <c r="AX126">
-        <v>13</v>
-      </c>
-      <c r="AY126">
-        <v>18</v>
-      </c>
-      <c r="AZ126">
-        <v>20</v>
-      </c>
-      <c r="BA126">
-        <v>7</v>
-      </c>
-      <c r="BB126">
-        <v>3</v>
-      </c>
-      <c r="BC126">
-        <v>10</v>
-      </c>
-      <c r="BD126">
-        <v>1.33</v>
-      </c>
-      <c r="BE126">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="BF126">
-        <v>4.68</v>
-      </c>
-      <c r="BG126">
-        <v>1.21</v>
-      </c>
-      <c r="BH126">
-        <v>3.58</v>
-      </c>
-      <c r="BI126">
-        <v>1.45</v>
-      </c>
       <c r="BJ126">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="BK126">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="BL126">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="BM126">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="BN126">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="BO126">
-        <v>2.96</v>
+        <v>2.46</v>
       </c>
       <c r="BP126">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="127" spans="1:68">
@@ -27017,7 +27044,7 @@
         <v>126</v>
       </c>
       <c r="B127">
-        <v>7845469</v>
+        <v>7845463</v>
       </c>
       <c r="C127" t="s">
         <v>68</v>
@@ -27032,190 +27059,190 @@
         <v>13</v>
       </c>
       <c r="G127" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="H127" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="I127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K127">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L127">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N127">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O127" t="s">
         <v>165</v>
       </c>
       <c r="P127" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="Q127">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="R127">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="S127">
-        <v>5.36</v>
+        <v>5.25</v>
       </c>
       <c r="T127">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U127">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="V127">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="W127">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="X127">
         <v>10</v>
       </c>
       <c r="Y127">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Z127">
-        <v>2.03</v>
+        <v>1.85</v>
       </c>
       <c r="AA127">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="AB127">
-        <v>3.94</v>
+        <v>4.6</v>
       </c>
       <c r="AC127">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AD127">
-        <v>5.55</v>
+        <v>6.1</v>
       </c>
       <c r="AE127">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AF127">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AG127">
-        <v>2.85</v>
+        <v>2.91</v>
       </c>
       <c r="AH127">
         <v>1.36</v>
       </c>
       <c r="AI127">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AJ127">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AK127">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="AL127">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AM127">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="AN127">
+        <v>1.4</v>
+      </c>
+      <c r="AO127">
+        <v>0.5</v>
+      </c>
+      <c r="AP127">
         <v>1.67</v>
       </c>
-      <c r="AO127">
-        <v>0.83</v>
-      </c>
-      <c r="AP127">
+      <c r="AQ127">
+        <v>0.43</v>
+      </c>
+      <c r="AR127">
+        <v>2.28</v>
+      </c>
+      <c r="AS127">
+        <v>1.08</v>
+      </c>
+      <c r="AT127">
+        <v>3.36</v>
+      </c>
+      <c r="AU127">
+        <v>12</v>
+      </c>
+      <c r="AV127">
+        <v>7</v>
+      </c>
+      <c r="AW127">
+        <v>6</v>
+      </c>
+      <c r="AX127">
+        <v>13</v>
+      </c>
+      <c r="AY127">
+        <v>18</v>
+      </c>
+      <c r="AZ127">
+        <v>20</v>
+      </c>
+      <c r="BA127">
+        <v>7</v>
+      </c>
+      <c r="BB127">
+        <v>3</v>
+      </c>
+      <c r="BC127">
+        <v>10</v>
+      </c>
+      <c r="BD127">
+        <v>1.33</v>
+      </c>
+      <c r="BE127">
+        <v>8.949999999999999</v>
+      </c>
+      <c r="BF127">
+        <v>4.68</v>
+      </c>
+      <c r="BG127">
+        <v>1.21</v>
+      </c>
+      <c r="BH127">
+        <v>3.58</v>
+      </c>
+      <c r="BI127">
+        <v>1.45</v>
+      </c>
+      <c r="BJ127">
+        <v>2.5</v>
+      </c>
+      <c r="BK127">
+        <v>1.78</v>
+      </c>
+      <c r="BL127">
+        <v>1.93</v>
+      </c>
+      <c r="BM127">
+        <v>2.18</v>
+      </c>
+      <c r="BN127">
         <v>1.57</v>
       </c>
-      <c r="AQ127">
-        <v>0.86</v>
-      </c>
-      <c r="AR127">
-        <v>1.92</v>
-      </c>
-      <c r="AS127">
-        <v>1.4</v>
-      </c>
-      <c r="AT127">
-        <v>3.32</v>
-      </c>
-      <c r="AU127">
-        <v>7</v>
-      </c>
-      <c r="AV127">
-        <v>3</v>
-      </c>
-      <c r="AW127">
-        <v>15</v>
-      </c>
-      <c r="AX127">
-        <v>5</v>
-      </c>
-      <c r="AY127">
-        <v>22</v>
-      </c>
-      <c r="AZ127">
-        <v>8</v>
-      </c>
-      <c r="BA127">
-        <v>10</v>
-      </c>
-      <c r="BB127">
-        <v>4</v>
-      </c>
-      <c r="BC127">
-        <v>14</v>
-      </c>
-      <c r="BD127">
-        <v>1.71</v>
-      </c>
-      <c r="BE127">
-        <v>8.6</v>
-      </c>
-      <c r="BF127">
-        <v>2.5</v>
-      </c>
-      <c r="BG127">
-        <v>1.22</v>
-      </c>
-      <c r="BH127">
-        <v>3.8</v>
-      </c>
-      <c r="BI127">
-        <v>1.32</v>
-      </c>
-      <c r="BJ127">
-        <v>2.88</v>
-      </c>
-      <c r="BK127">
-        <v>1.6</v>
-      </c>
-      <c r="BL127">
-        <v>2.18</v>
-      </c>
-      <c r="BM127">
-        <v>1.95</v>
-      </c>
-      <c r="BN127">
-        <v>1.75</v>
-      </c>
       <c r="BO127">
-        <v>2.46</v>
+        <v>2.96</v>
       </c>
       <c r="BP127">
-        <v>1.46</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="128" spans="1:68">
@@ -27265,7 +27292,7 @@
         <v>90</v>
       </c>
       <c r="P128" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="Q128">
         <v>3.2</v>
@@ -27471,7 +27498,7 @@
         <v>166</v>
       </c>
       <c r="P129" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="Q129">
         <v>2.68</v>
@@ -28089,7 +28116,7 @@
         <v>90</v>
       </c>
       <c r="P132" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="Q132">
         <v>2.7</v>
@@ -28864,6 +28891,1242 @@
       </c>
       <c r="BP135">
         <v>1.51</v>
+      </c>
+    </row>
+    <row r="136" spans="1:68">
+      <c r="A136" s="1">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>7845477</v>
+      </c>
+      <c r="C136" t="s">
+        <v>68</v>
+      </c>
+      <c r="D136" t="s">
+        <v>69</v>
+      </c>
+      <c r="E136" s="2">
+        <v>45865.6875</v>
+      </c>
+      <c r="F136">
+        <v>14</v>
+      </c>
+      <c r="G136" t="s">
+        <v>78</v>
+      </c>
+      <c r="H136" t="s">
+        <v>80</v>
+      </c>
+      <c r="I136">
+        <v>1</v>
+      </c>
+      <c r="J136">
+        <v>1</v>
+      </c>
+      <c r="K136">
+        <v>2</v>
+      </c>
+      <c r="L136">
+        <v>2</v>
+      </c>
+      <c r="M136">
+        <v>1</v>
+      </c>
+      <c r="N136">
+        <v>3</v>
+      </c>
+      <c r="O136" t="s">
+        <v>171</v>
+      </c>
+      <c r="P136" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q136">
+        <v>2.9</v>
+      </c>
+      <c r="R136">
+        <v>1.77</v>
+      </c>
+      <c r="S136">
+        <v>3.95</v>
+      </c>
+      <c r="T136">
+        <v>1.65</v>
+      </c>
+      <c r="U136">
+        <v>2.15</v>
+      </c>
+      <c r="V136">
+        <v>4.4</v>
+      </c>
+      <c r="W136">
+        <v>1.2</v>
+      </c>
+      <c r="X136">
+        <v>15</v>
+      </c>
+      <c r="Y136">
+        <v>1.02</v>
+      </c>
+      <c r="Z136">
+        <v>2</v>
+      </c>
+      <c r="AA136">
+        <v>2.7</v>
+      </c>
+      <c r="AB136">
+        <v>3.9</v>
+      </c>
+      <c r="AC136">
+        <v>1.13</v>
+      </c>
+      <c r="AD136">
+        <v>4.75</v>
+      </c>
+      <c r="AE136">
+        <v>1.74</v>
+      </c>
+      <c r="AF136">
+        <v>1.96</v>
+      </c>
+      <c r="AG136">
+        <v>2.82</v>
+      </c>
+      <c r="AH136">
+        <v>1.27</v>
+      </c>
+      <c r="AI136">
+        <v>2.65</v>
+      </c>
+      <c r="AJ136">
+        <v>1.4</v>
+      </c>
+      <c r="AK136">
+        <v>1.44</v>
+      </c>
+      <c r="AL136">
+        <v>1.29</v>
+      </c>
+      <c r="AM136">
+        <v>1.72</v>
+      </c>
+      <c r="AN136">
+        <v>3</v>
+      </c>
+      <c r="AO136">
+        <v>2.17</v>
+      </c>
+      <c r="AP136">
+        <v>3</v>
+      </c>
+      <c r="AQ136">
+        <v>1.86</v>
+      </c>
+      <c r="AR136">
+        <v>1.53</v>
+      </c>
+      <c r="AS136">
+        <v>1.63</v>
+      </c>
+      <c r="AT136">
+        <v>3.16</v>
+      </c>
+      <c r="AU136">
+        <v>6</v>
+      </c>
+      <c r="AV136">
+        <v>6</v>
+      </c>
+      <c r="AW136">
+        <v>6</v>
+      </c>
+      <c r="AX136">
+        <v>3</v>
+      </c>
+      <c r="AY136">
+        <v>12</v>
+      </c>
+      <c r="AZ136">
+        <v>9</v>
+      </c>
+      <c r="BA136">
+        <v>5</v>
+      </c>
+      <c r="BB136">
+        <v>3</v>
+      </c>
+      <c r="BC136">
+        <v>8</v>
+      </c>
+      <c r="BD136">
+        <v>1.85</v>
+      </c>
+      <c r="BE136">
+        <v>7.34</v>
+      </c>
+      <c r="BF136">
+        <v>2.7</v>
+      </c>
+      <c r="BG136">
+        <v>1.29</v>
+      </c>
+      <c r="BH136">
+        <v>3.3</v>
+      </c>
+      <c r="BI136">
+        <v>1.5</v>
+      </c>
+      <c r="BJ136">
+        <v>2.35</v>
+      </c>
+      <c r="BK136">
+        <v>1.92</v>
+      </c>
+      <c r="BL136">
+        <v>1.91</v>
+      </c>
+      <c r="BM136">
+        <v>2.25</v>
+      </c>
+      <c r="BN136">
+        <v>1.57</v>
+      </c>
+      <c r="BO136">
+        <v>2.8</v>
+      </c>
+      <c r="BP136">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="137" spans="1:68">
+      <c r="A137" s="1">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>7845478</v>
+      </c>
+      <c r="C137" t="s">
+        <v>68</v>
+      </c>
+      <c r="D137" t="s">
+        <v>69</v>
+      </c>
+      <c r="E137" s="2">
+        <v>45865.6875</v>
+      </c>
+      <c r="F137">
+        <v>14</v>
+      </c>
+      <c r="G137" t="s">
+        <v>71</v>
+      </c>
+      <c r="H137" t="s">
+        <v>82</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>1</v>
+      </c>
+      <c r="K137">
+        <v>1</v>
+      </c>
+      <c r="L137">
+        <v>1</v>
+      </c>
+      <c r="M137">
+        <v>2</v>
+      </c>
+      <c r="N137">
+        <v>3</v>
+      </c>
+      <c r="O137" t="s">
+        <v>126</v>
+      </c>
+      <c r="P137" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q137">
+        <v>2.4</v>
+      </c>
+      <c r="R137">
+        <v>1.86</v>
+      </c>
+      <c r="S137">
+        <v>6.43</v>
+      </c>
+      <c r="T137">
+        <v>1.5</v>
+      </c>
+      <c r="U137">
+        <v>2.26</v>
+      </c>
+      <c r="V137">
+        <v>3.5</v>
+      </c>
+      <c r="W137">
+        <v>1.25</v>
+      </c>
+      <c r="X137">
+        <v>11</v>
+      </c>
+      <c r="Y137">
+        <v>1.02</v>
+      </c>
+      <c r="Z137">
+        <v>1.66</v>
+      </c>
+      <c r="AA137">
+        <v>3</v>
+      </c>
+      <c r="AB137">
+        <v>5.6</v>
+      </c>
+      <c r="AC137">
+        <v>1.06</v>
+      </c>
+      <c r="AD137">
+        <v>6.5</v>
+      </c>
+      <c r="AE137">
+        <v>1.55</v>
+      </c>
+      <c r="AF137">
+        <v>2.35</v>
+      </c>
+      <c r="AG137">
+        <v>2.62</v>
+      </c>
+      <c r="AH137">
+        <v>1.44</v>
+      </c>
+      <c r="AI137">
+        <v>2.4</v>
+      </c>
+      <c r="AJ137">
+        <v>1.42</v>
+      </c>
+      <c r="AK137">
+        <v>1.34</v>
+      </c>
+      <c r="AL137">
+        <v>1.25</v>
+      </c>
+      <c r="AM137">
+        <v>2</v>
+      </c>
+      <c r="AN137">
+        <v>1.5</v>
+      </c>
+      <c r="AO137">
+        <v>0.83</v>
+      </c>
+      <c r="AP137">
+        <v>1.29</v>
+      </c>
+      <c r="AQ137">
+        <v>1.14</v>
+      </c>
+      <c r="AR137">
+        <v>1.91</v>
+      </c>
+      <c r="AS137">
+        <v>1.24</v>
+      </c>
+      <c r="AT137">
+        <v>3.15</v>
+      </c>
+      <c r="AU137">
+        <v>8</v>
+      </c>
+      <c r="AV137">
+        <v>4</v>
+      </c>
+      <c r="AW137">
+        <v>8</v>
+      </c>
+      <c r="AX137">
+        <v>4</v>
+      </c>
+      <c r="AY137">
+        <v>16</v>
+      </c>
+      <c r="AZ137">
+        <v>8</v>
+      </c>
+      <c r="BA137">
+        <v>10</v>
+      </c>
+      <c r="BB137">
+        <v>4</v>
+      </c>
+      <c r="BC137">
+        <v>14</v>
+      </c>
+      <c r="BD137">
+        <v>1.35</v>
+      </c>
+      <c r="BE137">
+        <v>9.4</v>
+      </c>
+      <c r="BF137">
+        <v>4.5</v>
+      </c>
+      <c r="BG137">
+        <v>1.12</v>
+      </c>
+      <c r="BH137">
+        <v>4.33</v>
+      </c>
+      <c r="BI137">
+        <v>1.27</v>
+      </c>
+      <c r="BJ137">
+        <v>3.14</v>
+      </c>
+      <c r="BK137">
+        <v>1.5</v>
+      </c>
+      <c r="BL137">
+        <v>2.28</v>
+      </c>
+      <c r="BM137">
+        <v>1.94</v>
+      </c>
+      <c r="BN137">
+        <v>1.78</v>
+      </c>
+      <c r="BO137">
+        <v>2.44</v>
+      </c>
+      <c r="BP137">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="138" spans="1:68">
+      <c r="A138" s="1">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>7845472</v>
+      </c>
+      <c r="C138" t="s">
+        <v>68</v>
+      </c>
+      <c r="D138" t="s">
+        <v>69</v>
+      </c>
+      <c r="E138" s="2">
+        <v>45865.6875</v>
+      </c>
+      <c r="F138">
+        <v>14</v>
+      </c>
+      <c r="G138" t="s">
+        <v>75</v>
+      </c>
+      <c r="H138" t="s">
+        <v>70</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+      <c r="J138">
+        <v>1</v>
+      </c>
+      <c r="K138">
+        <v>2</v>
+      </c>
+      <c r="L138">
+        <v>3</v>
+      </c>
+      <c r="M138">
+        <v>1</v>
+      </c>
+      <c r="N138">
+        <v>4</v>
+      </c>
+      <c r="O138" t="s">
+        <v>172</v>
+      </c>
+      <c r="P138" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q138">
+        <v>3.3</v>
+      </c>
+      <c r="R138">
+        <v>1.96</v>
+      </c>
+      <c r="S138">
+        <v>3.86</v>
+      </c>
+      <c r="T138">
+        <v>1.53</v>
+      </c>
+      <c r="U138">
+        <v>2.34</v>
+      </c>
+      <c r="V138">
+        <v>3.52</v>
+      </c>
+      <c r="W138">
+        <v>1.29</v>
+      </c>
+      <c r="X138">
+        <v>10</v>
+      </c>
+      <c r="Y138">
+        <v>1.03</v>
+      </c>
+      <c r="Z138">
+        <v>2.4</v>
+      </c>
+      <c r="AA138">
+        <v>3.05</v>
+      </c>
+      <c r="AB138">
+        <v>2.95</v>
+      </c>
+      <c r="AC138">
+        <v>1.04</v>
+      </c>
+      <c r="AD138">
+        <v>6.85</v>
+      </c>
+      <c r="AE138">
+        <v>1.46</v>
+      </c>
+      <c r="AF138">
+        <v>2.43</v>
+      </c>
+      <c r="AG138">
+        <v>2.35</v>
+      </c>
+      <c r="AH138">
+        <v>1.52</v>
+      </c>
+      <c r="AI138">
+        <v>1.93</v>
+      </c>
+      <c r="AJ138">
+        <v>1.72</v>
+      </c>
+      <c r="AK138">
+        <v>1.38</v>
+      </c>
+      <c r="AL138">
+        <v>1.3</v>
+      </c>
+      <c r="AM138">
+        <v>1.55</v>
+      </c>
+      <c r="AN138">
+        <v>1.83</v>
+      </c>
+      <c r="AO138">
+        <v>1.33</v>
+      </c>
+      <c r="AP138">
+        <v>2</v>
+      </c>
+      <c r="AQ138">
+        <v>1.14</v>
+      </c>
+      <c r="AR138">
+        <v>1.56</v>
+      </c>
+      <c r="AS138">
+        <v>1.14</v>
+      </c>
+      <c r="AT138">
+        <v>2.7</v>
+      </c>
+      <c r="AU138">
+        <v>6</v>
+      </c>
+      <c r="AV138">
+        <v>8</v>
+      </c>
+      <c r="AW138">
+        <v>3</v>
+      </c>
+      <c r="AX138">
+        <v>7</v>
+      </c>
+      <c r="AY138">
+        <v>9</v>
+      </c>
+      <c r="AZ138">
+        <v>15</v>
+      </c>
+      <c r="BA138">
+        <v>6</v>
+      </c>
+      <c r="BB138">
+        <v>8</v>
+      </c>
+      <c r="BC138">
+        <v>14</v>
+      </c>
+      <c r="BD138">
+        <v>1.62</v>
+      </c>
+      <c r="BE138">
+        <v>7.75</v>
+      </c>
+      <c r="BF138">
+        <v>3.02</v>
+      </c>
+      <c r="BG138">
+        <v>1.15</v>
+      </c>
+      <c r="BH138">
+        <v>4</v>
+      </c>
+      <c r="BI138">
+        <v>1.34</v>
+      </c>
+      <c r="BJ138">
+        <v>2.77</v>
+      </c>
+      <c r="BK138">
+        <v>1.65</v>
+      </c>
+      <c r="BL138">
+        <v>2.1</v>
+      </c>
+      <c r="BM138">
+        <v>2.04</v>
+      </c>
+      <c r="BN138">
+        <v>1.76</v>
+      </c>
+      <c r="BO138">
+        <v>2.63</v>
+      </c>
+      <c r="BP138">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:68">
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>7845475</v>
+      </c>
+      <c r="C139" t="s">
+        <v>68</v>
+      </c>
+      <c r="D139" t="s">
+        <v>69</v>
+      </c>
+      <c r="E139" s="2">
+        <v>45865.79166666666</v>
+      </c>
+      <c r="F139">
+        <v>14</v>
+      </c>
+      <c r="G139" t="s">
+        <v>77</v>
+      </c>
+      <c r="H139" t="s">
+        <v>84</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>1</v>
+      </c>
+      <c r="K139">
+        <v>1</v>
+      </c>
+      <c r="L139">
+        <v>1</v>
+      </c>
+      <c r="M139">
+        <v>1</v>
+      </c>
+      <c r="N139">
+        <v>2</v>
+      </c>
+      <c r="O139" t="s">
+        <v>156</v>
+      </c>
+      <c r="P139" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q139">
+        <v>2.31</v>
+      </c>
+      <c r="R139">
+        <v>1.84</v>
+      </c>
+      <c r="S139">
+        <v>5.1</v>
+      </c>
+      <c r="T139">
+        <v>1.57</v>
+      </c>
+      <c r="U139">
+        <v>2.3</v>
+      </c>
+      <c r="V139">
+        <v>3.6</v>
+      </c>
+      <c r="W139">
+        <v>1.21</v>
+      </c>
+      <c r="X139">
+        <v>10.5</v>
+      </c>
+      <c r="Y139">
+        <v>1.02</v>
+      </c>
+      <c r="Z139">
+        <v>1.74</v>
+      </c>
+      <c r="AA139">
+        <v>3.1</v>
+      </c>
+      <c r="AB139">
+        <v>5</v>
+      </c>
+      <c r="AC139">
+        <v>1.1</v>
+      </c>
+      <c r="AD139">
+        <v>5.75</v>
+      </c>
+      <c r="AE139">
+        <v>1.55</v>
+      </c>
+      <c r="AF139">
+        <v>2.17</v>
+      </c>
+      <c r="AG139">
+        <v>2.2</v>
+      </c>
+      <c r="AH139">
+        <v>1.55</v>
+      </c>
+      <c r="AI139">
+        <v>2.4</v>
+      </c>
+      <c r="AJ139">
+        <v>1.48</v>
+      </c>
+      <c r="AK139">
+        <v>1.23</v>
+      </c>
+      <c r="AL139">
+        <v>1.19</v>
+      </c>
+      <c r="AM139">
+        <v>2.08</v>
+      </c>
+      <c r="AN139">
+        <v>1.83</v>
+      </c>
+      <c r="AO139">
+        <v>0.43</v>
+      </c>
+      <c r="AP139">
+        <v>1.71</v>
+      </c>
+      <c r="AQ139">
+        <v>0.5</v>
+      </c>
+      <c r="AR139">
+        <v>1.86</v>
+      </c>
+      <c r="AS139">
+        <v>1.66</v>
+      </c>
+      <c r="AT139">
+        <v>3.52</v>
+      </c>
+      <c r="AU139">
+        <v>3</v>
+      </c>
+      <c r="AV139">
+        <v>4</v>
+      </c>
+      <c r="AW139">
+        <v>4</v>
+      </c>
+      <c r="AX139">
+        <v>4</v>
+      </c>
+      <c r="AY139">
+        <v>7</v>
+      </c>
+      <c r="AZ139">
+        <v>8</v>
+      </c>
+      <c r="BA139">
+        <v>9</v>
+      </c>
+      <c r="BB139">
+        <v>3</v>
+      </c>
+      <c r="BC139">
+        <v>12</v>
+      </c>
+      <c r="BD139">
+        <v>1.58</v>
+      </c>
+      <c r="BE139">
+        <v>7.75</v>
+      </c>
+      <c r="BF139">
+        <v>3.25</v>
+      </c>
+      <c r="BG139">
+        <v>1.2</v>
+      </c>
+      <c r="BH139">
+        <v>4.15</v>
+      </c>
+      <c r="BI139">
+        <v>1.33</v>
+      </c>
+      <c r="BJ139">
+        <v>2.83</v>
+      </c>
+      <c r="BK139">
+        <v>1.67</v>
+      </c>
+      <c r="BL139">
+        <v>1.94</v>
+      </c>
+      <c r="BM139">
+        <v>2.05</v>
+      </c>
+      <c r="BN139">
+        <v>1.68</v>
+      </c>
+      <c r="BO139">
+        <v>2.65</v>
+      </c>
+      <c r="BP139">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="140" spans="1:68">
+      <c r="A140" s="1">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>7845474</v>
+      </c>
+      <c r="C140" t="s">
+        <v>68</v>
+      </c>
+      <c r="D140" t="s">
+        <v>69</v>
+      </c>
+      <c r="E140" s="2">
+        <v>45866.8125</v>
+      </c>
+      <c r="F140">
+        <v>14</v>
+      </c>
+      <c r="G140" t="s">
+        <v>88</v>
+      </c>
+      <c r="H140" t="s">
+        <v>86</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>1</v>
+      </c>
+      <c r="M140">
+        <v>1</v>
+      </c>
+      <c r="N140">
+        <v>2</v>
+      </c>
+      <c r="O140" t="s">
+        <v>173</v>
+      </c>
+      <c r="P140" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q140">
+        <v>3.2</v>
+      </c>
+      <c r="R140">
+        <v>1.91</v>
+      </c>
+      <c r="S140">
+        <v>3.45</v>
+      </c>
+      <c r="T140">
+        <v>1.47</v>
+      </c>
+      <c r="U140">
+        <v>2.4</v>
+      </c>
+      <c r="V140">
+        <v>3.2</v>
+      </c>
+      <c r="W140">
+        <v>1.27</v>
+      </c>
+      <c r="X140">
+        <v>10</v>
+      </c>
+      <c r="Y140">
+        <v>1.05</v>
+      </c>
+      <c r="Z140">
+        <v>2.55</v>
+      </c>
+      <c r="AA140">
+        <v>3.03</v>
+      </c>
+      <c r="AB140">
+        <v>2.66</v>
+      </c>
+      <c r="AC140">
+        <v>1.08</v>
+      </c>
+      <c r="AD140">
+        <v>7.5</v>
+      </c>
+      <c r="AE140">
+        <v>1.5</v>
+      </c>
+      <c r="AF140">
+        <v>2.43</v>
+      </c>
+      <c r="AG140">
+        <v>2.4</v>
+      </c>
+      <c r="AH140">
+        <v>1.49</v>
+      </c>
+      <c r="AI140">
+        <v>2.05</v>
+      </c>
+      <c r="AJ140">
+        <v>1.75</v>
+      </c>
+      <c r="AK140">
+        <v>1.3</v>
+      </c>
+      <c r="AL140">
+        <v>1.32</v>
+      </c>
+      <c r="AM140">
+        <v>1.47</v>
+      </c>
+      <c r="AN140">
+        <v>1.33</v>
+      </c>
+      <c r="AO140">
+        <v>1</v>
+      </c>
+      <c r="AP140">
+        <v>1.29</v>
+      </c>
+      <c r="AQ140">
+        <v>1</v>
+      </c>
+      <c r="AR140">
+        <v>1.43</v>
+      </c>
+      <c r="AS140">
+        <v>1.75</v>
+      </c>
+      <c r="AT140">
+        <v>3.18</v>
+      </c>
+      <c r="AU140">
+        <v>5</v>
+      </c>
+      <c r="AV140">
+        <v>4</v>
+      </c>
+      <c r="AW140">
+        <v>11</v>
+      </c>
+      <c r="AX140">
+        <v>15</v>
+      </c>
+      <c r="AY140">
+        <v>16</v>
+      </c>
+      <c r="AZ140">
+        <v>19</v>
+      </c>
+      <c r="BA140">
+        <v>4</v>
+      </c>
+      <c r="BB140">
+        <v>5</v>
+      </c>
+      <c r="BC140">
+        <v>9</v>
+      </c>
+      <c r="BD140">
+        <v>2.21</v>
+      </c>
+      <c r="BE140">
+        <v>8</v>
+      </c>
+      <c r="BF140">
+        <v>2</v>
+      </c>
+      <c r="BG140">
+        <v>1.22</v>
+      </c>
+      <c r="BH140">
+        <v>4.08</v>
+      </c>
+      <c r="BI140">
+        <v>1.4</v>
+      </c>
+      <c r="BJ140">
+        <v>2.78</v>
+      </c>
+      <c r="BK140">
+        <v>1.83</v>
+      </c>
+      <c r="BL140">
+        <v>2.11</v>
+      </c>
+      <c r="BM140">
+        <v>2.05</v>
+      </c>
+      <c r="BN140">
+        <v>1.7</v>
+      </c>
+      <c r="BO140">
+        <v>2.6</v>
+      </c>
+      <c r="BP140">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="141" spans="1:68">
+      <c r="A141" s="1">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>7845480</v>
+      </c>
+      <c r="C141" t="s">
+        <v>68</v>
+      </c>
+      <c r="D141" t="s">
+        <v>69</v>
+      </c>
+      <c r="E141" s="2">
+        <v>45866.8125</v>
+      </c>
+      <c r="F141">
+        <v>14</v>
+      </c>
+      <c r="G141" t="s">
+        <v>73</v>
+      </c>
+      <c r="H141" t="s">
+        <v>87</v>
+      </c>
+      <c r="I141">
+        <v>1</v>
+      </c>
+      <c r="J141">
+        <v>2</v>
+      </c>
+      <c r="K141">
+        <v>3</v>
+      </c>
+      <c r="L141">
+        <v>1</v>
+      </c>
+      <c r="M141">
+        <v>3</v>
+      </c>
+      <c r="N141">
+        <v>4</v>
+      </c>
+      <c r="O141" t="s">
+        <v>174</v>
+      </c>
+      <c r="P141" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q141">
+        <v>2.78</v>
+      </c>
+      <c r="R141">
+        <v>1.93</v>
+      </c>
+      <c r="S141">
+        <v>4.2</v>
+      </c>
+      <c r="T141">
+        <v>1.45</v>
+      </c>
+      <c r="U141">
+        <v>2.45</v>
+      </c>
+      <c r="V141">
+        <v>3.55</v>
+      </c>
+      <c r="W141">
+        <v>1.27</v>
+      </c>
+      <c r="X141">
+        <v>11</v>
+      </c>
+      <c r="Y141">
+        <v>1.04</v>
+      </c>
+      <c r="Z141">
+        <v>2.11</v>
+      </c>
+      <c r="AA141">
+        <v>3</v>
+      </c>
+      <c r="AB141">
+        <v>3.64</v>
+      </c>
+      <c r="AC141">
+        <v>1.09</v>
+      </c>
+      <c r="AD141">
+        <v>6.5</v>
+      </c>
+      <c r="AE141">
+        <v>1.46</v>
+      </c>
+      <c r="AF141">
+        <v>2.6</v>
+      </c>
+      <c r="AG141">
+        <v>2.3</v>
+      </c>
+      <c r="AH141">
+        <v>1.55</v>
+      </c>
+      <c r="AI141">
+        <v>1.87</v>
+      </c>
+      <c r="AJ141">
+        <v>1.67</v>
+      </c>
+      <c r="AK141">
+        <v>1.24</v>
+      </c>
+      <c r="AL141">
+        <v>1.28</v>
+      </c>
+      <c r="AM141">
+        <v>1.75</v>
+      </c>
+      <c r="AN141">
+        <v>1.57</v>
+      </c>
+      <c r="AO141">
+        <v>1.33</v>
+      </c>
+      <c r="AP141">
+        <v>1.38</v>
+      </c>
+      <c r="AQ141">
+        <v>1.57</v>
+      </c>
+      <c r="AR141">
+        <v>1.51</v>
+      </c>
+      <c r="AS141">
+        <v>1.54</v>
+      </c>
+      <c r="AT141">
+        <v>3.05</v>
+      </c>
+      <c r="AU141">
+        <v>5</v>
+      </c>
+      <c r="AV141">
+        <v>4</v>
+      </c>
+      <c r="AW141">
+        <v>12</v>
+      </c>
+      <c r="AX141">
+        <v>5</v>
+      </c>
+      <c r="AY141">
+        <v>17</v>
+      </c>
+      <c r="AZ141">
+        <v>9</v>
+      </c>
+      <c r="BA141">
+        <v>7</v>
+      </c>
+      <c r="BB141">
+        <v>0</v>
+      </c>
+      <c r="BC141">
+        <v>7</v>
+      </c>
+      <c r="BD141">
+        <v>1.73</v>
+      </c>
+      <c r="BE141">
+        <v>8</v>
+      </c>
+      <c r="BF141">
+        <v>3.18</v>
+      </c>
+      <c r="BG141">
+        <v>1.19</v>
+      </c>
+      <c r="BH141">
+        <v>4.1</v>
+      </c>
+      <c r="BI141">
+        <v>1.31</v>
+      </c>
+      <c r="BJ141">
+        <v>3.2</v>
+      </c>
+      <c r="BK141">
+        <v>1.52</v>
+      </c>
+      <c r="BL141">
+        <v>2.25</v>
+      </c>
+      <c r="BM141">
+        <v>1.85</v>
+      </c>
+      <c r="BN141">
+        <v>1.85</v>
+      </c>
+      <c r="BO141">
+        <v>2.5</v>
+      </c>
+      <c r="BP141">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -31010,22 +31010,22 @@
         <v>3.18</v>
       </c>
       <c r="AU140" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV140" t="n">
         <v>4</v>
       </c>
       <c r="AW140" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY140" t="n">
         <v>11</v>
       </c>
-      <c r="AX140" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY140" t="n">
-        <v>16</v>
-      </c>
       <c r="AZ140" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="BA140" t="n">
         <v>4</v>
@@ -31228,22 +31228,22 @@
         <v>3.05</v>
       </c>
       <c r="AU141" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW141" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AX141" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY141" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ141" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA141" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -31010,22 +31010,22 @@
         <v>3.18</v>
       </c>
       <c r="AU140" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV140" t="n">
         <v>4</v>
       </c>
       <c r="AW140" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AX140" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AY140" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ140" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="BA140" t="n">
         <v>4</v>
@@ -31228,22 +31228,22 @@
         <v>3.05</v>
       </c>
       <c r="AU141" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV141" t="n">
         <v>4</v>
       </c>
-      <c r="AV141" t="n">
-        <v>3</v>
-      </c>
       <c r="AW141" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ141" t="n">
         <v>9</v>
-      </c>
-      <c r="AX141" t="n">
-        <v>3</v>
-      </c>
-      <c r="AY141" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ141" t="n">
-        <v>6</v>
       </c>
       <c r="BA141" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP141"/>
+  <dimension ref="A1:BP144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,10 +926,10 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV2" t="n">
         <v>6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>7</v>
       </c>
       <c r="AW2" t="n">
         <v>7</v>
@@ -938,10 +938,10 @@
         <v>9</v>
       </c>
       <c r="AY2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
         <v>5</v>
@@ -1144,10 +1144,10 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW3" t="n">
         <v>13</v>
@@ -1156,10 +1156,10 @@
         <v>8</v>
       </c>
       <c r="AY3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA3" t="n">
         <v>1</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ4" t="n">
         <v>1.14</v>
@@ -1362,10 +1362,10 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW4" t="n">
         <v>11</v>
@@ -1374,10 +1374,10 @@
         <v>3</v>
       </c>
       <c r="AY4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA4" t="n">
         <v>8</v>
@@ -1580,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW5" t="n">
         <v>5</v>
@@ -1592,10 +1592,10 @@
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA5" t="n">
         <v>3</v>
@@ -1798,10 +1798,10 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW6" t="n">
         <v>4</v>
@@ -1810,10 +1810,10 @@
         <v>9</v>
       </c>
       <c r="AY6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
         <v>6</v>
@@ -2016,10 +2016,10 @@
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW7" t="n">
         <v>7</v>
@@ -2028,10 +2028,10 @@
         <v>9</v>
       </c>
       <c r="AY7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>11</v>
       </c>
       <c r="BA7" t="n">
         <v>2</v>
@@ -2234,10 +2234,10 @@
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW8" t="n">
         <v>6</v>
@@ -2246,10 +2246,10 @@
         <v>5</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA8" t="n">
         <v>6</v>
@@ -2452,10 +2452,10 @@
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW9" t="n">
         <v>10</v>
@@ -2464,10 +2464,10 @@
         <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA9" t="n">
         <v>6</v>
@@ -2670,10 +2670,10 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW10" t="n">
         <v>3</v>
@@ -2682,10 +2682,10 @@
         <v>4</v>
       </c>
       <c r="AY10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA10" t="n">
         <v>7</v>
@@ -2888,10 +2888,10 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW11" t="n">
         <v>8</v>
@@ -2900,10 +2900,10 @@
         <v>8</v>
       </c>
       <c r="AY11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA11" t="n">
         <v>5</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.57</v>
@@ -3106,10 +3106,10 @@
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW12" t="n">
         <v>7</v>
@@ -3118,10 +3118,10 @@
         <v>14</v>
       </c>
       <c r="AY12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA12" t="n">
         <v>4</v>
@@ -3312,7 +3312,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3324,10 +3324,10 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV13" t="n">
         <v>4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>5</v>
       </c>
       <c r="AW13" t="n">
         <v>8</v>
@@ -3336,10 +3336,10 @@
         <v>5</v>
       </c>
       <c r="AY13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA13" t="n">
         <v>8</v>
@@ -3542,10 +3542,10 @@
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW14" t="n">
         <v>14</v>
@@ -3554,10 +3554,10 @@
         <v>4</v>
       </c>
       <c r="AY14" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA14" t="n">
         <v>9</v>
@@ -3760,10 +3760,10 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW15" t="n">
         <v>3</v>
@@ -3772,10 +3772,10 @@
         <v>6</v>
       </c>
       <c r="AY15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>9</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>10</v>
       </c>
       <c r="BA15" t="n">
         <v>3</v>
@@ -3978,10 +3978,10 @@
         <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW16" t="n">
         <v>14</v>
@@ -3990,10 +3990,10 @@
         <v>5</v>
       </c>
       <c r="AY16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA16" t="n">
         <v>5</v>
@@ -4196,10 +4196,10 @@
         <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW17" t="n">
         <v>6</v>
@@ -4208,10 +4208,10 @@
         <v>6</v>
       </c>
       <c r="AY17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA17" t="n">
         <v>5</v>
@@ -4414,10 +4414,10 @@
         <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW18" t="n">
         <v>14</v>
@@ -4426,10 +4426,10 @@
         <v>6</v>
       </c>
       <c r="AY18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA18" t="n">
         <v>5</v>
@@ -4620,7 +4620,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4632,10 +4632,10 @@
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW19" t="n">
         <v>4</v>
@@ -4644,10 +4644,10 @@
         <v>12</v>
       </c>
       <c r="AY19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA19" t="n">
         <v>3</v>
@@ -4838,7 +4838,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -4850,10 +4850,10 @@
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW20" t="n">
         <v>3</v>
@@ -4862,10 +4862,10 @@
         <v>10</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA20" t="n">
         <v>2</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.86</v>
@@ -5068,10 +5068,10 @@
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW21" t="n">
         <v>14</v>
@@ -5080,10 +5080,10 @@
         <v>6</v>
       </c>
       <c r="AY21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA21" t="n">
         <v>5</v>
@@ -5277,19 +5277,19 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.7</v>
+        <v>3.44</v>
       </c>
       <c r="AU22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW22" t="n">
         <v>9</v>
@@ -5298,10 +5298,10 @@
         <v>9</v>
       </c>
       <c r="AY22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA22" t="n">
         <v>12</v>
@@ -5495,19 +5495,19 @@
         <v>1.86</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.74</v>
+        <v>2.61</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.26</v>
+        <v>3.99</v>
       </c>
       <c r="AU23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW23" t="n">
         <v>13</v>
@@ -5516,10 +5516,10 @@
         <v>5</v>
       </c>
       <c r="AY23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA23" t="n">
         <v>3</v>
@@ -5710,22 +5710,22 @@
         <v>1.29</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.87</v>
+        <v>2.61</v>
       </c>
       <c r="AU24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW24" t="n">
         <v>5</v>
@@ -5734,10 +5734,10 @@
         <v>2</v>
       </c>
       <c r="AY24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA24" t="n">
         <v>9</v>
@@ -5925,25 +5925,25 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.57</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.17</v>
+        <v>2.91</v>
       </c>
       <c r="AU25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW25" t="n">
         <v>2</v>
@@ -5952,10 +5952,10 @@
         <v>5</v>
       </c>
       <c r="AY25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA25" t="n">
         <v>5</v>
@@ -6149,19 +6149,19 @@
         <v>0.43</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="AU26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW26" t="n">
         <v>8</v>
@@ -6170,10 +6170,10 @@
         <v>6</v>
       </c>
       <c r="AY26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA26" t="n">
         <v>5</v>
@@ -6367,19 +6367,19 @@
         <v>1.57</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.64</v>
+        <v>2.38</v>
       </c>
       <c r="AU27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW27" t="n">
         <v>7</v>
@@ -6388,10 +6388,10 @@
         <v>4</v>
       </c>
       <c r="AY27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA27" t="n">
         <v>6</v>
@@ -6585,16 +6585,16 @@
         <v>1.14</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>0.87</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.06</v>
+        <v>0.93</v>
       </c>
       <c r="AT28" t="n">
-        <v>2.07</v>
+        <v>1.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV28" t="n">
         <v>0</v>
@@ -6603,13 +6603,13 @@
         <v>6</v>
       </c>
       <c r="AX28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA28" t="n">
         <v>9</v>
@@ -6803,19 +6803,19 @@
         <v>1.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.06</v>
+        <v>0.92</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.83</v>
+        <v>0.7</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="AU29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW29" t="n">
         <v>3</v>
@@ -6824,10 +6824,10 @@
         <v>5</v>
       </c>
       <c r="AY29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA29" t="n">
         <v>2</v>
@@ -7021,19 +7021,19 @@
         <v>0.86</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.88</v>
+        <v>0.74</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.86</v>
+        <v>2.59</v>
       </c>
       <c r="AU30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW30" t="n">
         <v>7</v>
@@ -7042,10 +7042,10 @@
         <v>4</v>
       </c>
       <c r="AY30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA30" t="n">
         <v>2</v>
@@ -7236,22 +7236,22 @@
         <v>3</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.86</v>
+        <v>0.73</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AT31" t="n">
-        <v>3.36</v>
+        <v>3.09</v>
       </c>
       <c r="AU31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW31" t="n">
         <v>4</v>
@@ -7260,10 +7260,10 @@
         <v>7</v>
       </c>
       <c r="AY31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ31" t="n">
         <v>8</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>9</v>
       </c>
       <c r="BA31" t="n">
         <v>4</v>
@@ -7451,25 +7451,25 @@
         <v>3</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ32" t="n">
         <v>1.14</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.06</v>
+        <v>0.93</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.86</v>
+        <v>2.59</v>
       </c>
       <c r="AU32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW32" t="n">
         <v>15</v>
@@ -7478,10 +7478,10 @@
         <v>3</v>
       </c>
       <c r="AY32" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ32" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA32" t="n">
         <v>8</v>
@@ -7675,19 +7675,19 @@
         <v>0.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AT33" t="n">
-        <v>3.79</v>
+        <v>3.53</v>
       </c>
       <c r="AU33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW33" t="n">
         <v>13</v>
@@ -7696,10 +7696,10 @@
         <v>6</v>
       </c>
       <c r="AY33" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA33" t="n">
         <v>10</v>
@@ -7893,19 +7893,19 @@
         <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.98</v>
+        <v>2.72</v>
       </c>
       <c r="AU34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV34" t="n">
         <v>7</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>8</v>
       </c>
       <c r="AW34" t="n">
         <v>8</v>
@@ -7914,10 +7914,10 @@
         <v>9</v>
       </c>
       <c r="AY34" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ34" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA34" t="n">
         <v>5</v>
@@ -8105,25 +8105,25 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ35" t="n">
         <v>1.14</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.72</v>
+        <v>0.58</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.18</v>
+        <v>1.91</v>
       </c>
       <c r="AU35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW35" t="n">
         <v>6</v>
@@ -8132,10 +8132,10 @@
         <v>7</v>
       </c>
       <c r="AY35" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ35" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA35" t="n">
         <v>1</v>
@@ -8329,19 +8329,19 @@
         <v>0.86</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="AU36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW36" t="n">
         <v>9</v>
@@ -8350,10 +8350,10 @@
         <v>7</v>
       </c>
       <c r="AY36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA36" t="n">
         <v>7</v>
@@ -8547,13 +8547,13 @@
         <v>0.57</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.46</v>
+        <v>3.19</v>
       </c>
       <c r="AU37" t="n">
         <v>-1</v>
@@ -8765,31 +8765,31 @@
         <v>1.57</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.66</v>
+        <v>3.39</v>
       </c>
       <c r="AU38" t="n">
         <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX38" t="n">
         <v>14</v>
       </c>
       <c r="AY38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ38" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA38" t="n">
         <v>7</v>
@@ -8980,22 +8980,22 @@
         <v>1.38</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AS39" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="AT39" t="n">
-        <v>2.71</v>
+        <v>2.45</v>
       </c>
       <c r="AU39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW39" t="n">
         <v>8</v>
@@ -9004,10 +9004,10 @@
         <v>7</v>
       </c>
       <c r="AY39" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA39" t="n">
         <v>6</v>
@@ -9201,19 +9201,19 @@
         <v>1.67</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AT40" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="AU40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW40" t="n">
         <v>4</v>
@@ -9222,10 +9222,10 @@
         <v>4</v>
       </c>
       <c r="AY40" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA40" t="n">
         <v>8</v>
@@ -9419,19 +9419,19 @@
         <v>1.29</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.03</v>
+        <v>0.9</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="AU41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW41" t="n">
         <v>8</v>
@@ -9440,10 +9440,10 @@
         <v>2</v>
       </c>
       <c r="AY41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ41" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA41" t="n">
         <v>16</v>
@@ -9637,19 +9637,19 @@
         <v>0.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AT42" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="AU42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW42" t="n">
         <v>11</v>
@@ -9658,10 +9658,10 @@
         <v>12</v>
       </c>
       <c r="AY42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA42" t="n">
         <v>3</v>
@@ -9855,19 +9855,19 @@
         <v>1.57</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AT43" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AU43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW43" t="n">
         <v>11</v>
@@ -9876,10 +9876,10 @@
         <v>4</v>
       </c>
       <c r="AY43" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ43" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA43" t="n">
         <v>9</v>
@@ -10073,19 +10073,19 @@
         <v>1.5</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.24</v>
+        <v>1.96</v>
       </c>
       <c r="AU44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW44" t="n">
         <v>11</v>
@@ -10094,10 +10094,10 @@
         <v>11</v>
       </c>
       <c r="AY44" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ44" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA44" t="n">
         <v>4</v>
@@ -10291,19 +10291,19 @@
         <v>1.14</v>
       </c>
       <c r="AR45" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.83</v>
+        <v>0.73</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="AU45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV45" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW45" t="n">
         <v>6</v>
@@ -10312,10 +10312,10 @@
         <v>6</v>
       </c>
       <c r="AY45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA45" t="n">
         <v>2</v>
@@ -10509,19 +10509,19 @@
         <v>0.86</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.17</v>
+        <v>1.03</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.34</v>
+        <v>2.07</v>
       </c>
       <c r="AU46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW46" t="n">
         <v>5</v>
@@ -10530,10 +10530,10 @@
         <v>2</v>
       </c>
       <c r="AY46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA46" t="n">
         <v>9</v>
@@ -10727,13 +10727,13 @@
         <v>0.57</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AT47" t="n">
-        <v>3.12</v>
+        <v>2.85</v>
       </c>
       <c r="AU47" t="n">
         <v>-1</v>
@@ -10939,25 +10939,25 @@
         <v>2</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ48" t="n">
         <v>1</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AT48" t="n">
-        <v>3.61</v>
+        <v>3.35</v>
       </c>
       <c r="AU48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW48" t="n">
         <v>13</v>
@@ -10966,10 +10966,10 @@
         <v>8</v>
       </c>
       <c r="AY48" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA48" t="n">
         <v>10</v>
@@ -11163,19 +11163,19 @@
         <v>0.43</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AS49" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT49" t="n">
-        <v>3.28</v>
+        <v>3.02</v>
       </c>
       <c r="AU49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW49" t="n">
         <v>10</v>
@@ -11184,10 +11184,10 @@
         <v>5</v>
       </c>
       <c r="AY49" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ49" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA49" t="n">
         <v>9</v>
@@ -11381,19 +11381,19 @@
         <v>1.86</v>
       </c>
       <c r="AR50" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AS50" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AT50" t="n">
-        <v>3.37</v>
+        <v>3.11</v>
       </c>
       <c r="AU50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW50" t="n">
         <v>8</v>
@@ -11402,10 +11402,10 @@
         <v>9</v>
       </c>
       <c r="AY50" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ50" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA50" t="n">
         <v>9</v>
@@ -11596,22 +11596,22 @@
         <v>2</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR51" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AS51" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.77</v>
+        <v>2.51</v>
       </c>
       <c r="AU51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV51" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW51" t="n">
         <v>5</v>
@@ -11620,10 +11620,10 @@
         <v>11</v>
       </c>
       <c r="AY51" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ51" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA51" t="n">
         <v>3</v>
@@ -11817,31 +11817,31 @@
         <v>0.86</v>
       </c>
       <c r="AR52" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AS52" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT52" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="AU52" t="n">
         <v>0</v>
       </c>
       <c r="AV52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX52" t="n">
         <v>4</v>
       </c>
       <c r="AY52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ52" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA52" t="n">
         <v>3</v>
@@ -12032,22 +12032,22 @@
         <v>2</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR53" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AS53" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="AT53" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="AU53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW53" t="n">
         <v>7</v>
@@ -12056,10 +12056,10 @@
         <v>6</v>
       </c>
       <c r="AY53" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA53" t="n">
         <v>4</v>
@@ -12253,19 +12253,19 @@
         <v>1.57</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AT54" t="n">
-        <v>2.82</v>
+        <v>2.55</v>
       </c>
       <c r="AU54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV54" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW54" t="n">
         <v>9</v>
@@ -12274,10 +12274,10 @@
         <v>2</v>
       </c>
       <c r="AY54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ54" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA54" t="n">
         <v>3</v>
@@ -12465,25 +12465,25 @@
         <v>1</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.57</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AS55" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="AT55" t="n">
-        <v>3.33</v>
+        <v>3.07</v>
       </c>
       <c r="AU55" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW55" t="n">
         <v>6</v>
@@ -12492,10 +12492,10 @@
         <v>5</v>
       </c>
       <c r="AY55" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA55" t="n">
         <v>8</v>
@@ -12689,19 +12689,19 @@
         <v>1.29</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AS56" t="n">
-        <v>1.12</v>
+        <v>0.98</v>
       </c>
       <c r="AT56" t="n">
-        <v>2.59</v>
+        <v>2.31</v>
       </c>
       <c r="AU56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW56" t="n">
         <v>14</v>
@@ -12710,10 +12710,10 @@
         <v>2</v>
       </c>
       <c r="AY56" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA56" t="n">
         <v>5</v>
@@ -12904,22 +12904,22 @@
         <v>1.33</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR57" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AS57" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AT57" t="n">
-        <v>4.08</v>
+        <v>3.81</v>
       </c>
       <c r="AU57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW57" t="n">
         <v>10</v>
@@ -12928,10 +12928,10 @@
         <v>3</v>
       </c>
       <c r="AY57" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ57" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA57" t="n">
         <v>9</v>
@@ -13125,19 +13125,19 @@
         <v>0</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AT58" t="n">
-        <v>3.19</v>
+        <v>2.91</v>
       </c>
       <c r="AU58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW58" t="n">
         <v>14</v>
@@ -13146,10 +13146,10 @@
         <v>11</v>
       </c>
       <c r="AY58" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ58" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA58" t="n">
         <v>5</v>
@@ -13343,16 +13343,16 @@
         <v>1.14</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AS59" t="n">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="AT59" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="AU59" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV59" t="n">
         <v>0</v>
@@ -13361,13 +13361,13 @@
         <v>6</v>
       </c>
       <c r="AX59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY59" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA59" t="n">
         <v>8</v>
@@ -13561,19 +13561,19 @@
         <v>1.67</v>
       </c>
       <c r="AR60" t="n">
-        <v>2.53</v>
+        <v>2.4</v>
       </c>
       <c r="AS60" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT60" t="n">
-        <v>3.85</v>
+        <v>3.59</v>
       </c>
       <c r="AU60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW60" t="n">
         <v>13</v>
@@ -13582,10 +13582,10 @@
         <v>7</v>
       </c>
       <c r="AY60" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ60" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA60" t="n">
         <v>4</v>
@@ -13773,25 +13773,25 @@
         <v>1.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.14</v>
       </c>
       <c r="AR61" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="AS61" t="n">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AT61" t="n">
-        <v>3.38</v>
+        <v>3.12</v>
       </c>
       <c r="AU61" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV61" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW61" t="n">
         <v>6</v>
@@ -13800,10 +13800,10 @@
         <v>7</v>
       </c>
       <c r="AY61" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ61" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA61" t="n">
         <v>8</v>
@@ -13991,25 +13991,25 @@
         <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.5</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AT62" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="AU62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW62" t="n">
         <v>12</v>
@@ -14018,10 +14018,10 @@
         <v>5</v>
       </c>
       <c r="AY62" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ62" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA62" t="n">
         <v>4</v>
@@ -14215,19 +14215,19 @@
         <v>1.86</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AS63" t="n">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AT63" t="n">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="AU63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV63" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW63" t="n">
         <v>9</v>
@@ -14236,10 +14236,10 @@
         <v>10</v>
       </c>
       <c r="AY63" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ63" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA63" t="n">
         <v>5</v>
@@ -14433,19 +14433,19 @@
         <v>1.29</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AS64" t="n">
-        <v>0.96</v>
+        <v>0.83</v>
       </c>
       <c r="AT64" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="AU64" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW64" t="n">
         <v>17</v>
@@ -14454,10 +14454,10 @@
         <v>7</v>
       </c>
       <c r="AY64" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ64" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA64" t="n">
         <v>3</v>
@@ -14651,19 +14651,19 @@
         <v>1.5</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AT65" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AU65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW65" t="n">
         <v>6</v>
@@ -14672,10 +14672,10 @@
         <v>6</v>
       </c>
       <c r="AY65" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ65" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA65" t="n">
         <v>5</v>
@@ -14869,19 +14869,19 @@
         <v>0.57</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AS66" t="n">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="AT66" t="n">
-        <v>3.42</v>
+        <v>3.15</v>
       </c>
       <c r="AU66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW66" t="n">
         <v>4</v>
@@ -14890,10 +14890,10 @@
         <v>3</v>
       </c>
       <c r="AY66" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ66" t="n">
         <v>6</v>
-      </c>
-      <c r="AZ66" t="n">
-        <v>7</v>
       </c>
       <c r="BA66" t="n">
         <v>3</v>
@@ -15087,16 +15087,16 @@
         <v>0.43</v>
       </c>
       <c r="AR67" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AS67" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AT67" t="n">
-        <v>2.61</v>
+        <v>2.35</v>
       </c>
       <c r="AU67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV67" t="n">
         <v>0</v>
@@ -15105,13 +15105,13 @@
         <v>14</v>
       </c>
       <c r="AX67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY67" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA67" t="n">
         <v>7</v>
@@ -15305,19 +15305,19 @@
         <v>0.86</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.08</v>
+        <v>0.95</v>
       </c>
       <c r="AT68" t="n">
-        <v>2.69</v>
+        <v>2.42</v>
       </c>
       <c r="AU68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW68" t="n">
         <v>4</v>
@@ -15326,10 +15326,10 @@
         <v>7</v>
       </c>
       <c r="AY68" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ68" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA68" t="n">
         <v>0</v>
@@ -15523,19 +15523,19 @@
         <v>1</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS69" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AT69" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="AU69" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV69" t="n">
         <v>5</v>
-      </c>
-      <c r="AV69" t="n">
-        <v>6</v>
       </c>
       <c r="AW69" t="n">
         <v>18</v>
@@ -15544,10 +15544,10 @@
         <v>5</v>
       </c>
       <c r="AY69" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ69" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA69" t="n">
         <v>5</v>
@@ -15741,19 +15741,19 @@
         <v>1.57</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AS70" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT70" t="n">
-        <v>2.78</v>
+        <v>2.52</v>
       </c>
       <c r="AU70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW70" t="n">
         <v>1</v>
@@ -15762,10 +15762,10 @@
         <v>15</v>
       </c>
       <c r="AY70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ70" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA70" t="n">
         <v>1</v>
@@ -15956,22 +15956,22 @@
         <v>1.38</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR71" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AS71" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AT71" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="AU71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW71" t="n">
         <v>10</v>
@@ -15980,10 +15980,10 @@
         <v>2</v>
       </c>
       <c r="AY71" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA71" t="n">
         <v>8</v>
@@ -16171,25 +16171,25 @@
         <v>1</v>
       </c>
       <c r="AP72" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.57</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AT72" t="n">
-        <v>3.37</v>
+        <v>3.1</v>
       </c>
       <c r="AU72" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW72" t="n">
         <v>10</v>
@@ -16198,10 +16198,10 @@
         <v>5</v>
       </c>
       <c r="AY72" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ72" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA72" t="n">
         <v>7</v>
@@ -16392,22 +16392,22 @@
         <v>1.29</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AT73" t="n">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="AU73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV73" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW73" t="n">
         <v>15</v>
@@ -16416,10 +16416,10 @@
         <v>4</v>
       </c>
       <c r="AY73" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ73" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA73" t="n">
         <v>4</v>
@@ -16613,19 +16613,19 @@
         <v>1.67</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AT74" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="AU74" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV74" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW74" t="n">
         <v>5</v>
@@ -16634,10 +16634,10 @@
         <v>10</v>
       </c>
       <c r="AY74" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ74" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA74" t="n">
         <v>3</v>
@@ -16831,19 +16831,19 @@
         <v>0</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AT75" t="n">
-        <v>3.39</v>
+        <v>3.12</v>
       </c>
       <c r="AU75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW75" t="n">
         <v>8</v>
@@ -16852,10 +16852,10 @@
         <v>3</v>
       </c>
       <c r="AY75" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA75" t="n">
         <v>4</v>
@@ -17049,19 +17049,19 @@
         <v>1.57</v>
       </c>
       <c r="AR76" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="AS76" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AT76" t="n">
-        <v>4.21</v>
+        <v>3.95</v>
       </c>
       <c r="AU76" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW76" t="n">
         <v>7</v>
@@ -17070,10 +17070,10 @@
         <v>9</v>
       </c>
       <c r="AY76" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ76" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA76" t="n">
         <v>6</v>
@@ -17267,19 +17267,19 @@
         <v>1.14</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="AT77" t="n">
-        <v>2.8</v>
+        <v>2.56</v>
       </c>
       <c r="AU77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW77" t="n">
         <v>7</v>
@@ -17288,10 +17288,10 @@
         <v>6</v>
       </c>
       <c r="AY77" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ77" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA77" t="n">
         <v>10</v>
@@ -17485,19 +17485,19 @@
         <v>1.14</v>
       </c>
       <c r="AR78" t="n">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AS78" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AT78" t="n">
-        <v>3.59</v>
+        <v>3.35</v>
       </c>
       <c r="AU78" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW78" t="n">
         <v>8</v>
@@ -17506,10 +17506,10 @@
         <v>5</v>
       </c>
       <c r="AY78" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ78" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA78" t="n">
         <v>9</v>
@@ -17700,22 +17700,22 @@
         <v>1.29</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS79" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AT79" t="n">
-        <v>3.01</v>
+        <v>2.74</v>
       </c>
       <c r="AU79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW79" t="n">
         <v>11</v>
@@ -17724,10 +17724,10 @@
         <v>5</v>
       </c>
       <c r="AY79" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ79" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA79" t="n">
         <v>10</v>
@@ -17915,25 +17915,25 @@
         <v>0.33</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ80" t="n">
         <v>1.14</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="AS80" t="n">
-        <v>1.03</v>
+        <v>0.92</v>
       </c>
       <c r="AT80" t="n">
-        <v>2.52</v>
+        <v>2.27</v>
       </c>
       <c r="AU80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW80" t="n">
         <v>9</v>
@@ -17942,10 +17942,10 @@
         <v>8</v>
       </c>
       <c r="AY80" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ80" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA80" t="n">
         <v>4</v>
@@ -18139,19 +18139,19 @@
         <v>0.86</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AT81" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="AU81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW81" t="n">
         <v>12</v>
@@ -18160,10 +18160,10 @@
         <v>3</v>
       </c>
       <c r="AY81" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ81" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA81" t="n">
         <v>12</v>
@@ -18351,25 +18351,25 @@
         <v>1.5</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.5</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AT82" t="n">
-        <v>3.01</v>
+        <v>2.74</v>
       </c>
       <c r="AU82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV82" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW82" t="n">
         <v>7</v>
@@ -18378,10 +18378,10 @@
         <v>12</v>
       </c>
       <c r="AY82" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ82" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA82" t="n">
         <v>3</v>
@@ -18575,19 +18575,19 @@
         <v>1.57</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AT83" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="AU83" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW83" t="n">
         <v>11</v>
@@ -18596,10 +18596,10 @@
         <v>14</v>
       </c>
       <c r="AY83" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ83" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA83" t="n">
         <v>9</v>
@@ -18793,19 +18793,19 @@
         <v>0.57</v>
       </c>
       <c r="AR84" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AS84" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AT84" t="n">
-        <v>3.29</v>
+        <v>3.03</v>
       </c>
       <c r="AU84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW84" t="n">
         <v>11</v>
@@ -18814,10 +18814,10 @@
         <v>4</v>
       </c>
       <c r="AY84" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ84" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA84" t="n">
         <v>7</v>
@@ -19011,19 +19011,19 @@
         <v>1.29</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AS85" t="n">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
       <c r="AT85" t="n">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AU85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW85" t="n">
         <v>11</v>
@@ -19032,10 +19032,10 @@
         <v>6</v>
       </c>
       <c r="AY85" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ85" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA85" t="n">
         <v>7</v>
@@ -19226,22 +19226,22 @@
         <v>2</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AT86" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="AU86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV86" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW86" t="n">
         <v>6</v>
@@ -19250,10 +19250,10 @@
         <v>3</v>
       </c>
       <c r="AY86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ86" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA86" t="n">
         <v>3</v>
@@ -19447,19 +19447,19 @@
         <v>0.43</v>
       </c>
       <c r="AR87" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="AT87" t="n">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="AU87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW87" t="n">
         <v>10</v>
@@ -19468,10 +19468,10 @@
         <v>6</v>
       </c>
       <c r="AY87" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ87" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA87" t="n">
         <v>11</v>
@@ -19665,19 +19665,19 @@
         <v>0.5</v>
       </c>
       <c r="AR88" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT88" t="n">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="AU88" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW88" t="n">
         <v>3</v>
@@ -19686,10 +19686,10 @@
         <v>5</v>
       </c>
       <c r="AY88" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ88" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ88" t="n">
-        <v>11</v>
       </c>
       <c r="BA88" t="n">
         <v>7</v>
@@ -19883,19 +19883,19 @@
         <v>0</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AT89" t="n">
-        <v>3.46</v>
+        <v>3.2</v>
       </c>
       <c r="AU89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW89" t="n">
         <v>5</v>
@@ -19904,10 +19904,10 @@
         <v>6</v>
       </c>
       <c r="AY89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ89" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA89" t="n">
         <v>7</v>
@@ -20095,25 +20095,25 @@
         <v>1.25</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.86</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AS90" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AT90" t="n">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
       <c r="AU90" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW90" t="n">
         <v>3</v>
@@ -20122,10 +20122,10 @@
         <v>4</v>
       </c>
       <c r="AY90" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ90" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA90" t="n">
         <v>4</v>
@@ -20319,19 +20319,19 @@
         <v>1</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AT91" t="n">
-        <v>3.25</v>
+        <v>3.01</v>
       </c>
       <c r="AU91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV91" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW91" t="n">
         <v>9</v>
@@ -20340,10 +20340,10 @@
         <v>7</v>
       </c>
       <c r="AY91" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ91" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA91" t="n">
         <v>5</v>
@@ -20537,19 +20537,19 @@
         <v>0.86</v>
       </c>
       <c r="AR92" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AS92" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AT92" t="n">
-        <v>2.93</v>
+        <v>2.66</v>
       </c>
       <c r="AU92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW92" t="n">
         <v>7</v>
@@ -20558,10 +20558,10 @@
         <v>6</v>
       </c>
       <c r="AY92" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ92" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA92" t="n">
         <v>7</v>
@@ -20755,31 +20755,31 @@
         <v>1.67</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AT93" t="n">
-        <v>3.07</v>
+        <v>2.81</v>
       </c>
       <c r="AU93" t="n">
         <v>0</v>
       </c>
       <c r="AV93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX93" t="n">
         <v>13</v>
       </c>
       <c r="AY93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ93" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA93" t="n">
         <v>0</v>
@@ -20973,19 +20973,19 @@
         <v>1.86</v>
       </c>
       <c r="AR94" t="n">
-        <v>2.68</v>
+        <v>2.55</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AT94" t="n">
-        <v>4.47</v>
+        <v>4.21</v>
       </c>
       <c r="AU94" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW94" t="n">
         <v>8</v>
@@ -20994,10 +20994,10 @@
         <v>8</v>
       </c>
       <c r="AY94" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ94" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA94" t="n">
         <v>7</v>
@@ -21191,19 +21191,19 @@
         <v>1.14</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AT95" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="AU95" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW95" t="n">
         <v>12</v>
@@ -21212,10 +21212,10 @@
         <v>8</v>
       </c>
       <c r="AY95" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ95" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA95" t="n">
         <v>8</v>
@@ -21409,19 +21409,19 @@
         <v>0.5</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AT96" t="n">
-        <v>3.39</v>
+        <v>3.13</v>
       </c>
       <c r="AU96" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV96" t="n">
         <v>6</v>
-      </c>
-      <c r="AV96" t="n">
-        <v>7</v>
       </c>
       <c r="AW96" t="n">
         <v>9</v>
@@ -21430,10 +21430,10 @@
         <v>14</v>
       </c>
       <c r="AY96" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ96" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA96" t="n">
         <v>8</v>
@@ -21621,25 +21621,25 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ97" t="n">
         <v>1.14</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AT97" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="AU97" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV97" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW97" t="n">
         <v>15</v>
@@ -21648,10 +21648,10 @@
         <v>3</v>
       </c>
       <c r="AY97" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ97" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA97" t="n">
         <v>15</v>
@@ -21845,19 +21845,19 @@
         <v>1.57</v>
       </c>
       <c r="AR98" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="AT98" t="n">
-        <v>2.79</v>
+        <v>2.55</v>
       </c>
       <c r="AU98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW98" t="n">
         <v>9</v>
@@ -21866,10 +21866,10 @@
         <v>9</v>
       </c>
       <c r="AY98" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ98" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA98" t="n">
         <v>4</v>
@@ -22063,19 +22063,19 @@
         <v>1.14</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="AT99" t="n">
-        <v>2.63</v>
+        <v>2.39</v>
       </c>
       <c r="AU99" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW99" t="n">
         <v>7</v>
@@ -22084,10 +22084,10 @@
         <v>2</v>
       </c>
       <c r="AY99" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA99" t="n">
         <v>8</v>
@@ -22281,19 +22281,19 @@
         <v>1.57</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AS100" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AT100" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="AU100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV100" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW100" t="n">
         <v>11</v>
@@ -22302,10 +22302,10 @@
         <v>7</v>
       </c>
       <c r="AY100" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ100" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA100" t="n">
         <v>4</v>
@@ -22496,22 +22496,22 @@
         <v>2</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AS101" t="n">
-        <v>1.12</v>
+        <v>0.99</v>
       </c>
       <c r="AT101" t="n">
-        <v>2.76</v>
+        <v>2.5</v>
       </c>
       <c r="AU101" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW101" t="n">
         <v>5</v>
@@ -22520,10 +22520,10 @@
         <v>4</v>
       </c>
       <c r="AY101" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ101" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA101" t="n">
         <v>5</v>
@@ -22717,19 +22717,19 @@
         <v>0.86</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT102" t="n">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
       <c r="AU102" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW102" t="n">
         <v>6</v>
@@ -22738,10 +22738,10 @@
         <v>6</v>
       </c>
       <c r="AY102" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ102" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA102" t="n">
         <v>7</v>
@@ -22935,19 +22935,19 @@
         <v>0.57</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AT103" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="AU103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV103" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW103" t="n">
         <v>11</v>
@@ -22956,10 +22956,10 @@
         <v>5</v>
       </c>
       <c r="AY103" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ103" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA103" t="n">
         <v>4</v>
@@ -23147,25 +23147,25 @@
         <v>1.2</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.29</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AT104" t="n">
-        <v>2.91</v>
+        <v>2.65</v>
       </c>
       <c r="AU104" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV104" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW104" t="n">
         <v>13</v>
@@ -23174,10 +23174,10 @@
         <v>5</v>
       </c>
       <c r="AY104" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ104" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA104" t="n">
         <v>6</v>
@@ -23371,19 +23371,19 @@
         <v>1.5</v>
       </c>
       <c r="AR105" t="n">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT105" t="n">
-        <v>3.98</v>
+        <v>3.71</v>
       </c>
       <c r="AU105" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW105" t="n">
         <v>6</v>
@@ -23392,10 +23392,10 @@
         <v>9</v>
       </c>
       <c r="AY105" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ105" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA105" t="n">
         <v>4</v>
@@ -23586,22 +23586,22 @@
         <v>2</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AT106" t="n">
-        <v>3.41</v>
+        <v>3.15</v>
       </c>
       <c r="AU106" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV106" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW106" t="n">
         <v>7</v>
@@ -23610,10 +23610,10 @@
         <v>4</v>
       </c>
       <c r="AY106" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ106" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA106" t="n">
         <v>5</v>
@@ -23807,19 +23807,19 @@
         <v>0</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AT107" t="n">
-        <v>3.33</v>
+        <v>3.06</v>
       </c>
       <c r="AU107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV107" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW107" t="n">
         <v>5</v>
@@ -23828,10 +23828,10 @@
         <v>14</v>
       </c>
       <c r="AY107" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ107" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA107" t="n">
         <v>4</v>
@@ -24025,19 +24025,19 @@
         <v>1</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.45</v>
+        <v>1.32</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
       <c r="AT108" t="n">
-        <v>3.27</v>
+        <v>3</v>
       </c>
       <c r="AU108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV108" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW108" t="n">
         <v>5</v>
@@ -24046,10 +24046,10 @@
         <v>9</v>
       </c>
       <c r="AY108" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ108" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA108" t="n">
         <v>3</v>
@@ -24240,22 +24240,22 @@
         <v>1.43</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR109" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AT109" t="n">
-        <v>2.65</v>
+        <v>2.38</v>
       </c>
       <c r="AU109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW109" t="n">
         <v>9</v>
@@ -24264,10 +24264,10 @@
         <v>11</v>
       </c>
       <c r="AY109" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ109" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA109" t="n">
         <v>4</v>
@@ -24455,22 +24455,22 @@
         <v>0.6</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.43</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AT110" t="n">
-        <v>2.61</v>
+        <v>2.36</v>
       </c>
       <c r="AU110" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV110" t="n">
         <v>0</v>
@@ -24479,13 +24479,13 @@
         <v>8</v>
       </c>
       <c r="AX110" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY110" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ110" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA110" t="n">
         <v>3</v>
@@ -24679,19 +24679,19 @@
         <v>1.57</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AT111" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AU111" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV111" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW111" t="n">
         <v>13</v>
@@ -24700,10 +24700,10 @@
         <v>8</v>
       </c>
       <c r="AY111" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ111" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA111" t="n">
         <v>7</v>
@@ -24897,19 +24897,19 @@
         <v>0.5</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="AT112" t="n">
-        <v>3.24</v>
+        <v>2.96</v>
       </c>
       <c r="AU112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW112" t="n">
         <v>8</v>
@@ -24918,10 +24918,10 @@
         <v>11</v>
       </c>
       <c r="AY112" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ112" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA112" t="n">
         <v>3</v>
@@ -25115,19 +25115,19 @@
         <v>1.86</v>
       </c>
       <c r="AR113" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AT113" t="n">
-        <v>3.72</v>
+        <v>3.45</v>
       </c>
       <c r="AU113" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW113" t="n">
         <v>4</v>
@@ -25136,10 +25136,10 @@
         <v>6</v>
       </c>
       <c r="AY113" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ113" t="n">
         <v>8</v>
-      </c>
-      <c r="AZ113" t="n">
-        <v>9</v>
       </c>
       <c r="BA113" t="n">
         <v>4</v>
@@ -25333,19 +25333,19 @@
         <v>1.5</v>
       </c>
       <c r="AR114" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="AS114" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT114" t="n">
-        <v>3.03</v>
+        <v>2.78</v>
       </c>
       <c r="AU114" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV114" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW114" t="n">
         <v>5</v>
@@ -25354,10 +25354,10 @@
         <v>12</v>
       </c>
       <c r="AY114" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ114" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA114" t="n">
         <v>2</v>
@@ -25551,19 +25551,19 @@
         <v>1.14</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.1</v>
+        <v>0.98</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AU115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW115" t="n">
         <v>9</v>
@@ -25572,10 +25572,10 @@
         <v>6</v>
       </c>
       <c r="AY115" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ115" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA115" t="n">
         <v>6</v>
@@ -25769,19 +25769,19 @@
         <v>1.67</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS116" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AT116" t="n">
-        <v>3.08</v>
+        <v>2.82</v>
       </c>
       <c r="AU116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW116" t="n">
         <v>6</v>
@@ -25790,10 +25790,10 @@
         <v>9</v>
       </c>
       <c r="AY116" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ116" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA116" t="n">
         <v>7</v>
@@ -25987,19 +25987,19 @@
         <v>1.14</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="AU117" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW117" t="n">
         <v>11</v>
@@ -26008,10 +26008,10 @@
         <v>7</v>
       </c>
       <c r="AY117" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ117" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA117" t="n">
         <v>4</v>
@@ -26205,19 +26205,19 @@
         <v>1.57</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AT118" t="n">
-        <v>3.24</v>
+        <v>2.98</v>
       </c>
       <c r="AU118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW118" t="n">
         <v>7</v>
@@ -26226,10 +26226,10 @@
         <v>2</v>
       </c>
       <c r="AY118" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ118" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA118" t="n">
         <v>6</v>
@@ -26423,16 +26423,16 @@
         <v>1.14</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AT119" t="n">
-        <v>2.86</v>
+        <v>2.6</v>
       </c>
       <c r="AU119" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV119" t="n">
         <v>0</v>
@@ -26441,13 +26441,13 @@
         <v>9</v>
       </c>
       <c r="AX119" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY119" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ119" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA119" t="n">
         <v>10</v>
@@ -26641,19 +26641,19 @@
         <v>1.57</v>
       </c>
       <c r="AR120" t="n">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="AT120" t="n">
-        <v>4.24</v>
+        <v>3.98</v>
       </c>
       <c r="AU120" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV120" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW120" t="n">
         <v>8</v>
@@ -26662,10 +26662,10 @@
         <v>2</v>
       </c>
       <c r="AY120" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ120" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA120" t="n">
         <v>7</v>
@@ -26859,31 +26859,31 @@
         <v>0.86</v>
       </c>
       <c r="AR121" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="AT121" t="n">
-        <v>2.57</v>
+        <v>2.32</v>
       </c>
       <c r="AU121" t="n">
         <v>0</v>
       </c>
       <c r="AV121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW121" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX121" t="n">
         <v>8</v>
       </c>
       <c r="AY121" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ121" t="n">
         <v>9</v>
-      </c>
-      <c r="AZ121" t="n">
-        <v>10</v>
       </c>
       <c r="BA121" t="n">
         <v>4</v>
@@ -27074,22 +27074,22 @@
         <v>1.29</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="AU122" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV122" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW122" t="n">
         <v>9</v>
@@ -27098,10 +27098,10 @@
         <v>5</v>
       </c>
       <c r="AY122" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ122" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA122" t="n">
         <v>3</v>
@@ -27289,25 +27289,25 @@
         <v>1</v>
       </c>
       <c r="AP123" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="AQ123" t="n">
         <v>1</v>
       </c>
       <c r="AR123" t="n">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AT123" t="n">
-        <v>3.82</v>
+        <v>3.56</v>
       </c>
       <c r="AU123" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV123" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW123" t="n">
         <v>6</v>
@@ -27316,10 +27316,10 @@
         <v>6</v>
       </c>
       <c r="AY123" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ123" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA123" t="n">
         <v>4</v>
@@ -27507,25 +27507,25 @@
         <v>1</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.86</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT124" t="n">
-        <v>2.71</v>
+        <v>2.44</v>
       </c>
       <c r="AU124" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW124" t="n">
         <v>10</v>
@@ -27534,10 +27534,10 @@
         <v>4</v>
       </c>
       <c r="AY124" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ124" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA124" t="n">
         <v>8</v>
@@ -27731,19 +27731,19 @@
         <v>0</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AT125" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="AU125" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW125" t="n">
         <v>11</v>
@@ -27752,10 +27752,10 @@
         <v>0</v>
       </c>
       <c r="AY125" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA125" t="n">
         <v>2</v>
@@ -27943,25 +27943,25 @@
         <v>0.83</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT126" t="n">
-        <v>3.32</v>
+        <v>3.06</v>
       </c>
       <c r="AU126" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW126" t="n">
         <v>15</v>
@@ -27970,10 +27970,10 @@
         <v>5</v>
       </c>
       <c r="AY126" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ126" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA126" t="n">
         <v>10</v>
@@ -28167,19 +28167,19 @@
         <v>0.43</v>
       </c>
       <c r="AR127" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AS127" t="n">
-        <v>1.08</v>
+        <v>0.97</v>
       </c>
       <c r="AT127" t="n">
-        <v>3.36</v>
+        <v>3.12</v>
       </c>
       <c r="AU127" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV127" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW127" t="n">
         <v>6</v>
@@ -28188,10 +28188,10 @@
         <v>13</v>
       </c>
       <c r="AY127" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ127" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA127" t="n">
         <v>7</v>
@@ -28385,19 +28385,19 @@
         <v>1.57</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AT128" t="n">
-        <v>3.01</v>
+        <v>2.75</v>
       </c>
       <c r="AU128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV128" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW128" t="n">
         <v>4</v>
@@ -28406,10 +28406,10 @@
         <v>3</v>
       </c>
       <c r="AY128" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ128" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA128" t="n">
         <v>3</v>
@@ -28603,19 +28603,19 @@
         <v>0.57</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.68</v>
+        <v>2.41</v>
       </c>
       <c r="AU129" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW129" t="n">
         <v>15</v>
@@ -28624,10 +28624,10 @@
         <v>0</v>
       </c>
       <c r="AY129" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA129" t="n">
         <v>9</v>
@@ -28821,16 +28821,16 @@
         <v>1.29</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.22</v>
+        <v>1.09</v>
       </c>
       <c r="AT130" t="n">
-        <v>2.82</v>
+        <v>2.57</v>
       </c>
       <c r="AU130" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV130" t="n">
         <v>0</v>
@@ -28839,13 +28839,13 @@
         <v>13</v>
       </c>
       <c r="AX130" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY130" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ130" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA130" t="n">
         <v>8</v>
@@ -29036,22 +29036,22 @@
         <v>1.43</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AT131" t="n">
-        <v>3.26</v>
+        <v>2.99</v>
       </c>
       <c r="AU131" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW131" t="n">
         <v>6</v>
@@ -29060,10 +29060,10 @@
         <v>12</v>
       </c>
       <c r="AY131" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ131" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA131" t="n">
         <v>2</v>
@@ -29257,19 +29257,19 @@
         <v>1.57</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AT132" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="AU132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV132" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW132" t="n">
         <v>9</v>
@@ -29278,10 +29278,10 @@
         <v>5</v>
       </c>
       <c r="AY132" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ132" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA132" t="n">
         <v>5</v>
@@ -29475,19 +29475,19 @@
         <v>1.5</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.64</v>
+        <v>1.51</v>
       </c>
       <c r="AT133" t="n">
-        <v>3.26</v>
+        <v>3</v>
       </c>
       <c r="AU133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV133" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW133" t="n">
         <v>5</v>
@@ -29496,10 +29496,10 @@
         <v>9</v>
       </c>
       <c r="AY133" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ133" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA133" t="n">
         <v>2</v>
@@ -29693,19 +29693,19 @@
         <v>1.14</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.19</v>
+        <v>1.07</v>
       </c>
       <c r="AT134" t="n">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="AU134" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV134" t="n">
         <v>4</v>
-      </c>
-      <c r="AV134" t="n">
-        <v>5</v>
       </c>
       <c r="AW134" t="n">
         <v>8</v>
@@ -29714,10 +29714,10 @@
         <v>10</v>
       </c>
       <c r="AY134" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ134" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA134" t="n">
         <v>7</v>
@@ -29911,19 +29911,19 @@
         <v>0.86</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.84</v>
+        <v>1.7</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AT135" t="n">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="AU135" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW135" t="n">
         <v>6</v>
@@ -29932,10 +29932,10 @@
         <v>5</v>
       </c>
       <c r="AY135" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ135" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA135" t="n">
         <v>6</v>
@@ -30129,19 +30129,19 @@
         <v>1.86</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AT136" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="AU136" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV136" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW136" t="n">
         <v>6</v>
@@ -30150,10 +30150,10 @@
         <v>3</v>
       </c>
       <c r="AY136" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ136" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA136" t="n">
         <v>5</v>
@@ -30347,19 +30347,19 @@
         <v>1.14</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AS137" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AT137" t="n">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="AU137" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV137" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW137" t="n">
         <v>8</v>
@@ -30368,10 +30368,10 @@
         <v>4</v>
       </c>
       <c r="AY137" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ137" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA137" t="n">
         <v>10</v>
@@ -30565,19 +30565,19 @@
         <v>1.14</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="AT138" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AU138" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV138" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW138" t="n">
         <v>3</v>
@@ -30586,10 +30586,10 @@
         <v>7</v>
       </c>
       <c r="AY138" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ138" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA138" t="n">
         <v>6</v>
@@ -30783,19 +30783,19 @@
         <v>0.5</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AT139" t="n">
-        <v>3.52</v>
+        <v>3.25</v>
       </c>
       <c r="AU139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV139" t="n">
         <v>3</v>
-      </c>
-      <c r="AV139" t="n">
-        <v>4</v>
       </c>
       <c r="AW139" t="n">
         <v>4</v>
@@ -30804,10 +30804,10 @@
         <v>4</v>
       </c>
       <c r="AY139" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ139" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ139" t="n">
-        <v>8</v>
       </c>
       <c r="BA139" t="n">
         <v>9</v>
@@ -31001,19 +31001,19 @@
         <v>1</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AT140" t="n">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
       <c r="AU140" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW140" t="n">
         <v>11</v>
@@ -31022,10 +31022,10 @@
         <v>15</v>
       </c>
       <c r="AY140" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ140" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA140" t="n">
         <v>4</v>
@@ -31219,19 +31219,19 @@
         <v>1.57</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AS141" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="AT141" t="n">
-        <v>3.05</v>
+        <v>2.79</v>
       </c>
       <c r="AU141" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV141" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW141" t="n">
         <v>12</v>
@@ -31240,10 +31240,10 @@
         <v>5</v>
       </c>
       <c r="AY141" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ141" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA141" t="n">
         <v>7</v>
@@ -31292,6 +31292,660 @@
       </c>
       <c r="BP141" t="n">
         <v>1.44</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="n">
+        <v>7845489</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>45871.70833333334</v>
+      </c>
+      <c r="F142" t="n">
+        <v>15</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>CSA</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Botafogo PB</t>
+        </is>
+      </c>
+      <c r="I142" t="n">
+        <v>1</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1</v>
+      </c>
+      <c r="L142" t="n">
+        <v>2</v>
+      </c>
+      <c r="M142" t="n">
+        <v>1</v>
+      </c>
+      <c r="N142" t="n">
+        <v>3</v>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>['35', '90+3']</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R142" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S142" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="T142" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U142" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V142" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="W142" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X142" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="n">
+        <v>7845482</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>45871.70833333334</v>
+      </c>
+      <c r="F143" t="n">
+        <v>15</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>1</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1</v>
+      </c>
+      <c r="N143" t="n">
+        <v>2</v>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R143" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S143" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T143" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U143" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V143" t="n">
+        <v>4</v>
+      </c>
+      <c r="W143" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X143" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="n">
+        <v>7845490</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>45871.8125</v>
+      </c>
+      <c r="F144" t="n">
+        <v>15</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R144" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S144" t="n">
+        <v>4</v>
+      </c>
+      <c r="T144" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U144" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V144" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="W144" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X144" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BF144" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG144" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH144" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="BI144" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BJ144" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK144" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL144" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BM144" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN144" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO144" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BP144" t="n">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP144"/>
+  <dimension ref="A1:BP148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1786,7 +1786,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.5</v>
@@ -2658,7 +2658,7 @@
         <v>3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3094,7 +3094,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.71</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
@@ -3966,7 +3966,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.57</v>
@@ -6146,7 +6146,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR26" t="n">
         <v>1.64</v>
@@ -7018,7 +7018,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR30" t="n">
         <v>1.85</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.5</v>
@@ -8323,7 +8323,7 @@
         <v>1</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.86</v>
@@ -8544,7 +8544,7 @@
         <v>2</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR37" t="n">
         <v>1.25</v>
@@ -8759,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.57</v>
@@ -9195,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.67</v>
@@ -9416,7 +9416,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR41" t="n">
         <v>1.73</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.5</v>
@@ -10506,7 +10506,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR46" t="n">
         <v>1.03</v>
@@ -10724,7 +10724,7 @@
         <v>3</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR47" t="n">
         <v>0.91</v>
@@ -11160,7 +11160,7 @@
         <v>2</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR49" t="n">
         <v>1.83</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.57</v>
@@ -12683,10 +12683,10 @@
         <v>1.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR56" t="n">
         <v>1.33</v>
@@ -12901,7 +12901,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.71</v>
@@ -14209,7 +14209,7 @@
         <v>2.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.86</v>
@@ -14430,7 +14430,7 @@
         <v>2</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR64" t="n">
         <v>1.23</v>
@@ -14866,7 +14866,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR66" t="n">
         <v>1.21</v>
@@ -15081,10 +15081,10 @@
         <v>0.67</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR67" t="n">
         <v>1.18</v>
@@ -15302,7 +15302,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR68" t="n">
         <v>1.47</v>
@@ -17479,7 +17479,7 @@
         <v>2</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ78" t="n">
         <v>1.14</v>
@@ -18133,7 +18133,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.86</v>
@@ -18790,7 +18790,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR84" t="n">
         <v>1.58</v>
@@ -19008,7 +19008,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR85" t="n">
         <v>1.09</v>
@@ -19444,7 +19444,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR87" t="n">
         <v>1.06</v>
@@ -19659,7 +19659,7 @@
         <v>0.25</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ88" t="n">
         <v>0.5</v>
@@ -20098,7 +20098,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR90" t="n">
         <v>1.76</v>
@@ -20313,7 +20313,7 @@
         <v>1.25</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ91" t="n">
         <v>1</v>
@@ -20967,7 +20967,7 @@
         <v>2.5</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.86</v>
@@ -21185,7 +21185,7 @@
         <v>1.25</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ95" t="n">
         <v>1.14</v>
@@ -22711,10 +22711,10 @@
         <v>1</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR102" t="n">
         <v>1.44</v>
@@ -22932,7 +22932,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR103" t="n">
         <v>1.42</v>
@@ -23150,7 +23150,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR104" t="n">
         <v>1.64</v>
@@ -24019,7 +24019,7 @@
         <v>1</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ108" t="n">
         <v>1</v>
@@ -24458,7 +24458,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR110" t="n">
         <v>1.34</v>
@@ -25109,7 +25109,7 @@
         <v>2.6</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.86</v>
@@ -26635,7 +26635,7 @@
         <v>1</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.57</v>
@@ -27510,7 +27510,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AR124" t="n">
         <v>1.39</v>
@@ -28164,7 +28164,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AR127" t="n">
         <v>2.15</v>
@@ -28379,7 +28379,7 @@
         <v>1.33</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.57</v>
@@ -28600,7 +28600,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AR129" t="n">
         <v>1.23</v>
@@ -28815,10 +28815,10 @@
         <v>1.5</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AR130" t="n">
         <v>1.48</v>
@@ -30777,7 +30777,7 @@
         <v>0.43</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AQ139" t="n">
         <v>0.5</v>
@@ -31946,6 +31946,878 @@
       </c>
       <c r="BP144" t="n">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="n">
+        <v>7845485</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>45872.6875</v>
+      </c>
+      <c r="F145" t="n">
+        <v>15</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Tombense</t>
+        </is>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>2</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="n">
+        <v>2</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>['56', '79']</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R145" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S145" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="T145" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U145" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V145" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W145" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X145" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB145" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI145" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ145" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK145" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL145" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM145" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN145" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO145" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BP145" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="n">
+        <v>7845486</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>45872.6875</v>
+      </c>
+      <c r="F146" t="n">
+        <v>15</v>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Maringá</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Floresta</t>
+        </is>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>1</v>
+      </c>
+      <c r="K146" t="n">
+        <v>1</v>
+      </c>
+      <c r="L146" t="n">
+        <v>1</v>
+      </c>
+      <c r="M146" t="n">
+        <v>1</v>
+      </c>
+      <c r="N146" t="n">
+        <v>2</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R146" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S146" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="T146" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U146" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V146" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W146" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X146" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT146" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="AU146" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB146" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BE146" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BF146" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG146" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH146" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI146" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ146" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BK146" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL146" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BM146" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN146" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO146" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP146" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="n">
+        <v>7845487</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>45872.79166666666</v>
+      </c>
+      <c r="F147" t="n">
+        <v>15</v>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Ypiranga Erechim</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Caxias</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>1</v>
+      </c>
+      <c r="K147" t="n">
+        <v>1</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>1</v>
+      </c>
+      <c r="N147" t="n">
+        <v>1</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R147" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S147" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U147" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V147" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W147" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X147" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BH147" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="BI147" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BJ147" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BK147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BL147" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM147" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BN147" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BO147" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BP147" t="n">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>7845481</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>45872.79166666666</v>
+      </c>
+      <c r="F148" t="n">
+        <v>15</v>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Retrô</t>
+        </is>
+      </c>
+      <c r="I148" t="n">
+        <v>1</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1</v>
+      </c>
+      <c r="L148" t="n">
+        <v>3</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="n">
+        <v>3</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>['42', '48', '51']</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R148" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S148" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="T148" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U148" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V148" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W148" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X148" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI148" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ148" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BK148" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL148" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BM148" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN148" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO148" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BP148" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP148"/>
+  <dimension ref="A1:BP151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.57</v>
@@ -1350,7 +1350,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.5</v>
@@ -4184,7 +4184,7 @@
         <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.86</v>
@@ -5489,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.86</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.38</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ28" t="n">
         <v>1.14</v>
@@ -7890,7 +7890,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AR34" t="n">
         <v>1.38</v>
@@ -8108,7 +8108,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR35" t="n">
         <v>1.33</v>
@@ -9198,7 +9198,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR40" t="n">
         <v>1.51</v>
@@ -10067,7 +10067,7 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.5</v>
@@ -11375,7 +11375,7 @@
         <v>2</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.86</v>
@@ -13122,7 +13122,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AR58" t="n">
         <v>1.16</v>
@@ -13555,10 +13555,10 @@
         <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR60" t="n">
         <v>2.4</v>
@@ -13776,7 +13776,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR61" t="n">
         <v>1.88</v>
@@ -15299,7 +15299,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ68" t="n">
         <v>0.88</v>
@@ -15735,7 +15735,7 @@
         <v>2</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.57</v>
@@ -16610,7 +16610,7 @@
         <v>3</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR74" t="n">
         <v>0.91</v>
@@ -16828,7 +16828,7 @@
         <v>2</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AR75" t="n">
         <v>1.47</v>
@@ -17043,7 +17043,7 @@
         <v>1.67</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.57</v>
@@ -17264,7 +17264,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR77" t="n">
         <v>1.27</v>
@@ -18569,7 +18569,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.57</v>
@@ -19441,7 +19441,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.38</v>
@@ -19880,7 +19880,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AR89" t="n">
         <v>1.74</v>
@@ -20752,7 +20752,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR93" t="n">
         <v>1.49</v>
@@ -21188,7 +21188,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR95" t="n">
         <v>1.7</v>
@@ -22929,7 +22929,7 @@
         <v>0.2</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.5</v>
@@ -23365,7 +23365,7 @@
         <v>1.4</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.5</v>
@@ -23804,7 +23804,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AR107" t="n">
         <v>1.66</v>
@@ -24237,7 +24237,7 @@
         <v>0.4</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ109" t="n">
         <v>0.88</v>
@@ -25766,7 +25766,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AR116" t="n">
         <v>1.38</v>
@@ -26420,7 +26420,7 @@
         <v>3</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR119" t="n">
         <v>1.37</v>
@@ -27071,7 +27071,7 @@
         <v>0.4</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.71</v>
@@ -27728,7 +27728,7 @@
         <v>2</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AR125" t="n">
         <v>1.67</v>
@@ -28161,7 +28161,7 @@
         <v>0.5</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ127" t="n">
         <v>0.38</v>
@@ -28597,7 +28597,7 @@
         <v>0.17</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.5</v>
@@ -30344,7 +30344,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR137" t="n">
         <v>1.77</v>
@@ -32818,6 +32818,660 @@
       </c>
       <c r="BP148" t="n">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="n">
+        <v>7845488</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>45873.66666666666</v>
+      </c>
+      <c r="F149" t="n">
+        <v>15</v>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Itabaiana</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R149" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S149" t="n">
+        <v>4</v>
+      </c>
+      <c r="T149" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U149" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="V149" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W149" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X149" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="BI149" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ149" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK149" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL149" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM149" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN149" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO149" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP149" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="n">
+        <v>7845483</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>45873.8125</v>
+      </c>
+      <c r="F150" t="n">
+        <v>15</v>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Anápolis</t>
+        </is>
+      </c>
+      <c r="I150" t="n">
+        <v>1</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>1</v>
+      </c>
+      <c r="L150" t="n">
+        <v>2</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="n">
+        <v>2</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>['45+3', '76']</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R150" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S150" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T150" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U150" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V150" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="W150" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X150" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB150" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE150" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF150" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BG150" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH150" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI150" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ150" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK150" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BL150" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM150" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN150" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO150" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BP150" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="n">
+        <v>7845484</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>45873.8125</v>
+      </c>
+      <c r="F151" t="n">
+        <v>15</v>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>1</v>
+      </c>
+      <c r="L151" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>['16']</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R151" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S151" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T151" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U151" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="V151" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W151" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X151" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BE151" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF151" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BG151" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH151" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI151" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ151" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BK151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL151" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BM151" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN151" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO151" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP151" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -32972,22 +32972,22 @@
         <v>2.74</v>
       </c>
       <c r="AU149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW149" t="n">
         <v>2</v>
       </c>
-      <c r="AV149" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW149" t="n">
+      <c r="AX149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ149" t="n">
         <v>4</v>
-      </c>
-      <c r="AX149" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY149" t="n">
-        <v>6</v>
-      </c>
-      <c r="AZ149" t="n">
-        <v>11</v>
       </c>
       <c r="BA149" t="n">
         <v>4</v>
@@ -33190,22 +33190,22 @@
         <v>3.33</v>
       </c>
       <c r="AU150" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW150" t="n">
         <v>9</v>
       </c>
-      <c r="AV150" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW150" t="n">
-        <v>10</v>
-      </c>
       <c r="AX150" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY150" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ150" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA150" t="n">
         <v>6</v>
@@ -33414,16 +33414,16 @@
         <v>1</v>
       </c>
       <c r="AW151" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ151" t="n">
         <v>9</v>
-      </c>
-      <c r="AX151" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY151" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ151" t="n">
-        <v>11</v>
       </c>
       <c r="BA151" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -32972,22 +32972,22 @@
         <v>2.74</v>
       </c>
       <c r="AU149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW149" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX149" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AY149" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AZ149" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="BA149" t="n">
         <v>4</v>
@@ -33190,22 +33190,22 @@
         <v>3.33</v>
       </c>
       <c r="AU150" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV150" t="n">
         <v>1</v>
       </c>
       <c r="AW150" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ150" t="n">
         <v>9</v>
-      </c>
-      <c r="AX150" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY150" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ150" t="n">
-        <v>7</v>
       </c>
       <c r="BA150" t="n">
         <v>6</v>
@@ -33414,16 +33414,16 @@
         <v>1</v>
       </c>
       <c r="AW151" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX151" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY151" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ151" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA151" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP151"/>
+  <dimension ref="A1:BP155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.57</v>
@@ -1132,7 +1132,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
@@ -2440,7 +2440,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2876,7 +2876,7 @@
         <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR23" t="n">
         <v>2.61</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.38</v>
@@ -6582,7 +6582,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR28" t="n">
         <v>0.87</v>
@@ -6797,10 +6797,10 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR29" t="n">
         <v>0.92</v>
@@ -7672,7 +7672,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR33" t="n">
         <v>2.49</v>
@@ -8977,7 +8977,7 @@
         <v>1</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.71</v>
@@ -9634,7 +9634,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR42" t="n">
         <v>1.28</v>
@@ -9849,7 +9849,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.57</v>
@@ -10070,7 +10070,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR44" t="n">
         <v>0.93</v>
@@ -10288,7 +10288,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR45" t="n">
         <v>1.49</v>
@@ -10503,7 +10503,7 @@
         <v>0.5</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.88</v>
@@ -11375,10 +11375,10 @@
         <v>2</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR50" t="n">
         <v>1.68</v>
@@ -13994,7 +13994,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR62" t="n">
         <v>1.8</v>
@@ -14212,7 +14212,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR63" t="n">
         <v>1.45</v>
@@ -14648,7 +14648,7 @@
         <v>2</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR65" t="n">
         <v>1.82</v>
@@ -14863,7 +14863,7 @@
         <v>0</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.5</v>
@@ -15299,7 +15299,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ68" t="n">
         <v>0.88</v>
@@ -15953,7 +15953,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.88</v>
@@ -17918,7 +17918,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR80" t="n">
         <v>1.35</v>
@@ -18354,7 +18354,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR82" t="n">
         <v>1.37</v>
@@ -18569,7 +18569,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.57</v>
@@ -19005,7 +19005,7 @@
         <v>0.75</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.5</v>
@@ -19662,7 +19662,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR88" t="n">
         <v>1.27</v>
@@ -19877,7 +19877,7 @@
         <v>0</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.13</v>
@@ -20531,7 +20531,7 @@
         <v>1.25</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.86</v>
@@ -20970,7 +20970,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR94" t="n">
         <v>2.55</v>
@@ -21406,7 +21406,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR96" t="n">
         <v>1.78</v>
@@ -21624,7 +21624,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR97" t="n">
         <v>1.76</v>
@@ -22929,7 +22929,7 @@
         <v>0.2</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.5</v>
@@ -23368,7 +23368,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR105" t="n">
         <v>2.27</v>
@@ -24673,7 +24673,7 @@
         <v>1.4</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.57</v>
@@ -24894,7 +24894,7 @@
         <v>2</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR112" t="n">
         <v>1.45</v>
@@ -25112,7 +25112,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR113" t="n">
         <v>1.87</v>
@@ -25330,7 +25330,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR114" t="n">
         <v>1.37</v>
@@ -25548,7 +25548,7 @@
         <v>2</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR115" t="n">
         <v>1.52</v>
@@ -25763,7 +25763,7 @@
         <v>2</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ116" t="n">
         <v>1.43</v>
@@ -25981,7 +25981,7 @@
         <v>1.4</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.14</v>
@@ -27071,7 +27071,7 @@
         <v>0.4</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.71</v>
@@ -29251,7 +29251,7 @@
         <v>1.33</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.57</v>
@@ -29472,7 +29472,7 @@
         <v>2</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AR133" t="n">
         <v>1.49</v>
@@ -29690,7 +29690,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AR134" t="n">
         <v>1.25</v>
@@ -30126,7 +30126,7 @@
         <v>3</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="AR136" t="n">
         <v>1.4</v>
@@ -30780,7 +30780,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="AR139" t="n">
         <v>1.73</v>
@@ -31213,7 +31213,7 @@
         <v>1.33</v>
       </c>
       <c r="AP141" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ141" t="n">
         <v>1.57</v>
@@ -33393,7 +33393,7 @@
         <v>1.67</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.43</v>
@@ -33471,6 +33471,878 @@
         <v>2.4</v>
       </c>
       <c r="BP151" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="n">
+        <v>7845500</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>45878.70833333334</v>
+      </c>
+      <c r="F152" t="n">
+        <v>16</v>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Botafogo PB</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="I152" t="n">
+        <v>2</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>2</v>
+      </c>
+      <c r="L152" t="n">
+        <v>2</v>
+      </c>
+      <c r="M152" t="n">
+        <v>1</v>
+      </c>
+      <c r="N152" t="n">
+        <v>3</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>['18', '38']</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R152" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S152" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T152" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U152" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V152" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="W152" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X152" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH152" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI152" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ152" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="BK152" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL152" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BM152" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN152" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO152" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP152" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="n">
+        <v>7845497</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>45878.70833333334</v>
+      </c>
+      <c r="F153" t="n">
+        <v>16</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Caxias</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="n">
+        <v>1</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R153" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S153" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="T153" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U153" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V153" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W153" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X153" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD153" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE153" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="BF153" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG153" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH153" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BI153" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BJ153" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BK153" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BL153" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM153" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BN153" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO153" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BP153" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="n">
+        <v>7845494</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>45878.8125</v>
+      </c>
+      <c r="F154" t="n">
+        <v>16</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+      <c r="I154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" t="n">
+        <v>1</v>
+      </c>
+      <c r="K154" t="n">
+        <v>2</v>
+      </c>
+      <c r="L154" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" t="n">
+        <v>2</v>
+      </c>
+      <c r="N154" t="n">
+        <v>3</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>['41', '52']</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="R154" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S154" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T154" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U154" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V154" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="W154" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X154" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG154" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH154" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI154" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ154" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK154" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL154" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="BM154" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BN154" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO154" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BP154" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="n">
+        <v>7845493</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>45878.8125</v>
+      </c>
+      <c r="F155" t="n">
+        <v>16</v>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Ypiranga Erechim</t>
+        </is>
+      </c>
+      <c r="I155" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" t="n">
+        <v>1</v>
+      </c>
+      <c r="K155" t="n">
+        <v>2</v>
+      </c>
+      <c r="L155" t="n">
+        <v>2</v>
+      </c>
+      <c r="M155" t="n">
+        <v>1</v>
+      </c>
+      <c r="N155" t="n">
+        <v>3</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>['29', '70']</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R155" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S155" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="T155" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U155" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V155" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="W155" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X155" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="BI155" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ155" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BK155" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL155" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM155" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN155" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO155" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BP155" t="n">
         <v>1.39</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP155"/>
+  <dimension ref="A1:BP159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ11" t="n">
         <v>1</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.14</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.43</v>
@@ -4402,7 +4402,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ22" t="n">
         <v>1</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ24" t="n">
         <v>0.88</v>
@@ -5928,7 +5928,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR25" t="n">
         <v>1.88</v>
@@ -6146,7 +6146,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR26" t="n">
         <v>1.64</v>
@@ -6364,7 +6364,7 @@
         <v>2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR27" t="n">
         <v>1</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.88</v>
@@ -8541,7 +8541,7 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ37" t="n">
         <v>0.5</v>
@@ -8762,7 +8762,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR38" t="n">
         <v>1.45</v>
@@ -9852,7 +9852,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR43" t="n">
         <v>1.92</v>
@@ -10285,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ45" t="n">
         <v>1</v>
@@ -11157,10 +11157,10 @@
         <v>0.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR49" t="n">
         <v>1.83</v>
@@ -12029,7 +12029,7 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.86</v>
@@ -12250,7 +12250,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR54" t="n">
         <v>1.22</v>
@@ -12468,7 +12468,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR55" t="n">
         <v>1.23</v>
@@ -13119,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.13</v>
@@ -14645,7 +14645,7 @@
         <v>1.67</v>
       </c>
       <c r="AP65" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.33</v>
@@ -15084,7 +15084,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR67" t="n">
         <v>1.18</v>
@@ -15517,7 +15517,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ69" t="n">
         <v>1</v>
@@ -15738,7 +15738,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR70" t="n">
         <v>1.26</v>
@@ -16174,7 +16174,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR72" t="n">
         <v>1.79</v>
@@ -16389,7 +16389,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.86</v>
@@ -16825,7 +16825,7 @@
         <v>0</v>
       </c>
       <c r="AP75" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.13</v>
@@ -17046,7 +17046,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR76" t="n">
         <v>2.3</v>
@@ -18572,7 +18572,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR83" t="n">
         <v>1.31</v>
@@ -18787,7 +18787,7 @@
         <v>0</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ84" t="n">
         <v>0.5</v>
@@ -19223,7 +19223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ86" t="n">
         <v>0.88</v>
@@ -19444,7 +19444,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR87" t="n">
         <v>1.06</v>
@@ -20749,7 +20749,7 @@
         <v>1.75</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.43</v>
@@ -21842,7 +21842,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR98" t="n">
         <v>1.36</v>
@@ -22275,10 +22275,10 @@
         <v>1.25</v>
       </c>
       <c r="AP100" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR100" t="n">
         <v>1.39</v>
@@ -23583,7 +23583,7 @@
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.86</v>
@@ -23801,7 +23801,7 @@
         <v>0</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ107" t="n">
         <v>0.13</v>
@@ -24458,7 +24458,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR110" t="n">
         <v>1.34</v>
@@ -24676,7 +24676,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR111" t="n">
         <v>1.23</v>
@@ -25545,7 +25545,7 @@
         <v>1.4</v>
       </c>
       <c r="AP115" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ115" t="n">
         <v>1</v>
@@ -26202,7 +26202,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR118" t="n">
         <v>1.77</v>
@@ -26638,7 +26638,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR120" t="n">
         <v>2.43</v>
@@ -26853,7 +26853,7 @@
         <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.86</v>
@@ -27725,7 +27725,7 @@
         <v>0</v>
       </c>
       <c r="AP125" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.13</v>
@@ -28164,7 +28164,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR127" t="n">
         <v>2.15</v>
@@ -28382,7 +28382,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR128" t="n">
         <v>1.26</v>
@@ -29033,7 +29033,7 @@
         <v>1</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AQ131" t="n">
         <v>0.86</v>
@@ -29254,7 +29254,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AR132" t="n">
         <v>1.58</v>
@@ -29469,7 +29469,7 @@
         <v>1.57</v>
       </c>
       <c r="AP133" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.33</v>
@@ -29687,7 +29687,7 @@
         <v>1.17</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AQ134" t="n">
         <v>1</v>
@@ -29905,7 +29905,7 @@
         <v>1</v>
       </c>
       <c r="AP135" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AQ135" t="n">
         <v>0.86</v>
@@ -31216,7 +31216,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AR141" t="n">
         <v>1.38</v>
@@ -32088,7 +32088,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AR145" t="n">
         <v>1.63</v>
@@ -33745,7 +33745,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>['52']</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -34344,6 +34344,878 @@
       </c>
       <c r="BP155" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="n">
+        <v>7845496</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>45879.45833333334</v>
+      </c>
+      <c r="F156" t="n">
+        <v>16</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>2</v>
+      </c>
+      <c r="N156" t="n">
+        <v>2</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>['64', '72']</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R156" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S156" t="n">
+        <v>4</v>
+      </c>
+      <c r="T156" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U156" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V156" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W156" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X156" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BG156" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH156" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="BI156" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ156" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK156" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BL156" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM156" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BN156" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO156" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BP156" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="n">
+        <v>7845495</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>45879.6875</v>
+      </c>
+      <c r="F157" t="n">
+        <v>16</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Anápolis</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>1</v>
+      </c>
+      <c r="J157" t="n">
+        <v>1</v>
+      </c>
+      <c r="K157" t="n">
+        <v>2</v>
+      </c>
+      <c r="L157" t="n">
+        <v>2</v>
+      </c>
+      <c r="M157" t="n">
+        <v>1</v>
+      </c>
+      <c r="N157" t="n">
+        <v>3</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>['13', '51']</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R157" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S157" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="T157" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U157" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V157" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W157" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X157" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH157" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BI157" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ157" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK157" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN157" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO157" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BP157" t="n">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="n">
+        <v>7845499</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>45879.6875</v>
+      </c>
+      <c r="F158" t="n">
+        <v>16</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Floresta</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Tombense</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>1</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>1</v>
+      </c>
+      <c r="L158" t="n">
+        <v>1</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="n">
+        <v>1</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="R158" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S158" t="n">
+        <v>5</v>
+      </c>
+      <c r="T158" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U158" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V158" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="W158" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X158" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY158" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB158" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC158" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE158" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF158" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BG158" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH158" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BI158" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BJ158" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BK158" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BL158" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM158" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BN158" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BO158" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BP158" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="n">
+        <v>7845491</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>45879.79166666666</v>
+      </c>
+      <c r="F159" t="n">
+        <v>16</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Retrô</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>1</v>
+      </c>
+      <c r="N159" t="n">
+        <v>1</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R159" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="S159" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T159" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U159" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V159" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="W159" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X159" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BJ159" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BK159" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BL159" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BM159" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BN159" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO159" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BP159" t="n">
+        <v>1.27</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP159"/>
+  <dimension ref="A1:BP161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.63</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ7" t="n">
         <v>1.75</v>
@@ -5056,7 +5056,7 @@
         <v>0.71</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.75</v>
@@ -8326,7 +8326,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR36" t="n">
         <v>1.21</v>
@@ -9413,7 +9413,7 @@
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.5</v>
@@ -11593,7 +11593,7 @@
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.88</v>
@@ -11814,7 +11814,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR52" t="n">
         <v>1.58</v>
@@ -13337,7 +13337,7 @@
         <v>3</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.14</v>
@@ -14427,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.5</v>
@@ -17697,7 +17697,7 @@
         <v>0.67</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.71</v>
@@ -18136,7 +18136,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR81" t="n">
         <v>1.57</v>
@@ -20534,7 +20534,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR92" t="n">
         <v>1.66</v>
@@ -21403,7 +21403,7 @@
         <v>0.2</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.78</v>
@@ -22493,7 +22493,7 @@
         <v>0.5</v>
       </c>
       <c r="AP101" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ101" t="n">
         <v>0.71</v>
@@ -24891,7 +24891,7 @@
         <v>0.33</v>
       </c>
       <c r="AP112" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.78</v>
@@ -26199,7 +26199,7 @@
         <v>1.4</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.75</v>
@@ -26856,7 +26856,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR121" t="n">
         <v>1.3</v>
@@ -29908,7 +29908,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AR135" t="n">
         <v>1.7</v>
@@ -30341,7 +30341,7 @@
         <v>0.83</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ137" t="n">
         <v>1</v>
@@ -30559,7 +30559,7 @@
         <v>1.33</v>
       </c>
       <c r="AP138" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.14</v>
@@ -34404,7 +34404,7 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>['64', '72']</t>
+          <t>['63', '71']</t>
         </is>
       </c>
       <c r="Q156" t="n">
@@ -34617,12 +34617,12 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>['13', '51']</t>
+          <t>['12', '51']</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>['10']</t>
+          <t>['9']</t>
         </is>
       </c>
       <c r="Q157" t="n">
@@ -34835,7 +34835,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>['37']</t>
+          <t>['36']</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -35155,19 +35155,19 @@
         <v>3</v>
       </c>
       <c r="AV159" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW159" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX159" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AY159" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ159" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="BA159" t="n">
         <v>4</v>
@@ -35216,6 +35216,442 @@
       </c>
       <c r="BP159" t="n">
         <v>1.27</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>7845492</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>45880.8125</v>
+      </c>
+      <c r="F160" t="n">
+        <v>16</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Itabaiana</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>CSA</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>1</v>
+      </c>
+      <c r="L160" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="n">
+        <v>1</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>['8']</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R160" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="S160" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="T160" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="U160" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V160" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W160" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X160" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY160" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BG160" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH160" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="BI160" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN160" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO160" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BP160" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>7845498</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>45880.8125</v>
+      </c>
+      <c r="F161" t="n">
+        <v>16</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Maringá</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K161" t="n">
+        <v>2</v>
+      </c>
+      <c r="L161" t="n">
+        <v>1</v>
+      </c>
+      <c r="M161" t="n">
+        <v>1</v>
+      </c>
+      <c r="N161" t="n">
+        <v>2</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>['45+5']</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R161" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S161" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T161" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U161" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V161" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W161" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X161" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN161" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO161" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BP161" t="n">
+        <v>1.59</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -34019,22 +34019,22 @@
         <v>2.42</v>
       </c>
       <c r="AU160">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV160">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW160">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX160">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY160">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ160">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BA160">
         <v>4</v>
@@ -34225,22 +34225,22 @@
         <v>3.53</v>
       </c>
       <c r="AU161">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AV161">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW161">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX161">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY161">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ161">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA161">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP161"/>
+  <dimension ref="A1:BP165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4" t="n">
         <v>1</v>
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3748,7 +3748,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>1.75</v>
@@ -4620,7 +4620,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5053,7 +5053,7 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.75</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.75</v>
@@ -7236,7 +7236,7 @@
         <v>3</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR31" t="n">
         <v>0.73</v>
@@ -7451,10 +7451,10 @@
         <v>3</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR32" t="n">
         <v>1.66</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.78</v>
@@ -7890,7 +7890,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR34" t="n">
         <v>1.38</v>
@@ -8105,7 +8105,7 @@
         <v>3</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ35" t="n">
         <v>1</v>
@@ -8544,7 +8544,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR37" t="n">
         <v>1.25</v>
@@ -10724,7 +10724,7 @@
         <v>3</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR47" t="n">
         <v>0.91</v>
@@ -10939,7 +10939,7 @@
         <v>2</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ48" t="n">
         <v>1</v>
@@ -12032,7 +12032,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR53" t="n">
         <v>1.25</v>
@@ -12465,7 +12465,7 @@
         <v>1</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.38</v>
@@ -12901,7 +12901,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.71</v>
@@ -13122,7 +13122,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR58" t="n">
         <v>1.16</v>
@@ -13340,7 +13340,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR59" t="n">
         <v>1.72</v>
@@ -13773,7 +13773,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ61" t="n">
         <v>1</v>
@@ -13991,7 +13991,7 @@
         <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.78</v>
@@ -14866,7 +14866,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR66" t="n">
         <v>1.21</v>
@@ -16171,7 +16171,7 @@
         <v>1</v>
       </c>
       <c r="AP72" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.75</v>
@@ -16392,7 +16392,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR73" t="n">
         <v>1.45</v>
@@ -16828,7 +16828,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR75" t="n">
         <v>1.47</v>
@@ -17479,10 +17479,10 @@
         <v>2</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR78" t="n">
         <v>2.33</v>
@@ -17915,7 +17915,7 @@
         <v>0.33</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ80" t="n">
         <v>1</v>
@@ -18351,7 +18351,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.33</v>
@@ -18790,7 +18790,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR84" t="n">
         <v>1.58</v>
@@ -19880,7 +19880,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR89" t="n">
         <v>1.74</v>
@@ -20095,7 +20095,7 @@
         <v>1.25</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.88</v>
@@ -20967,7 +20967,7 @@
         <v>2.5</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.63</v>
@@ -21621,7 +21621,7 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ97" t="n">
         <v>1</v>
@@ -22060,7 +22060,7 @@
         <v>3</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR99" t="n">
         <v>1.23</v>
@@ -22932,7 +22932,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR103" t="n">
         <v>1.42</v>
@@ -23147,7 +23147,7 @@
         <v>1.2</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.5</v>
@@ -23586,7 +23586,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR106" t="n">
         <v>1.67</v>
@@ -23804,7 +23804,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR107" t="n">
         <v>1.66</v>
@@ -24455,7 +24455,7 @@
         <v>0.6</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.33</v>
@@ -25984,7 +25984,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR117" t="n">
         <v>1.6</v>
@@ -26635,7 +26635,7 @@
         <v>1</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.38</v>
@@ -27289,7 +27289,7 @@
         <v>1</v>
       </c>
       <c r="AP123" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ123" t="n">
         <v>1</v>
@@ -27507,7 +27507,7 @@
         <v>1</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.88</v>
@@ -27728,7 +27728,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR125" t="n">
         <v>1.67</v>
@@ -27943,7 +27943,7 @@
         <v>0.83</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ126" t="n">
         <v>0.88</v>
@@ -28600,7 +28600,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR129" t="n">
         <v>1.23</v>
@@ -29036,7 +29036,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR131" t="n">
         <v>1.53</v>
@@ -30562,7 +30562,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AR138" t="n">
         <v>1.43</v>
@@ -31431,7 +31431,7 @@
         <v>0.83</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.71</v>
@@ -31649,10 +31649,10 @@
         <v>0.83</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="AQ143" t="n">
-        <v>0.86</v>
+        <v>1.13</v>
       </c>
       <c r="AR143" t="n">
         <v>1.44</v>
@@ -31867,7 +31867,7 @@
         <v>0.86</v>
       </c>
       <c r="AP144" t="n">
-        <v>0.71</v>
+        <v>0.63</v>
       </c>
       <c r="AQ144" t="n">
         <v>0.88</v>
@@ -32303,7 +32303,7 @@
         <v>0.86</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.88</v>
@@ -32742,7 +32742,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ148" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AR148" t="n">
         <v>1.55</v>
@@ -32960,7 +32960,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
       <c r="AR149" t="n">
         <v>1.35</v>
@@ -35652,6 +35652,878 @@
       </c>
       <c r="BP161" t="n">
         <v>1.59</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>7845502</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>45885.70833333334</v>
+      </c>
+      <c r="F162" t="n">
+        <v>17</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Itabaiana</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>1</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="n">
+        <v>1</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R162" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S162" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="T162" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U162" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V162" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W162" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X162" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BF162" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG162" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH162" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BI162" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ162" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BK162" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BM162" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BN162" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO162" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP162" t="n">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="n">
+        <v>7845506</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>45885.70833333334</v>
+      </c>
+      <c r="F163" t="n">
+        <v>17</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Maringá</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Retrô</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>1</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>1</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R163" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S163" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T163" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U163" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V163" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W163" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X163" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI163" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BJ163" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="BK163" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BM163" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BN163" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO163" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BP163" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="n">
+        <v>7845509</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>45885.8125</v>
+      </c>
+      <c r="F164" t="n">
+        <v>17</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>CSA</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>2</v>
+      </c>
+      <c r="M164" t="n">
+        <v>2</v>
+      </c>
+      <c r="N164" t="n">
+        <v>4</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>['48', '85']</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>['59', '77']</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R164" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S164" t="n">
+        <v>5</v>
+      </c>
+      <c r="T164" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U164" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V164" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W164" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X164" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BN164" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BO164" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BP164" t="n">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="n">
+        <v>7845510</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>45885.8125</v>
+      </c>
+      <c r="F165" t="n">
+        <v>17</v>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="I165" t="n">
+        <v>2</v>
+      </c>
+      <c r="J165" t="n">
+        <v>2</v>
+      </c>
+      <c r="K165" t="n">
+        <v>4</v>
+      </c>
+      <c r="L165" t="n">
+        <v>3</v>
+      </c>
+      <c r="M165" t="n">
+        <v>4</v>
+      </c>
+      <c r="N165" t="n">
+        <v>7</v>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>['7', '37', '58']</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>['5', '45', '62', '73']</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R165" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S165" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="T165" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U165" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V165" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W165" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X165" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y165" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ165" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA165" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB165" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC165" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF165" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG165" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH165" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BI165" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ165" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BK165" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL165" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BM165" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN165" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO165" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BP165" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -8574,13 +8574,13 @@
         <v>-1</v>
       </c>
       <c r="BA37" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB37" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC37" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="BD37" t="n">
         <v>2.12</v>
@@ -10754,13 +10754,13 @@
         <v>-1</v>
       </c>
       <c r="BA47" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BB47" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="BD47" t="n">
         <v>1.54</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP165"/>
+  <dimension ref="A1:BP169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.33</v>
@@ -2658,7 +2658,7 @@
         <v>3</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.71</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.5</v>
@@ -4184,7 +4184,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.13</v>
@@ -4838,7 +4838,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.63</v>
@@ -5710,7 +5710,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR24" t="n">
         <v>0.96</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ28" t="n">
         <v>1</v>
@@ -7018,7 +7018,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR30" t="n">
         <v>1.85</v>
@@ -8108,7 +8108,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR35" t="n">
         <v>1.33</v>
@@ -8759,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.38</v>
@@ -9195,10 +9195,10 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR40" t="n">
         <v>1.51</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.78</v>
@@ -10067,7 +10067,7 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.33</v>
@@ -10506,7 +10506,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR46" t="n">
         <v>1.03</v>
@@ -11596,7 +11596,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR51" t="n">
         <v>1.33</v>
@@ -12683,7 +12683,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.5</v>
@@ -13555,10 +13555,10 @@
         <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR60" t="n">
         <v>2.4</v>
@@ -13776,7 +13776,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR61" t="n">
         <v>1.88</v>
@@ -14209,7 +14209,7 @@
         <v>2.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.63</v>
@@ -15302,7 +15302,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR68" t="n">
         <v>1.47</v>
@@ -15735,7 +15735,7 @@
         <v>2</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.75</v>
@@ -15956,7 +15956,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR71" t="n">
         <v>1.82</v>
@@ -16610,7 +16610,7 @@
         <v>3</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR74" t="n">
         <v>0.91</v>
@@ -17043,7 +17043,7 @@
         <v>1.67</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.38</v>
@@ -17264,7 +17264,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR77" t="n">
         <v>1.27</v>
@@ -18133,7 +18133,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.75</v>
@@ -19226,7 +19226,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR86" t="n">
         <v>1.74</v>
@@ -19441,7 +19441,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.33</v>
@@ -20098,7 +20098,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR90" t="n">
         <v>1.76</v>
@@ -20313,7 +20313,7 @@
         <v>1.25</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ91" t="n">
         <v>1</v>
@@ -20752,7 +20752,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR93" t="n">
         <v>1.49</v>
@@ -21185,10 +21185,10 @@
         <v>1.25</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR95" t="n">
         <v>1.7</v>
@@ -22711,10 +22711,10 @@
         <v>1</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR102" t="n">
         <v>1.44</v>
@@ -23365,7 +23365,7 @@
         <v>1.4</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.33</v>
@@ -24237,10 +24237,10 @@
         <v>0.4</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR109" t="n">
         <v>1.16</v>
@@ -25109,7 +25109,7 @@
         <v>2.6</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.63</v>
@@ -25766,7 +25766,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR116" t="n">
         <v>1.38</v>
@@ -26420,7 +26420,7 @@
         <v>3</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR119" t="n">
         <v>1.37</v>
@@ -27510,7 +27510,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR124" t="n">
         <v>1.39</v>
@@ -27946,7 +27946,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR126" t="n">
         <v>1.79</v>
@@ -28161,7 +28161,7 @@
         <v>0.5</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ127" t="n">
         <v>0.33</v>
@@ -28597,7 +28597,7 @@
         <v>0.17</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.44</v>
@@ -28815,7 +28815,7 @@
         <v>1.5</v>
       </c>
       <c r="AP130" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ130" t="n">
         <v>1.5</v>
@@ -30344,7 +30344,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR137" t="n">
         <v>1.77</v>
@@ -30777,7 +30777,7 @@
         <v>0.43</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ139" t="n">
         <v>0.78</v>
@@ -31870,7 +31870,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ144" t="n">
-        <v>0.88</v>
+        <v>1.11</v>
       </c>
       <c r="AR144" t="n">
         <v>1.83</v>
@@ -32085,7 +32085,7 @@
         <v>0.43</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.33</v>
@@ -32306,7 +32306,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="AR146" t="n">
         <v>2.38</v>
@@ -32739,7 +32739,7 @@
         <v>0.57</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AQ148" t="n">
         <v>0.44</v>
@@ -32957,7 +32957,7 @@
         <v>0</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.11</v>
@@ -33175,10 +33175,10 @@
         <v>1.14</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR150" t="n">
         <v>2.17</v>
@@ -33396,7 +33396,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="AR151" t="n">
         <v>1.43</v>
@@ -36524,6 +36524,878 @@
       </c>
       <c r="BP165" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="n">
+        <v>7845505</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>45886.6875</v>
+      </c>
+      <c r="F166" t="n">
+        <v>17</v>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>1</v>
+      </c>
+      <c r="K166" t="n">
+        <v>1</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>3</v>
+      </c>
+      <c r="N166" t="n">
+        <v>3</v>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>['19', '90+5', '90+1']</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R166" t="n">
+        <v>2</v>
+      </c>
+      <c r="S166" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T166" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U166" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V166" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="W166" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X166" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ166" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA166" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB166" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC166" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD166" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BE166" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF166" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="BG166" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH166" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="BI166" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ166" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK166" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL166" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM166" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BN166" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO166" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BP166" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="n">
+        <v>7845508</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>45886.6875</v>
+      </c>
+      <c r="F167" t="n">
+        <v>17</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>1</v>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="n">
+        <v>2</v>
+      </c>
+      <c r="N167" t="n">
+        <v>3</v>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>['90+4', '90+7']</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>3</v>
+      </c>
+      <c r="R167" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S167" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T167" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U167" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V167" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="W167" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X167" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF167" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AG167" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH167" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI167" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ167" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK167" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL167" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM167" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN167" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP167" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ167" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR167" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ167" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA167" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB167" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC167" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD167" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BE167" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF167" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BG167" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH167" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI167" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ167" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK167" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL167" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BM167" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BN167" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO167" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP167" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="n">
+        <v>7845503</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>45886.79166666666</v>
+      </c>
+      <c r="F168" t="n">
+        <v>17</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Floresta</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="n">
+        <v>1</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>['84']</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R168" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S168" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T168" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U168" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V168" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W168" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X168" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ168" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA168" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB168" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC168" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD168" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BE168" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF168" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG168" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BH168" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BI168" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ168" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BK168" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL168" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BM168" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN168" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO168" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BP168" t="n">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="n">
+        <v>7845501</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>45886.79166666666</v>
+      </c>
+      <c r="F169" t="n">
+        <v>17</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Anápolis</t>
+        </is>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="n">
+        <v>1</v>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R169" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S169" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T169" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U169" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="V169" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="W169" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X169" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="AE169" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF169" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG169" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AH169" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI169" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AJ169" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AK169" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AL169" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AM169" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AN169" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP169" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ169" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AR169" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ169" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA169" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB169" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC169" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD169" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BE169" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BF169" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="BG169" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH169" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI169" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ169" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK169" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BL169" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BM169" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BN169" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO169" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BP169" t="n">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -36802,7 +36802,7 @@
       </c>
       <c r="P167" t="inlineStr">
         <is>
-          <t>['90+4', '90+7']</t>
+          <t>['90+3', '90+6']</t>
         </is>
       </c>
       <c r="Q167" t="n">
@@ -36896,22 +36896,22 @@
         <v>2.69</v>
       </c>
       <c r="AU167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV167" t="n">
         <v>7</v>
       </c>
       <c r="AW167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY167" t="n">
         <v>4</v>
       </c>
-      <c r="AX167" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY167" t="n">
-        <v>5</v>
-      </c>
       <c r="AZ167" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA167" t="n">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP169"/>
+  <dimension ref="A1:BP171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3312,7 +3312,7 @@
         <v>2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.11</v>
@@ -3966,7 +3966,7 @@
         <v>2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ20" t="n">
         <v>1.11</v>
@@ -7887,7 +7887,7 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.11</v>
@@ -8323,7 +8323,7 @@
         <v>1</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.75</v>
@@ -8980,7 +8980,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR39" t="n">
         <v>1.37</v>
@@ -9416,7 +9416,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR41" t="n">
         <v>1.73</v>
@@ -11811,7 +11811,7 @@
         <v>0.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ52" t="n">
         <v>0.75</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.75</v>
@@ -12686,7 +12686,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR56" t="n">
         <v>1.33</v>
@@ -12904,7 +12904,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR57" t="n">
         <v>2.71</v>
@@ -14430,7 +14430,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR64" t="n">
         <v>1.23</v>
@@ -15081,7 +15081,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.33</v>
@@ -17261,7 +17261,7 @@
         <v>1.33</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.89</v>
@@ -17700,7 +17700,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR79" t="n">
         <v>1.74</v>
@@ -19008,7 +19008,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR85" t="n">
         <v>1.09</v>
@@ -19659,7 +19659,7 @@
         <v>0.25</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ88" t="n">
         <v>0.78</v>
@@ -21839,7 +21839,7 @@
         <v>1</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.75</v>
@@ -22496,7 +22496,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR101" t="n">
         <v>1.51</v>
@@ -23150,7 +23150,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR104" t="n">
         <v>1.64</v>
@@ -24019,7 +24019,7 @@
         <v>1</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ108" t="n">
         <v>1</v>
@@ -25327,7 +25327,7 @@
         <v>1.33</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.33</v>
@@ -27074,7 +27074,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR122" t="n">
         <v>1.47</v>
@@ -28379,7 +28379,7 @@
         <v>1.33</v>
       </c>
       <c r="AP128" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ128" t="n">
         <v>1.75</v>
@@ -28818,7 +28818,7 @@
         <v>2</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR130" t="n">
         <v>1.48</v>
@@ -30995,7 +30995,7 @@
         <v>1</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ140" t="n">
         <v>1</v>
@@ -31434,7 +31434,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="AR142" t="n">
         <v>1.87</v>
@@ -32521,10 +32521,10 @@
         <v>1.29</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AR147" t="n">
         <v>1.19</v>
@@ -37120,16 +37120,16 @@
         <v>0</v>
       </c>
       <c r="AW168" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AX168" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AY168" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ168" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BA168" t="n">
         <v>5</v>
@@ -37332,22 +37332,22 @@
         <v>2.7</v>
       </c>
       <c r="AU169" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV169" t="n">
         <v>0</v>
       </c>
       <c r="AW169" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AX169" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AY169" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AZ169" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BA169" t="n">
         <v>6</v>
@@ -37396,6 +37396,442 @@
       </c>
       <c r="BP169" t="n">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="n">
+        <v>7845504</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>45887.8125</v>
+      </c>
+      <c r="F170" t="n">
+        <v>17</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Tombense</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Caxias</t>
+        </is>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R170" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S170" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="T170" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U170" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="V170" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W170" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X170" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ170" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA170" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB170" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC170" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD170" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BE170" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="BF170" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BG170" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH170" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI170" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ170" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BK170" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL170" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM170" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN170" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO170" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BP170" t="n">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="n">
+        <v>7845507</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>45887.8125</v>
+      </c>
+      <c r="F171" t="n">
+        <v>17</v>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Ypiranga Erechim</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Botafogo PB</t>
+        </is>
+      </c>
+      <c r="I171" t="n">
+        <v>2</v>
+      </c>
+      <c r="J171" t="n">
+        <v>2</v>
+      </c>
+      <c r="K171" t="n">
+        <v>4</v>
+      </c>
+      <c r="L171" t="n">
+        <v>2</v>
+      </c>
+      <c r="M171" t="n">
+        <v>2</v>
+      </c>
+      <c r="N171" t="n">
+        <v>4</v>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>['10', '32']</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>['5', '44']</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R171" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S171" t="n">
+        <v>4</v>
+      </c>
+      <c r="T171" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U171" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V171" t="n">
+        <v>4</v>
+      </c>
+      <c r="W171" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X171" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y171" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB171" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC171" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD171" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BE171" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BF171" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BG171" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH171" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI171" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ171" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK171" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BL171" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM171" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN171" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BO171" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BP171" t="n">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -36896,22 +36896,22 @@
         <v>2.69</v>
       </c>
       <c r="AU167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV167" t="n">
         <v>7</v>
       </c>
       <c r="AW167" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AX167" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY167" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ167" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA167" t="n">
         <v>6</v>
@@ -37120,16 +37120,16 @@
         <v>0</v>
       </c>
       <c r="AW168" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX168" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AY168" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AZ168" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BA168" t="n">
         <v>5</v>
@@ -37332,22 +37332,22 @@
         <v>2.7</v>
       </c>
       <c r="AU169" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV169" t="n">
         <v>0</v>
       </c>
       <c r="AW169" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AX169" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AY169" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AZ169" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BA169" t="n">
         <v>6</v>
@@ -37768,7 +37768,7 @@
         <v>2.35</v>
       </c>
       <c r="AU171" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV171" t="n">
         <v>5</v>
@@ -37780,7 +37780,7 @@
         <v>6</v>
       </c>
       <c r="AY171" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AZ171" t="n">
         <v>11</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -37669,7 +37669,7 @@
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>['10', '32']</t>
+          <t>['10', '31']</t>
         </is>
       </c>
       <c r="P171" t="inlineStr">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP171"/>
+  <dimension ref="A1:BP173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,10 +911,10 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.78</v>
@@ -2876,7 +2876,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR11" t="n">
         <v>0</v>
@@ -6143,7 +6143,7 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.33</v>
@@ -6582,7 +6582,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR28" t="n">
         <v>0.87</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.13</v>
@@ -8762,7 +8762,7 @@
         <v>2</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR38" t="n">
         <v>1.45</v>
@@ -10288,7 +10288,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR45" t="n">
         <v>1.49</v>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.44</v>
@@ -11375,7 +11375,7 @@
         <v>2</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ50" t="n">
         <v>1.63</v>
@@ -12468,7 +12468,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR55" t="n">
         <v>1.23</v>
@@ -15299,7 +15299,7 @@
         <v>1.33</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ68" t="n">
         <v>0.78</v>
@@ -16607,7 +16607,7 @@
         <v>2.33</v>
       </c>
       <c r="AP74" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.63</v>
@@ -17046,7 +17046,7 @@
         <v>2</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR76" t="n">
         <v>2.3</v>
@@ -17918,7 +17918,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR80" t="n">
         <v>1.35</v>
@@ -18569,7 +18569,7 @@
         <v>1.5</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ83" t="n">
         <v>1.75</v>
@@ -21624,7 +21624,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ97" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR97" t="n">
         <v>1.76</v>
@@ -22057,7 +22057,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ99" t="n">
         <v>1.13</v>
@@ -22278,7 +22278,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR100" t="n">
         <v>1.39</v>
@@ -22929,7 +22929,7 @@
         <v>0.2</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.44</v>
@@ -25548,7 +25548,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR115" t="n">
         <v>1.52</v>
@@ -26417,7 +26417,7 @@
         <v>1</v>
       </c>
       <c r="AP119" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ119" t="n">
         <v>0.89</v>
@@ -26638,7 +26638,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR120" t="n">
         <v>2.43</v>
@@ -27071,7 +27071,7 @@
         <v>0.4</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ122" t="n">
         <v>0.75</v>
@@ -29690,7 +29690,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR134" t="n">
         <v>1.25</v>
@@ -30123,7 +30123,7 @@
         <v>2.17</v>
       </c>
       <c r="AP136" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ136" t="n">
         <v>1.63</v>
@@ -31216,7 +31216,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR141" t="n">
         <v>1.38</v>
@@ -33393,7 +33393,7 @@
         <v>1.67</v>
       </c>
       <c r="AP151" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ151" t="n">
         <v>1.63</v>
@@ -33829,7 +33829,7 @@
         <v>1.5</v>
       </c>
       <c r="AP153" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.33</v>
@@ -34047,7 +34047,7 @@
         <v>0.5</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.78</v>
@@ -34268,7 +34268,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AR155" t="n">
         <v>1.57</v>
@@ -34704,7 +34704,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AR157" t="n">
         <v>1.53</v>
@@ -37832,6 +37832,442 @@
       </c>
       <c r="BP171" t="n">
         <v>1.58</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="n">
+        <v>7845517</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>45892.70833333334</v>
+      </c>
+      <c r="F172" t="n">
+        <v>18</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Caxias</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>1</v>
+      </c>
+      <c r="K172" t="n">
+        <v>1</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
+        <v>1</v>
+      </c>
+      <c r="N172" t="n">
+        <v>1</v>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>['30']</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R172" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S172" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T172" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U172" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V172" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W172" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X172" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ172" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA172" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB172" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC172" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD172" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BE172" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF172" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BG172" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH172" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BI172" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BJ172" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BK172" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL172" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BM172" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN172" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO172" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP172" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="n">
+        <v>7845514</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>45892.70833333334</v>
+      </c>
+      <c r="F173" t="n">
+        <v>18</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Ypiranga Erechim</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>1</v>
+      </c>
+      <c r="K173" t="n">
+        <v>1</v>
+      </c>
+      <c r="L173" t="n">
+        <v>2</v>
+      </c>
+      <c r="M173" t="n">
+        <v>1</v>
+      </c>
+      <c r="N173" t="n">
+        <v>3</v>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>['48', '64']</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>['20']</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R173" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S173" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T173" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U173" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V173" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W173" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X173" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX173" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY173" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ173" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA173" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB173" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC173" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD173" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE173" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF173" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BG173" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH173" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI173" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ173" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BK173" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BL173" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BM173" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BN173" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO173" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BP173" t="n">
+        <v>1.51</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP173"/>
+  <dimension ref="A1:BP174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ3" t="n">
         <v>1.63</v>
@@ -2658,7 +2658,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -7018,7 +7018,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR30" t="n">
         <v>1.85</v>
@@ -9413,7 +9413,7 @@
         <v>0</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.44</v>
@@ -10506,7 +10506,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR46" t="n">
         <v>1.03</v>
@@ -13337,7 +13337,7 @@
         <v>3</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.13</v>
@@ -15302,7 +15302,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR68" t="n">
         <v>1.47</v>
@@ -17697,7 +17697,7 @@
         <v>0.67</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.75</v>
@@ -20098,7 +20098,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR90" t="n">
         <v>1.76</v>
@@ -21403,7 +21403,7 @@
         <v>0.2</v>
       </c>
       <c r="AP96" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ96" t="n">
         <v>0.78</v>
@@ -22714,7 +22714,7 @@
         <v>2</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR102" t="n">
         <v>1.44</v>
@@ -26199,7 +26199,7 @@
         <v>1.4</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.75</v>
@@ -27510,7 +27510,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR124" t="n">
         <v>1.39</v>
@@ -30341,7 +30341,7 @@
         <v>0.83</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ137" t="n">
         <v>0.89</v>
@@ -32306,7 +32306,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ146" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR146" t="n">
         <v>2.38</v>
@@ -35573,7 +35573,7 @@
         <v>1</v>
       </c>
       <c r="AP161" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AQ161" t="n">
         <v>1</v>
@@ -37102,7 +37102,7 @@
         <v>2</v>
       </c>
       <c r="AQ168" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR168" t="n">
         <v>2.18</v>
@@ -38268,6 +38268,224 @@
       </c>
       <c r="BP173" t="n">
         <v>1.51</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="n">
+        <v>7845518</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>45892.8125</v>
+      </c>
+      <c r="F174" t="n">
+        <v>18</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Floresta</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>1</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>1</v>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" t="n">
+        <v>1</v>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>['23']</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="R174" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S174" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T174" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U174" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V174" t="n">
+        <v>4</v>
+      </c>
+      <c r="W174" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X174" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AF174" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG174" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AH174" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI174" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AJ174" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AK174" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL174" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM174" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN174" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP174" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AQ174" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR174" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AU174" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY174" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ174" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA174" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB174" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC174" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD174" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BE174" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF174" t="n">
+        <v>3</v>
+      </c>
+      <c r="BG174" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH174" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BI174" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ174" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BK174" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BL174" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BM174" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN174" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO174" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BP174" t="n">
+        <v>1.55</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -1244,26 +1244,26 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.89</v>
+        <v>0.67</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2770,31 +2770,31 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>['-1', '-1', '-1']</t>
+          <t>['7', '38', '72']</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['88']</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -2888,22 +2888,22 @@
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AX11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AY11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="BA11" t="n">
         <v>5</v>
@@ -5277,13 +5277,13 @@
         <v>1</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="AS22" t="n">
         <v>1.75</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.44</v>
+        <v>3.12</v>
       </c>
       <c r="AU22" t="n">
         <v>5</v>
@@ -5919,13 +5919,13 @@
         <v>1.82</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.75</v>
@@ -6588,10 +6588,10 @@
         <v>0.87</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.93</v>
+        <v>0.43</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
@@ -8102,13 +8102,13 @@
         <v>3</v>
       </c>
       <c r="AO35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AP35" t="n">
         <v>1.89</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.89</v>
+        <v>0.67</v>
       </c>
       <c r="AR35" t="n">
         <v>1.33</v>
@@ -10294,10 +10294,10 @@
         <v>1.49</v>
       </c>
       <c r="AS45" t="n">
-        <v>0.73</v>
+        <v>0.48</v>
       </c>
       <c r="AT45" t="n">
-        <v>2.22</v>
+        <v>1.97</v>
       </c>
       <c r="AU45" t="n">
         <v>1</v>
@@ -10933,13 +10933,13 @@
         <v>1.5</v>
       </c>
       <c r="AN48" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO48" t="n">
         <v>2</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AQ48" t="n">
         <v>1</v>
@@ -11163,13 +11163,13 @@
         <v>0.33</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AS49" t="n">
         <v>1.19</v>
       </c>
       <c r="AT49" t="n">
-        <v>3.02</v>
+        <v>2.86</v>
       </c>
       <c r="AU49" t="n">
         <v>5</v>
@@ -11826,22 +11826,22 @@
         <v>2.67</v>
       </c>
       <c r="AU52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV52" t="n">
         <v>2</v>
       </c>
       <c r="AW52" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX52" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AY52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AZ52" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BA52" t="n">
         <v>3</v>
@@ -12044,10 +12044,10 @@
         <v>3</v>
       </c>
       <c r="AU53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW53" t="n">
         <v>7</v>
@@ -12056,10 +12056,10 @@
         <v>6</v>
       </c>
       <c r="AY53" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ53" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA53" t="n">
         <v>4</v>
@@ -12265,19 +12265,19 @@
         <v>1</v>
       </c>
       <c r="AV54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW54" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY54" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ54" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ54" t="n">
-        <v>8</v>
       </c>
       <c r="BA54" t="n">
         <v>3</v>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>['45+2', '54', '78', '82']</t>
+          <t>['45+2', '54', '77', '82']</t>
         </is>
       </c>
       <c r="Q55" t="n">
@@ -12480,22 +12480,22 @@
         <v>3.07</v>
       </c>
       <c r="AU55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV55" t="n">
         <v>5</v>
       </c>
       <c r="AW55" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX55" t="n">
         <v>6</v>
       </c>
-      <c r="AX55" t="n">
-        <v>5</v>
-      </c>
       <c r="AY55" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA55" t="n">
         <v>8</v>
@@ -12701,19 +12701,19 @@
         <v>5</v>
       </c>
       <c r="AV56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW56" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AX56" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AY56" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AZ56" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BA56" t="n">
         <v>5</v>
@@ -12922,16 +12922,16 @@
         <v>3</v>
       </c>
       <c r="AW57" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AX57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY57" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AZ57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA57" t="n">
         <v>9</v>
@@ -13143,13 +13143,13 @@
         <v>14</v>
       </c>
       <c r="AX58" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AY58" t="n">
         <v>17</v>
       </c>
       <c r="AZ58" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA58" t="n">
         <v>5</v>
@@ -13358,16 +13358,16 @@
         <v>0</v>
       </c>
       <c r="AW59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY59" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA59" t="n">
         <v>8</v>
@@ -13476,7 +13476,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>['4', '86']</t>
+          <t>['4', '85']</t>
         </is>
       </c>
       <c r="Q60" t="n">
@@ -13570,19 +13570,19 @@
         <v>3.59</v>
       </c>
       <c r="AU60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV60" t="n">
         <v>3</v>
       </c>
       <c r="AW60" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX60" t="n">
         <v>7</v>
       </c>
       <c r="AY60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ60" t="n">
         <v>10</v>
@@ -13770,13 +13770,13 @@
         <v>0.5</v>
       </c>
       <c r="AO61" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="AP61" t="n">
         <v>0.63</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.89</v>
+        <v>0.67</v>
       </c>
       <c r="AR61" t="n">
         <v>1.88</v>
@@ -13788,22 +13788,22 @@
         <v>3.12</v>
       </c>
       <c r="AU61" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW61" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AX61" t="n">
         <v>7</v>
       </c>
       <c r="AY61" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AZ61" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA61" t="n">
         <v>8</v>
@@ -13985,13 +13985,13 @@
         <v>2.2</v>
       </c>
       <c r="AN62" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AO62" t="n">
         <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AQ62" t="n">
         <v>0.78</v>
@@ -14006,22 +14006,22 @@
         <v>3.1</v>
       </c>
       <c r="AU62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV62" t="n">
         <v>2</v>
       </c>
       <c r="AW62" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX62" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY62" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ62" t="n">
         <v>12</v>
-      </c>
-      <c r="AX62" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY62" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ62" t="n">
-        <v>7</v>
       </c>
       <c r="BA62" t="n">
         <v>4</v>
@@ -14227,16 +14227,16 @@
         <v>1</v>
       </c>
       <c r="AV63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW63" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX63" t="n">
         <v>9</v>
       </c>
-      <c r="AX63" t="n">
-        <v>10</v>
-      </c>
       <c r="AY63" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ63" t="n">
         <v>15</v>
@@ -14436,28 +14436,28 @@
         <v>1.23</v>
       </c>
       <c r="AS64" t="n">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="AT64" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="AU64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV64" t="n">
         <v>3</v>
       </c>
       <c r="AW64" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AX64" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY64" t="n">
+        <v>19</v>
+      </c>
+      <c r="AZ64" t="n">
         <v>7</v>
-      </c>
-      <c r="AY64" t="n">
-        <v>23</v>
-      </c>
-      <c r="AZ64" t="n">
-        <v>10</v>
       </c>
       <c r="BA64" t="n">
         <v>3</v>
@@ -14651,31 +14651,31 @@
         <v>1.33</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="AS65" t="n">
         <v>1.32</v>
       </c>
       <c r="AT65" t="n">
-        <v>3.14</v>
+        <v>3.03</v>
       </c>
       <c r="AU65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV65" t="n">
         <v>4</v>
       </c>
       <c r="AW65" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AX65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AZ65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA65" t="n">
         <v>5</v>
@@ -14878,31 +14878,31 @@
         <v>3.15</v>
       </c>
       <c r="AU66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV66" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AW66" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AX66" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AY66" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AZ66" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="BA66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB66" t="n">
         <v>8</v>
       </c>
       <c r="BC66" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD66" t="n">
         <v>1.5</v>
@@ -15087,13 +15087,13 @@
         <v>0.33</v>
       </c>
       <c r="AR67" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AS67" t="n">
         <v>1.17</v>
       </c>
       <c r="AT67" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AU67" t="n">
         <v>1</v>
@@ -15314,22 +15314,22 @@
         <v>2.42</v>
       </c>
       <c r="AU68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV68" t="n">
         <v>3</v>
       </c>
       <c r="AW68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX68" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY68" t="n">
         <v>5</v>
       </c>
       <c r="AZ68" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA68" t="n">
         <v>0</v>
@@ -15532,22 +15532,22 @@
         <v>3</v>
       </c>
       <c r="AU69" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV69" t="n">
         <v>4</v>
       </c>
-      <c r="AV69" t="n">
-        <v>5</v>
-      </c>
       <c r="AW69" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX69" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY69" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AZ69" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA69" t="n">
         <v>5</v>
@@ -15753,19 +15753,19 @@
         <v>1</v>
       </c>
       <c r="AV70" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX70" t="n">
         <v>15</v>
       </c>
       <c r="AY70" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AZ70" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA70" t="n">
         <v>1</v>
@@ -15968,22 +15968,22 @@
         <v>3.18</v>
       </c>
       <c r="AU71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV71" t="n">
         <v>2</v>
       </c>
       <c r="AW71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AX71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY71" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AZ71" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BA71" t="n">
         <v>8</v>
@@ -16177,31 +16177,31 @@
         <v>1.75</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="AS72" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AT72" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="AU72" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW72" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX72" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY72" t="n">
         <v>14</v>
       </c>
       <c r="AZ72" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA72" t="n">
         <v>7</v>
@@ -16398,28 +16398,28 @@
         <v>1.45</v>
       </c>
       <c r="AS73" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AT73" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="AU73" t="n">
         <v>1</v>
       </c>
       <c r="AV73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW73" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX73" t="n">
         <v>4</v>
       </c>
       <c r="AY73" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AZ73" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA73" t="n">
         <v>4</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>['19', '33', '39', '90+3']</t>
+          <t>['17', '31', '37', '90+3']</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>['22', '45+3']</t>
+          <t>['20', '45']</t>
         </is>
       </c>
       <c r="Q74" t="n">
@@ -16616,28 +16616,28 @@
         <v>0.91</v>
       </c>
       <c r="AS74" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AT74" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AU74" t="n">
         <v>7</v>
       </c>
       <c r="AV74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW74" t="n">
         <v>5</v>
       </c>
       <c r="AX74" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY74" t="n">
         <v>12</v>
       </c>
       <c r="AZ74" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA74" t="n">
         <v>3</v>
@@ -16831,31 +16831,31 @@
         <v>0.11</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AS75" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AT75" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AU75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV75" t="n">
         <v>2</v>
       </c>
       <c r="AW75" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AX75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY75" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AZ75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA75" t="n">
         <v>4</v>
@@ -17049,13 +17049,13 @@
         <v>1.56</v>
       </c>
       <c r="AR76" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AS76" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AT76" t="n">
-        <v>3.95</v>
+        <v>3.89</v>
       </c>
       <c r="AU76" t="n">
         <v>9</v>
@@ -17258,22 +17258,22 @@
         <v>2.33</v>
       </c>
       <c r="AO77" t="n">
-        <v>1.33</v>
+        <v>0.67</v>
       </c>
       <c r="AP77" t="n">
         <v>1.25</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.89</v>
+        <v>0.67</v>
       </c>
       <c r="AR77" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AS77" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AT77" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="AU77" t="n">
         <v>5</v>
@@ -17485,28 +17485,28 @@
         <v>1.13</v>
       </c>
       <c r="AR78" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="AS78" t="n">
-        <v>1.02</v>
+        <v>0.97</v>
       </c>
       <c r="AT78" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="AU78" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AV78" t="n">
         <v>5</v>
       </c>
       <c r="AW78" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX78" t="n">
         <v>5</v>
       </c>
       <c r="AY78" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ78" t="n">
         <v>10</v>
@@ -17613,7 +17613,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -17703,13 +17703,13 @@
         <v>0.75</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AS79" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AT79" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="AU79" t="n">
         <v>4</v>
@@ -17718,16 +17718,16 @@
         <v>1</v>
       </c>
       <c r="AW79" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY79" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ79" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA79" t="n">
         <v>10</v>
@@ -17836,7 +17836,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="Q80" t="n">
@@ -17921,28 +17921,28 @@
         <v>0.89</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AS80" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="AT80" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AU80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW80" t="n">
         <v>9</v>
       </c>
       <c r="AX80" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AY80" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ80" t="n">
         <v>12</v>
@@ -18054,7 +18054,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>['19', '27', '65']</t>
+          <t>['19', '28', '65']</t>
         </is>
       </c>
       <c r="Q81" t="n">
@@ -18139,31 +18139,31 @@
         <v>0.75</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AS81" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AT81" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="AU81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV81" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW81" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AX81" t="n">
         <v>3</v>
       </c>
       <c r="AY81" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AZ81" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA81" t="n">
         <v>12</v>
@@ -18235,7 +18235,7 @@
         <v>45822.70833333334</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -18357,31 +18357,31 @@
         <v>1.33</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AS82" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AT82" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AU82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW82" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX82" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AY82" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AZ82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA82" t="n">
         <v>3</v>
@@ -18453,7 +18453,7 @@
         <v>45822.70833333334</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>['90+2']</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -18575,31 +18575,31 @@
         <v>1.75</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AS83" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="AU83" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AV83" t="n">
         <v>2</v>
       </c>
       <c r="AW83" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX83" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AY83" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ83" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA83" t="n">
         <v>9</v>
@@ -18671,7 +18671,7 @@
         <v>45822.8125</v>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -18793,31 +18793,31 @@
         <v>0.44</v>
       </c>
       <c r="AR84" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AS84" t="n">
-        <v>1.45</v>
+        <v>1.86</v>
       </c>
       <c r="AT84" t="n">
-        <v>3.03</v>
+        <v>3.43</v>
       </c>
       <c r="AU84" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV84" t="n">
         <v>1</v>
       </c>
       <c r="AW84" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX84" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY84" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ84" t="n">
         <v>4</v>
-      </c>
-      <c r="AY84" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ84" t="n">
-        <v>5</v>
       </c>
       <c r="BA84" t="n">
         <v>7</v>
@@ -18889,7 +18889,7 @@
         <v>45822.8125</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -19011,31 +19011,31 @@
         <v>1.44</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.09</v>
+        <v>1.31</v>
       </c>
       <c r="AS85" t="n">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="AT85" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AU85" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV85" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW85" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX85" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY85" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AZ85" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA85" t="n">
         <v>7</v>
@@ -19107,7 +19107,7 @@
         <v>45823.6875</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -19229,28 +19229,28 @@
         <v>1.11</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="AS86" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AT86" t="n">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="AU86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW86" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY86" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ86" t="n">
         <v>8</v>
@@ -19325,7 +19325,7 @@
         <v>45823.6875</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -19447,31 +19447,31 @@
         <v>0.33</v>
       </c>
       <c r="AR87" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AS87" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AT87" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AU87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV87" t="n">
         <v>3</v>
       </c>
       <c r="AW87" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX87" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY87" t="n">
         <v>13</v>
       </c>
       <c r="AZ87" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA87" t="n">
         <v>11</v>
@@ -19543,7 +19543,7 @@
         <v>45823.79166666666</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -19665,13 +19665,13 @@
         <v>0.78</v>
       </c>
       <c r="AR88" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AS88" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AT88" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="AU88" t="n">
         <v>6</v>
@@ -19680,13 +19680,13 @@
         <v>5</v>
       </c>
       <c r="AW88" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AX88" t="n">
         <v>5</v>
       </c>
       <c r="AY88" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ88" t="n">
         <v>10</v>
@@ -19761,7 +19761,7 @@
         <v>45823.79166666666</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -19883,13 +19883,13 @@
         <v>0.11</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="AS89" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="AT89" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="AU89" t="n">
         <v>4</v>
@@ -19898,16 +19898,16 @@
         <v>3</v>
       </c>
       <c r="AW89" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AX89" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY89" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ89" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA89" t="n">
         <v>7</v>
@@ -19979,7 +19979,7 @@
         <v>45824.8125</v>
       </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -20089,43 +20089,43 @@
         <v>2.35</v>
       </c>
       <c r="AN90" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AO90" t="n">
         <v>1.25</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.7</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="AS90" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AT90" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AU90" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV90" t="n">
         <v>5</v>
       </c>
-      <c r="AV90" t="n">
+      <c r="AW90" t="n">
         <v>4</v>
       </c>
-      <c r="AW90" t="n">
-        <v>3</v>
-      </c>
       <c r="AX90" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY90" t="n">
         <v>8</v>
       </c>
       <c r="AZ90" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BA90" t="n">
         <v>4</v>
@@ -20197,7 +20197,7 @@
         <v>45824.8125</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -20319,31 +20319,31 @@
         <v>1</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AT91" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="AU91" t="n">
         <v>4</v>
       </c>
       <c r="AV91" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AW91" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX91" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY91" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ91" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA91" t="n">
         <v>5</v>
@@ -20415,7 +20415,7 @@
         <v>45836.70833333334</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -20537,13 +20537,13 @@
         <v>0.75</v>
       </c>
       <c r="AR92" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AS92" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AT92" t="n">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AU92" t="n">
         <v>3</v>
@@ -20552,13 +20552,13 @@
         <v>2</v>
       </c>
       <c r="AW92" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX92" t="n">
         <v>6</v>
       </c>
       <c r="AY92" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ92" t="n">
         <v>8</v>
@@ -20633,7 +20633,7 @@
         <v>45836.70833333334</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -20755,31 +20755,31 @@
         <v>1.63</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AT93" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AU93" t="n">
         <v>0</v>
       </c>
       <c r="AV93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX93" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ93" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA93" t="n">
         <v>0</v>
@@ -20851,7 +20851,7 @@
         <v>45836.8125</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -20973,31 +20973,31 @@
         <v>1.63</v>
       </c>
       <c r="AR94" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AS94" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AT94" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
       <c r="AU94" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW94" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX94" t="n">
         <v>7</v>
       </c>
-      <c r="AV94" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW94" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX94" t="n">
-        <v>8</v>
-      </c>
       <c r="AY94" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AZ94" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA94" t="n">
         <v>7</v>
@@ -21069,7 +21069,7 @@
         <v>45836.8125</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -21182,25 +21182,25 @@
         <v>1.25</v>
       </c>
       <c r="AO95" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="AP95" t="n">
         <v>1.67</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.89</v>
+        <v>0.67</v>
       </c>
       <c r="AR95" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AS95" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AT95" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AU95" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV95" t="n">
         <v>1</v>
@@ -21209,13 +21209,13 @@
         <v>12</v>
       </c>
       <c r="AX95" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY95" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ95" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA95" t="n">
         <v>8</v>
@@ -21287,7 +21287,7 @@
         <v>45837.6875</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -21409,13 +21409,13 @@
         <v>0.78</v>
       </c>
       <c r="AR96" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AS96" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AT96" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="AU96" t="n">
         <v>5</v>
@@ -21424,16 +21424,16 @@
         <v>6</v>
       </c>
       <c r="AW96" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX96" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AY96" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ96" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA96" t="n">
         <v>8</v>
@@ -21505,7 +21505,7 @@
         <v>45837.6875</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -21627,13 +21627,13 @@
         <v>0.89</v>
       </c>
       <c r="AR97" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="AS97" t="n">
-        <v>1.04</v>
+        <v>0.86</v>
       </c>
       <c r="AT97" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="AU97" t="n">
         <v>6</v>
@@ -21723,7 +21723,7 @@
         <v>45837.79166666666</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -21845,13 +21845,13 @@
         <v>1.75</v>
       </c>
       <c r="AR98" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AS98" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AT98" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="AU98" t="n">
         <v>3</v>
@@ -21860,16 +21860,16 @@
         <v>3</v>
       </c>
       <c r="AW98" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX98" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AY98" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ98" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA98" t="n">
         <v>4</v>
@@ -21941,7 +21941,7 @@
         <v>45837.79166666666</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -22063,13 +22063,13 @@
         <v>1.13</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AS99" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AT99" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="AU99" t="n">
         <v>6</v>
@@ -22078,16 +22078,16 @@
         <v>1</v>
       </c>
       <c r="AW99" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AX99" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AY99" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AZ99" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BA99" t="n">
         <v>8</v>
@@ -22159,7 +22159,7 @@
         <v>45838.66666666666</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -22281,31 +22281,31 @@
         <v>1.56</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="AS100" t="n">
         <v>1.6</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="AU100" t="n">
         <v>6</v>
       </c>
       <c r="AV100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW100" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX100" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY100" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ100" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA100" t="n">
         <v>4</v>
@@ -22377,7 +22377,7 @@
         <v>45838.8125</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -22499,28 +22499,28 @@
         <v>0.75</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AS101" t="n">
-        <v>0.99</v>
+        <v>1.02</v>
       </c>
       <c r="AT101" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AU101" t="n">
         <v>4</v>
       </c>
       <c r="AV101" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW101" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX101" t="n">
         <v>5</v>
       </c>
-      <c r="AX101" t="n">
-        <v>4</v>
-      </c>
       <c r="AY101" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AZ101" t="n">
         <v>7</v>
@@ -22595,7 +22595,7 @@
         <v>45843.70833333334</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -22717,28 +22717,28 @@
         <v>0.7</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AS102" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AT102" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="AU102" t="n">
         <v>4</v>
       </c>
       <c r="AV102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW102" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX102" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY102" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ102" t="n">
         <v>9</v>
@@ -22813,7 +22813,7 @@
         <v>45843.70833333334</v>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>['45+2', '90+4']</t>
+          <t>['45+1', '90+4']</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -22935,31 +22935,31 @@
         <v>0.44</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AS103" t="n">
-        <v>1.21</v>
+        <v>1.43</v>
       </c>
       <c r="AT103" t="n">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="AU103" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AV103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW103" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX103" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY103" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ103" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA103" t="n">
         <v>4</v>
@@ -23031,7 +23031,7 @@
         <v>45843.8125</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -23063,12 +23063,12 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>['23', '45+3']</t>
+          <t>['24', '45+4']</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>['8', '11', '41']</t>
+          <t>['8', '11', '40']</t>
         </is>
       </c>
       <c r="Q104" t="n">
@@ -23141,28 +23141,28 @@
         <v>1.8</v>
       </c>
       <c r="AN104" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AO104" t="n">
         <v>1.2</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.44</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT104" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="AU104" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AV104" t="n">
         <v>6</v>
@@ -23171,13 +23171,13 @@
         <v>13</v>
       </c>
       <c r="AX104" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY104" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AZ104" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BA104" t="n">
         <v>6</v>
@@ -23249,7 +23249,7 @@
         <v>45843.8125</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -23286,7 +23286,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['90+3']</t>
         </is>
       </c>
       <c r="Q105" t="n">
@@ -23371,16 +23371,16 @@
         <v>1.33</v>
       </c>
       <c r="AR105" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AS105" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AT105" t="n">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="AU105" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV105" t="n">
         <v>2</v>
@@ -23389,13 +23389,13 @@
         <v>6</v>
       </c>
       <c r="AX105" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY105" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ105" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA105" t="n">
         <v>4</v>
@@ -23467,7 +23467,7 @@
         <v>45844.6875</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -23589,31 +23589,31 @@
         <v>1.13</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AS106" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AT106" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="AU106" t="n">
         <v>5</v>
       </c>
       <c r="AV106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW106" t="n">
         <v>4</v>
       </c>
-      <c r="AW106" t="n">
-        <v>7</v>
-      </c>
       <c r="AX106" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY106" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ106" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA106" t="n">
         <v>5</v>
@@ -23685,7 +23685,7 @@
         <v>45844.6875</v>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -23807,31 +23807,31 @@
         <v>0.11</v>
       </c>
       <c r="AR107" t="n">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AS107" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AT107" t="n">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="AU107" t="n">
         <v>2</v>
       </c>
       <c r="AV107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW107" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX107" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AY107" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ107" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA107" t="n">
         <v>4</v>
@@ -23903,7 +23903,7 @@
         <v>45844.79166666666</v>
       </c>
       <c r="F108" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -24025,31 +24025,31 @@
         <v>1</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AS108" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AT108" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="AU108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV108" t="n">
         <v>5</v>
       </c>
       <c r="AW108" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AX108" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AY108" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ108" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="BA108" t="n">
         <v>3</v>
@@ -24121,7 +24121,7 @@
         <v>45844.79166666666</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -24246,37 +24246,37 @@
         <v>1.16</v>
       </c>
       <c r="AS109" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AT109" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AU109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV109" t="n">
         <v>3</v>
       </c>
       <c r="AW109" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX109" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ109" t="n">
         <v>11</v>
       </c>
-      <c r="AY109" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ109" t="n">
-        <v>14</v>
-      </c>
       <c r="BA109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB109" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC109" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BD109" t="n">
         <v>1.87</v>
@@ -24339,7 +24339,7 @@
         <v>45845.8125</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -24461,13 +24461,13 @@
         <v>0.33</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AS110" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AT110" t="n">
-        <v>2.36</v>
+        <v>2.22</v>
       </c>
       <c r="AU110" t="n">
         <v>3</v>
@@ -24476,13 +24476,13 @@
         <v>0</v>
       </c>
       <c r="AW110" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX110" t="n">
         <v>6</v>
       </c>
       <c r="AY110" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ110" t="n">
         <v>6</v>
@@ -24557,7 +24557,7 @@
         <v>45845.8125</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -24679,31 +24679,31 @@
         <v>1.75</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="AS111" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AT111" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AU111" t="n">
         <v>7</v>
       </c>
       <c r="AV111" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AW111" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX111" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY111" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ111" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA111" t="n">
         <v>7</v>
@@ -24775,7 +24775,7 @@
         <v>45850.70833333334</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -24897,31 +24897,31 @@
         <v>0.78</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AT112" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="AU112" t="n">
         <v>2</v>
       </c>
       <c r="AV112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW112" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX112" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AY112" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ112" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BA112" t="n">
         <v>3</v>
@@ -24993,7 +24993,7 @@
         <v>45850.70833333334</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -25115,31 +25115,31 @@
         <v>1.63</v>
       </c>
       <c r="AR113" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AS113" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AT113" t="n">
-        <v>3.45</v>
+        <v>3.33</v>
       </c>
       <c r="AU113" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV113" t="n">
         <v>3</v>
       </c>
-      <c r="AV113" t="n">
-        <v>2</v>
-      </c>
       <c r="AW113" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX113" t="n">
         <v>4</v>
       </c>
-      <c r="AX113" t="n">
-        <v>6</v>
-      </c>
       <c r="AY113" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ113" t="n">
         <v>7</v>
-      </c>
-      <c r="AZ113" t="n">
-        <v>8</v>
       </c>
       <c r="BA113" t="n">
         <v>4</v>
@@ -25211,7 +25211,7 @@
         <v>45850.8125</v>
       </c>
       <c r="F114" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -25333,22 +25333,22 @@
         <v>1.33</v>
       </c>
       <c r="AR114" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS114" t="n">
         <v>1.37</v>
       </c>
-      <c r="AS114" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AT114" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AU114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV114" t="n">
         <v>5</v>
       </c>
       <c r="AW114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX114" t="n">
         <v>12</v>
@@ -25429,7 +25429,7 @@
         <v>45850.8125</v>
       </c>
       <c r="F115" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -25551,28 +25551,28 @@
         <v>0.89</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AS115" t="n">
-        <v>0.98</v>
+        <v>0.83</v>
       </c>
       <c r="AT115" t="n">
-        <v>2.5</v>
+        <v>2.24</v>
       </c>
       <c r="AU115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV115" t="n">
         <v>3</v>
       </c>
-      <c r="AV115" t="n">
-        <v>5</v>
-      </c>
       <c r="AW115" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX115" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY115" t="n">
         <v>9</v>
-      </c>
-      <c r="AX115" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY115" t="n">
-        <v>12</v>
       </c>
       <c r="AZ115" t="n">
         <v>11</v>
@@ -25647,7 +25647,7 @@
         <v>45851.6875</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -25769,31 +25769,31 @@
         <v>1.63</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="AS116" t="n">
         <v>1.44</v>
       </c>
       <c r="AT116" t="n">
-        <v>2.82</v>
+        <v>2.97</v>
       </c>
       <c r="AU116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW116" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AX116" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AY116" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AZ116" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="BA116" t="n">
         <v>7</v>
@@ -25865,7 +25865,7 @@
         <v>45851.6875</v>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -25987,31 +25987,31 @@
         <v>1.13</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AS117" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AT117" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="AU117" t="n">
         <v>3</v>
       </c>
       <c r="AV117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW117" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX117" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AY117" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ117" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BA117" t="n">
         <v>4</v>
@@ -26083,7 +26083,7 @@
         <v>45851.79166666666</v>
       </c>
       <c r="F118" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -26205,13 +26205,13 @@
         <v>1.75</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AS118" t="n">
         <v>1.21</v>
       </c>
       <c r="AT118" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="AU118" t="n">
         <v>6</v>
@@ -26220,16 +26220,16 @@
         <v>2</v>
       </c>
       <c r="AW118" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AX118" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AY118" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AZ118" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BA118" t="n">
         <v>6</v>
@@ -26301,7 +26301,7 @@
         <v>45851.79166666666</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -26414,22 +26414,22 @@
         <v>3</v>
       </c>
       <c r="AO119" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AP119" t="n">
         <v>2.67</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.89</v>
+        <v>0.67</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AS119" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AT119" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AU119" t="n">
         <v>4</v>
@@ -26438,16 +26438,16 @@
         <v>0</v>
       </c>
       <c r="AW119" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX119" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY119" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AZ119" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA119" t="n">
         <v>10</v>
@@ -26519,7 +26519,7 @@
         <v>45852.8125</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -26641,22 +26641,22 @@
         <v>1.56</v>
       </c>
       <c r="AR120" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AT120" t="n">
         <v>3.98</v>
       </c>
       <c r="AU120" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV120" t="n">
         <v>2</v>
       </c>
       <c r="AW120" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX120" t="n">
         <v>2</v>
@@ -26737,7 +26737,7 @@
         <v>45852.8125</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -26859,13 +26859,13 @@
         <v>0.75</v>
       </c>
       <c r="AR121" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AS121" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AT121" t="n">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="AU121" t="n">
         <v>0</v>
@@ -26874,16 +26874,16 @@
         <v>1</v>
       </c>
       <c r="AW121" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX121" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY121" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ121" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA121" t="n">
         <v>4</v>
@@ -26955,7 +26955,7 @@
         <v>45857.70833333334</v>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -27077,13 +27077,13 @@
         <v>0.75</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AS122" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AT122" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="AU122" t="n">
         <v>2</v>
@@ -27092,16 +27092,16 @@
         <v>6</v>
       </c>
       <c r="AW122" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX122" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY122" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ122" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA122" t="n">
         <v>3</v>
@@ -27173,7 +27173,7 @@
         <v>45857.70833333334</v>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>['63', '83', '90+5']</t>
+          <t>['63', '83', '90+4']</t>
         </is>
       </c>
       <c r="Q123" t="n">
@@ -27295,13 +27295,13 @@
         <v>1</v>
       </c>
       <c r="AR123" t="n">
-        <v>1.89</v>
+        <v>1.66</v>
       </c>
       <c r="AS123" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AT123" t="n">
-        <v>3.56</v>
+        <v>3.34</v>
       </c>
       <c r="AU123" t="n">
         <v>6</v>
@@ -27310,25 +27310,25 @@
         <v>4</v>
       </c>
       <c r="AW123" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC123" t="n">
         <v>6</v>
-      </c>
-      <c r="AX123" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY123" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ123" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA123" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB123" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC123" t="n">
-        <v>8</v>
       </c>
       <c r="BD123" t="n">
         <v>1.53</v>
@@ -27391,7 +27391,7 @@
         <v>45857.8125</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -27513,31 +27513,31 @@
         <v>0.7</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AT124" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="AU124" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV124" t="n">
         <v>2</v>
       </c>
       <c r="AW124" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX124" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY124" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AZ124" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BA124" t="n">
         <v>8</v>
@@ -27609,7 +27609,7 @@
         <v>45857.8125</v>
       </c>
       <c r="F125" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -27731,13 +27731,13 @@
         <v>0.11</v>
       </c>
       <c r="AR125" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AS125" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AT125" t="n">
-        <v>3.18</v>
+        <v>2.89</v>
       </c>
       <c r="AU125" t="n">
         <v>6</v>
@@ -27746,16 +27746,16 @@
         <v>2</v>
       </c>
       <c r="AW125" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY125" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ125" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA125" t="n">
         <v>2</v>
@@ -27937,43 +27937,43 @@
         <v>1.7</v>
       </c>
       <c r="AN126" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AO126" t="n">
         <v>0.83</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.11</v>
       </c>
       <c r="AR126" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AS126" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AT126" t="n">
-        <v>3.06</v>
+        <v>3.16</v>
       </c>
       <c r="AU126" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AV126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW126" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AX126" t="n">
         <v>5</v>
       </c>
       <c r="AY126" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AZ126" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA126" t="n">
         <v>10</v>
@@ -28170,28 +28170,28 @@
         <v>2.15</v>
       </c>
       <c r="AS127" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="AT127" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AU127" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV127" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AW127" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX127" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AY127" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AZ127" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA127" t="n">
         <v>7</v>
@@ -28385,13 +28385,13 @@
         <v>1.75</v>
       </c>
       <c r="AR128" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="AT128" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AU128" t="n">
         <v>1</v>
@@ -28400,16 +28400,16 @@
         <v>4</v>
       </c>
       <c r="AW128" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AX128" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY128" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AZ128" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BA128" t="n">
         <v>3</v>
@@ -28603,31 +28603,31 @@
         <v>0.44</v>
       </c>
       <c r="AR129" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AS129" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AT129" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="AU129" t="n">
         <v>5</v>
       </c>
       <c r="AV129" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW129" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AX129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY129" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AZ129" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BA129" t="n">
         <v>9</v>
@@ -28821,16 +28821,16 @@
         <v>1.44</v>
       </c>
       <c r="AR130" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AS130" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AT130" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AU130" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV130" t="n">
         <v>0</v>
@@ -28842,7 +28842,7 @@
         <v>7</v>
       </c>
       <c r="AY130" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ130" t="n">
         <v>7</v>
@@ -29039,31 +29039,31 @@
         <v>1.13</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AS131" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="AT131" t="n">
-        <v>2.99</v>
+        <v>2.8</v>
       </c>
       <c r="AU131" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV131" t="n">
         <v>2</v>
       </c>
       <c r="AW131" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX131" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY131" t="n">
         <v>11</v>
       </c>
       <c r="AZ131" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA131" t="n">
         <v>2</v>
@@ -29172,7 +29172,7 @@
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="Q132" t="n">
@@ -29257,31 +29257,31 @@
         <v>1.75</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AS132" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AT132" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AU132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV132" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AW132" t="n">
         <v>9</v>
       </c>
       <c r="AX132" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY132" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ132" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA132" t="n">
         <v>5</v>
@@ -29475,13 +29475,13 @@
         <v>1.33</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AS133" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AT133" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="AU133" t="n">
         <v>2</v>
@@ -29693,31 +29693,31 @@
         <v>0.89</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AS134" t="n">
-        <v>1.07</v>
+        <v>0.89</v>
       </c>
       <c r="AT134" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="AU134" t="n">
         <v>3</v>
       </c>
       <c r="AV134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW134" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX134" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AY134" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ134" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA134" t="n">
         <v>7</v>
@@ -29821,7 +29821,7 @@
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>['13', '22', '86']</t>
+          <t>['13', '22', '85']</t>
         </is>
       </c>
       <c r="P135" t="inlineStr">
@@ -29911,16 +29911,16 @@
         <v>0.75</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AT135" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AU135" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV135" t="n">
         <v>2</v>
@@ -29929,13 +29929,13 @@
         <v>6</v>
       </c>
       <c r="AX135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ135" t="n">
         <v>5</v>
-      </c>
-      <c r="AY135" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ135" t="n">
-        <v>7</v>
       </c>
       <c r="BA135" t="n">
         <v>6</v>
@@ -30129,31 +30129,31 @@
         <v>1.63</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AS136" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AT136" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="AU136" t="n">
         <v>5</v>
       </c>
       <c r="AV136" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW136" t="n">
         <v>6</v>
       </c>
       <c r="AX136" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY136" t="n">
         <v>11</v>
       </c>
       <c r="AZ136" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA136" t="n">
         <v>5</v>
@@ -30338,22 +30338,22 @@
         <v>1.5</v>
       </c>
       <c r="AO137" t="n">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="AP137" t="n">
         <v>1.44</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.89</v>
+        <v>0.67</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AS137" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AT137" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="AU137" t="n">
         <v>7</v>
@@ -30362,13 +30362,13 @@
         <v>3</v>
       </c>
       <c r="AW137" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX137" t="n">
         <v>4</v>
       </c>
       <c r="AY137" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ137" t="n">
         <v>7</v>
@@ -30565,13 +30565,13 @@
         <v>1.13</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AS138" t="n">
-        <v>1.02</v>
+        <v>0.95</v>
       </c>
       <c r="AT138" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AU138" t="n">
         <v>5</v>
@@ -30783,31 +30783,31 @@
         <v>0.78</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AS139" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AT139" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="AU139" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AV139" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW139" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AX139" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY139" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="AZ139" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BA139" t="n">
         <v>9</v>
@@ -31001,16 +31001,16 @@
         <v>1</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AT140" t="n">
-        <v>2.93</v>
+        <v>3.03</v>
       </c>
       <c r="AU140" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV140" t="n">
         <v>3</v>
@@ -31019,13 +31019,13 @@
         <v>11</v>
       </c>
       <c r="AX140" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AY140" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ140" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA140" t="n">
         <v>4</v>
@@ -31129,7 +31129,7 @@
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="P141" t="inlineStr">
@@ -31219,13 +31219,13 @@
         <v>1.56</v>
       </c>
       <c r="AR141" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS141" t="n">
         <v>1.38</v>
       </c>
-      <c r="AS141" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AT141" t="n">
-        <v>2.79</v>
+        <v>2.97</v>
       </c>
       <c r="AU141" t="n">
         <v>4</v>
@@ -31234,16 +31234,16 @@
         <v>3</v>
       </c>
       <c r="AW141" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX141" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY141" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ141" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA141" t="n">
         <v>7</v>
@@ -31352,7 +31352,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="Q142" t="n">
@@ -31425,43 +31425,43 @@
         <v>1.83</v>
       </c>
       <c r="AN142" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AO142" t="n">
         <v>0.83</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.75</v>
       </c>
       <c r="AR142" t="n">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AS142" t="n">
         <v>1.11</v>
       </c>
       <c r="AT142" t="n">
-        <v>2.98</v>
+        <v>3.16</v>
       </c>
       <c r="AU142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW142" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AX142" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY142" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AZ142" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="BA142" t="n">
         <v>5</v>
@@ -31655,31 +31655,31 @@
         <v>1.13</v>
       </c>
       <c r="AR143" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AS143" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AT143" t="n">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="AU143" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV143" t="n">
         <v>2</v>
       </c>
       <c r="AW143" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX143" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ143" t="n">
         <v>8</v>
-      </c>
-      <c r="AY143" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ143" t="n">
-        <v>10</v>
       </c>
       <c r="BA143" t="n">
         <v>6</v>
@@ -31873,31 +31873,31 @@
         <v>1.11</v>
       </c>
       <c r="AR144" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="AS144" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AT144" t="n">
-        <v>3.04</v>
+        <v>2.85</v>
       </c>
       <c r="AU144" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW144" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX144" t="n">
         <v>9</v>
       </c>
       <c r="AY144" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ144" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA144" t="n">
         <v>11</v>
@@ -32001,7 +32001,7 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>['56', '79']</t>
+          <t>['56', '78']</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -32091,31 +32091,31 @@
         <v>0.33</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AS145" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AT145" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="AU145" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV145" t="n">
         <v>1</v>
       </c>
       <c r="AW145" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX145" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ145" t="n">
         <v>6</v>
-      </c>
-      <c r="AY145" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ145" t="n">
-        <v>7</v>
       </c>
       <c r="BA145" t="n">
         <v>5</v>
@@ -32309,31 +32309,31 @@
         <v>0.7</v>
       </c>
       <c r="AR146" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AS146" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AT146" t="n">
-        <v>3.41</v>
+        <v>3.48</v>
       </c>
       <c r="AU146" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV146" t="n">
         <v>1</v>
       </c>
       <c r="AW146" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX146" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ146" t="n">
         <v>7</v>
-      </c>
-      <c r="AY146" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ146" t="n">
-        <v>8</v>
       </c>
       <c r="BA146" t="n">
         <v>10</v>
@@ -32527,13 +32527,13 @@
         <v>1.44</v>
       </c>
       <c r="AR147" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AS147" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AT147" t="n">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="AU147" t="n">
         <v>4</v>
@@ -32542,16 +32542,16 @@
         <v>4</v>
       </c>
       <c r="AW147" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX147" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY147" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ147" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA147" t="n">
         <v>5</v>
@@ -32745,13 +32745,13 @@
         <v>0.44</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AS148" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AT148" t="n">
-        <v>2.59</v>
+        <v>2.73</v>
       </c>
       <c r="AU148" t="n">
         <v>4</v>
@@ -32966,28 +32966,28 @@
         <v>1.35</v>
       </c>
       <c r="AS149" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AT149" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="AU149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW149" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX149" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY149" t="n">
         <v>6</v>
       </c>
       <c r="AZ149" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA149" t="n">
         <v>4</v>
@@ -33172,22 +33172,22 @@
         <v>1.67</v>
       </c>
       <c r="AO150" t="n">
-        <v>1.14</v>
+        <v>0.86</v>
       </c>
       <c r="AP150" t="n">
         <v>2</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.89</v>
+        <v>0.67</v>
       </c>
       <c r="AR150" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="AS150" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AT150" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="AU150" t="n">
         <v>9</v>
@@ -33196,16 +33196,16 @@
         <v>1</v>
       </c>
       <c r="AW150" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX150" t="n">
         <v>10</v>
       </c>
-      <c r="AX150" t="n">
-        <v>8</v>
-      </c>
       <c r="AY150" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AZ150" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA150" t="n">
         <v>6</v>
@@ -33399,31 +33399,31 @@
         <v>1.63</v>
       </c>
       <c r="AR151" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AS151" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AT151" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="AU151" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV151" t="n">
         <v>1</v>
       </c>
       <c r="AW151" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX151" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AY151" t="n">
         <v>12</v>
       </c>
       <c r="AZ151" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA151" t="n">
         <v>3</v>
@@ -33617,31 +33617,31 @@
         <v>1.63</v>
       </c>
       <c r="AR152" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="AS152" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AT152" t="n">
-        <v>2.91</v>
+        <v>3.09</v>
       </c>
       <c r="AU152" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV152" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AW152" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX152" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY152" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AZ152" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="BA152" t="n">
         <v>5</v>
@@ -33745,7 +33745,7 @@
       </c>
       <c r="O153" t="inlineStr">
         <is>
-          <t>['52']</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="P153" t="inlineStr">
@@ -33835,13 +33835,13 @@
         <v>1.33</v>
       </c>
       <c r="AR153" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AS153" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AT153" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="AU153" t="n">
         <v>4</v>
@@ -33850,16 +33850,16 @@
         <v>3</v>
       </c>
       <c r="AW153" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX153" t="n">
         <v>5</v>
       </c>
-      <c r="AX153" t="n">
-        <v>4</v>
-      </c>
       <c r="AY153" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ153" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA153" t="n">
         <v>5</v>
@@ -34053,13 +34053,13 @@
         <v>0.78</v>
       </c>
       <c r="AR154" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AS154" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AT154" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AU154" t="n">
         <v>3</v>
@@ -34068,13 +34068,13 @@
         <v>3</v>
       </c>
       <c r="AW154" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX154" t="n">
         <v>8</v>
       </c>
       <c r="AY154" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ154" t="n">
         <v>11</v>
@@ -34271,28 +34271,28 @@
         <v>0.89</v>
       </c>
       <c r="AR155" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AS155" t="n">
-        <v>1.15</v>
+        <v>0.99</v>
       </c>
       <c r="AT155" t="n">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="AU155" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV155" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW155" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AX155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY155" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ155" t="n">
         <v>4</v>
@@ -34404,7 +34404,7 @@
       </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>['63', '71']</t>
+          <t>['64', '72']</t>
         </is>
       </c>
       <c r="Q156" t="n">
@@ -34489,31 +34489,31 @@
         <v>1.75</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AS156" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AT156" t="n">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="AU156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV156" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW156" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX156" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY156" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AZ156" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA156" t="n">
         <v>10</v>
@@ -34617,12 +34617,12 @@
       </c>
       <c r="O157" t="inlineStr">
         <is>
-          <t>['12', '51']</t>
+          <t>['13', '51']</t>
         </is>
       </c>
       <c r="P157" t="inlineStr">
         <is>
-          <t>['9']</t>
+          <t>['10']</t>
         </is>
       </c>
       <c r="Q157" t="n">
@@ -34707,31 +34707,31 @@
         <v>1.56</v>
       </c>
       <c r="AR157" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AS157" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AT157" t="n">
-        <v>2.89</v>
+        <v>2.78</v>
       </c>
       <c r="AU157" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV157" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AW157" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX157" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY157" t="n">
         <v>11</v>
       </c>
       <c r="AZ157" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA157" t="n">
         <v>3</v>
@@ -34835,7 +34835,7 @@
       </c>
       <c r="O158" t="inlineStr">
         <is>
-          <t>['36']</t>
+          <t>['37']</t>
         </is>
       </c>
       <c r="P158" t="inlineStr">
@@ -34925,13 +34925,13 @@
         <v>0.33</v>
       </c>
       <c r="AR158" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AT158" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="AU158" t="n">
         <v>2</v>
@@ -34940,13 +34940,13 @@
         <v>1</v>
       </c>
       <c r="AW158" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX158" t="n">
         <v>5</v>
       </c>
       <c r="AY158" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ158" t="n">
         <v>6</v>
@@ -35143,31 +35143,31 @@
         <v>1.75</v>
       </c>
       <c r="AR159" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AS159" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AT159" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="AU159" t="n">
         <v>3</v>
       </c>
       <c r="AV159" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AW159" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX159" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY159" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ159" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA159" t="n">
         <v>4</v>
@@ -35361,31 +35361,31 @@
         <v>0.75</v>
       </c>
       <c r="AR160" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AS160" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AT160" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AU160" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV160" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW160" t="n">
         <v>8</v>
       </c>
       <c r="AX160" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AY160" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ160" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA160" t="n">
         <v>4</v>
@@ -35579,31 +35579,31 @@
         <v>1</v>
       </c>
       <c r="AR161" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AS161" t="n">
         <v>1.64</v>
       </c>
       <c r="AT161" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="AU161" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV161" t="n">
         <v>5</v>
       </c>
-      <c r="AV161" t="n">
-        <v>3</v>
-      </c>
       <c r="AW161" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX161" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AY161" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AZ161" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="BA161" t="n">
         <v>7</v>
@@ -35797,28 +35797,28 @@
         <v>0.11</v>
       </c>
       <c r="AR162" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AS162" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AT162" t="n">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="AU162" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV162" t="n">
         <v>1</v>
       </c>
       <c r="AW162" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX162" t="n">
         <v>4</v>
       </c>
       <c r="AY162" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ162" t="n">
         <v>5</v>
@@ -36015,31 +36015,31 @@
         <v>0.44</v>
       </c>
       <c r="AR163" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AS163" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="AT163" t="n">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="AU163" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AV163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW163" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AX163" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY163" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AZ163" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA163" t="n">
         <v>13</v>
@@ -36148,7 +36148,7 @@
       </c>
       <c r="P164" t="inlineStr">
         <is>
-          <t>['59', '77']</t>
+          <t>['59', '76']</t>
         </is>
       </c>
       <c r="Q164" t="n">
@@ -36221,43 +36221,43 @@
         <v>1.7</v>
       </c>
       <c r="AN164" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="AO164" t="n">
         <v>1.14</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.13</v>
       </c>
       <c r="AR164" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AS164" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AT164" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="AU164" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV164" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW164" t="n">
         <v>5</v>
       </c>
-      <c r="AW164" t="n">
-        <v>3</v>
-      </c>
       <c r="AX164" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY164" t="n">
         <v>7</v>
       </c>
       <c r="AZ164" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BA164" t="n">
         <v>8</v>
@@ -36451,31 +36451,31 @@
         <v>1.13</v>
       </c>
       <c r="AR165" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AS165" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="AT165" t="n">
-        <v>3.22</v>
+        <v>2.94</v>
       </c>
       <c r="AU165" t="n">
         <v>7</v>
       </c>
       <c r="AV165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW165" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX165" t="n">
         <v>4</v>
       </c>
       <c r="AY165" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ165" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA165" t="n">
         <v>8</v>
@@ -36669,13 +36669,13 @@
         <v>1.11</v>
       </c>
       <c r="AR166" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AS166" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AT166" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="AU166" t="n">
         <v>3</v>
@@ -36890,13 +36890,13 @@
         <v>1.31</v>
       </c>
       <c r="AS167" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AT167" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="AU167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV167" t="n">
         <v>7</v>
@@ -36905,13 +36905,13 @@
         <v>4</v>
       </c>
       <c r="AX167" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AY167" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ167" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BA167" t="n">
         <v>6</v>
@@ -37105,13 +37105,13 @@
         <v>0.7</v>
       </c>
       <c r="AR168" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="AS168" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AT168" t="n">
-        <v>3.21</v>
+        <v>3.3</v>
       </c>
       <c r="AU168" t="n">
         <v>6</v>
@@ -37120,16 +37120,16 @@
         <v>0</v>
       </c>
       <c r="AW168" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX168" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY168" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ168" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA168" t="n">
         <v>5</v>
@@ -37314,40 +37314,40 @@
         <v>1.88</v>
       </c>
       <c r="AO169" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP169" t="n">
         <v>2</v>
       </c>
       <c r="AQ169" t="n">
-        <v>0.89</v>
+        <v>0.67</v>
       </c>
       <c r="AR169" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="AS169" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AT169" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AU169" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX169" t="n">
         <v>7</v>
       </c>
-      <c r="AV169" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW169" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX169" t="n">
-        <v>9</v>
-      </c>
       <c r="AY169" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ169" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA169" t="n">
         <v>6</v>
@@ -37541,31 +37541,31 @@
         <v>1.44</v>
       </c>
       <c r="AR170" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AS170" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AT170" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AU170" t="n">
         <v>2</v>
       </c>
       <c r="AV170" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW170" t="n">
         <v>15</v>
       </c>
       <c r="AX170" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY170" t="n">
         <v>17</v>
       </c>
       <c r="AZ170" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA170" t="n">
         <v>11</v>
@@ -37759,40 +37759,40 @@
         <v>0.75</v>
       </c>
       <c r="AR171" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AS171" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AT171" t="n">
-        <v>2.35</v>
+        <v>2.49</v>
       </c>
       <c r="AU171" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ171" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA171" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB171" t="n">
         <v>5</v>
       </c>
-      <c r="AV171" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW171" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX171" t="n">
+      <c r="BC171" t="n">
         <v>6</v>
-      </c>
-      <c r="AY171" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ171" t="n">
-        <v>11</v>
-      </c>
-      <c r="BA171" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB171" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC171" t="n">
-        <v>8</v>
       </c>
       <c r="BD171" t="n">
         <v>1.91</v>
@@ -37977,10 +37977,10 @@
         <v>1.56</v>
       </c>
       <c r="AR172" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AS172" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AT172" t="n">
         <v>2.78</v>
@@ -38195,13 +38195,13 @@
         <v>0.89</v>
       </c>
       <c r="AR173" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="AS173" t="n">
-        <v>1.1</v>
+        <v>0.95</v>
       </c>
       <c r="AT173" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AU173" t="n">
         <v>6</v>
@@ -38413,13 +38413,13 @@
         <v>0.7</v>
       </c>
       <c r="AR174" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="AS174" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT174" t="n">
-        <v>2.87</v>
+        <v>3.01</v>
       </c>
       <c r="AU174" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP174"/>
+  <dimension ref="A1:BP179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,7 +1350,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.78</v>
@@ -1783,10 +1783,10 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2001,10 +2001,10 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.89</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ22" t="n">
         <v>1</v>
@@ -5707,7 +5707,7 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ24" t="n">
         <v>1.11</v>
@@ -5928,7 +5928,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR25" t="n">
         <v>1.88</v>
@@ -6146,7 +6146,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR26" t="n">
         <v>1.64</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ27" t="n">
         <v>1.75</v>
@@ -6797,10 +6797,10 @@
         <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR29" t="n">
         <v>0.92</v>
@@ -8108,7 +8108,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR35" t="n">
         <v>1.33</v>
@@ -9195,7 +9195,7 @@
         <v>3</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.63</v>
@@ -10070,7 +10070,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR44" t="n">
         <v>0.93</v>
@@ -10503,7 +10503,7 @@
         <v>0.5</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ46" t="n">
         <v>0.7</v>
@@ -11157,10 +11157,10 @@
         <v>0.5</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR49" t="n">
         <v>1.67</v>
@@ -11593,7 +11593,7 @@
         <v>0</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ51" t="n">
         <v>1.11</v>
@@ -12250,7 +12250,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR54" t="n">
         <v>1.22</v>
@@ -12683,7 +12683,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.44</v>
@@ -13119,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.11</v>
@@ -13776,7 +13776,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR61" t="n">
         <v>1.88</v>
@@ -14427,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="AP64" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ64" t="n">
         <v>1.44</v>
@@ -14645,10 +14645,10 @@
         <v>1.67</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ65" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR65" t="n">
         <v>1.71</v>
@@ -14863,7 +14863,7 @@
         <v>0</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.44</v>
@@ -15084,7 +15084,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR67" t="n">
         <v>1.2</v>
@@ -16174,7 +16174,7 @@
         <v>0.63</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR72" t="n">
         <v>1.48</v>
@@ -16389,7 +16389,7 @@
         <v>0.33</v>
       </c>
       <c r="AP73" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.13</v>
@@ -17264,7 +17264,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR77" t="n">
         <v>1.4</v>
@@ -18133,7 +18133,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.75</v>
@@ -18354,7 +18354,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR82" t="n">
         <v>1.29</v>
@@ -19005,7 +19005,7 @@
         <v>0.75</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.44</v>
@@ -19223,7 +19223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ86" t="n">
         <v>1.11</v>
@@ -19444,7 +19444,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR87" t="n">
         <v>1.09</v>
@@ -20749,7 +20749,7 @@
         <v>1.75</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.63</v>
@@ -21185,10 +21185,10 @@
         <v>0.75</v>
       </c>
       <c r="AP95" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR95" t="n">
         <v>1.62</v>
@@ -21842,7 +21842,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR98" t="n">
         <v>1.45</v>
@@ -22493,7 +22493,7 @@
         <v>0.5</v>
       </c>
       <c r="AP101" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ101" t="n">
         <v>0.75</v>
@@ -23368,7 +23368,7 @@
         <v>2</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR105" t="n">
         <v>2.24</v>
@@ -23583,7 +23583,7 @@
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.13</v>
@@ -24458,7 +24458,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR110" t="n">
         <v>1.21</v>
@@ -24673,7 +24673,7 @@
         <v>1.4</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ111" t="n">
         <v>1.75</v>
@@ -24891,7 +24891,7 @@
         <v>0.33</v>
       </c>
       <c r="AP112" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.78</v>
@@ -25109,7 +25109,7 @@
         <v>2.6</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.63</v>
@@ -25330,7 +25330,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR114" t="n">
         <v>1.46</v>
@@ -25763,7 +25763,7 @@
         <v>2</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ116" t="n">
         <v>1.63</v>
@@ -26202,7 +26202,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR118" t="n">
         <v>1.75</v>
@@ -26420,7 +26420,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR119" t="n">
         <v>1.4</v>
@@ -26853,7 +26853,7 @@
         <v>1</v>
       </c>
       <c r="AP121" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ121" t="n">
         <v>0.75</v>
@@ -27725,7 +27725,7 @@
         <v>0</v>
       </c>
       <c r="AP125" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.11</v>
@@ -28164,7 +28164,7 @@
         <v>2</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR127" t="n">
         <v>2.15</v>
@@ -29254,7 +29254,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ132" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR132" t="n">
         <v>1.59</v>
@@ -29472,7 +29472,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR133" t="n">
         <v>1.33</v>
@@ -29687,7 +29687,7 @@
         <v>1.17</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.89</v>
@@ -29905,7 +29905,7 @@
         <v>1</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ135" t="n">
         <v>0.75</v>
@@ -30344,7 +30344,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR137" t="n">
         <v>1.81</v>
@@ -30559,7 +30559,7 @@
         <v>1.33</v>
       </c>
       <c r="AP138" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.13</v>
@@ -30777,7 +30777,7 @@
         <v>0.43</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ139" t="n">
         <v>0.78</v>
@@ -31213,7 +31213,7 @@
         <v>1.33</v>
       </c>
       <c r="AP141" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ141" t="n">
         <v>1.56</v>
@@ -32085,10 +32085,10 @@
         <v>0.43</v>
       </c>
       <c r="AP145" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR145" t="n">
         <v>1.78</v>
@@ -33178,7 +33178,7 @@
         <v>2</v>
       </c>
       <c r="AQ150" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR150" t="n">
         <v>2.21</v>
@@ -33611,7 +33611,7 @@
         <v>1.86</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ152" t="n">
         <v>1.63</v>
@@ -33832,7 +33832,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AR153" t="n">
         <v>1.49</v>
@@ -34483,10 +34483,10 @@
         <v>1.57</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AR156" t="n">
         <v>1.55</v>
@@ -34922,7 +34922,7 @@
         <v>2.13</v>
       </c>
       <c r="AQ158" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AR158" t="n">
         <v>1.26</v>
@@ -35137,7 +35137,7 @@
         <v>1.57</v>
       </c>
       <c r="AP159" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AQ159" t="n">
         <v>1.75</v>
@@ -35355,7 +35355,7 @@
         <v>0.86</v>
       </c>
       <c r="AP160" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AQ160" t="n">
         <v>0.75</v>
@@ -36663,7 +36663,7 @@
         <v>0.88</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AQ166" t="n">
         <v>1.11</v>
@@ -37320,7 +37320,7 @@
         <v>2</v>
       </c>
       <c r="AQ169" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AR169" t="n">
         <v>1.52</v>
@@ -38486,6 +38486,1096 @@
       </c>
       <c r="BP174" t="n">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="n">
+        <v>7845516</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>45893.6875</v>
+      </c>
+      <c r="F175" t="n">
+        <v>18</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Anápolis</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>1</v>
+      </c>
+      <c r="L175" t="n">
+        <v>1</v>
+      </c>
+      <c r="M175" t="n">
+        <v>1</v>
+      </c>
+      <c r="N175" t="n">
+        <v>2</v>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>['45+3']</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R175" t="n">
+        <v>2</v>
+      </c>
+      <c r="S175" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T175" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U175" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V175" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W175" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X175" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU175" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ175" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA175" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB175" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC175" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD175" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BE175" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="BF175" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG175" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH175" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="BI175" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ175" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BK175" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL175" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BM175" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN175" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO175" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BP175" t="n">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="n">
+        <v>7845512</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>45893.6875</v>
+      </c>
+      <c r="F176" t="n">
+        <v>18</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Itabaiana</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Maringá</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
+        <v>2</v>
+      </c>
+      <c r="J176" t="n">
+        <v>2</v>
+      </c>
+      <c r="K176" t="n">
+        <v>4</v>
+      </c>
+      <c r="L176" t="n">
+        <v>2</v>
+      </c>
+      <c r="M176" t="n">
+        <v>2</v>
+      </c>
+      <c r="N176" t="n">
+        <v>4</v>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>['4', '37']</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>['19', '44']</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R176" t="n">
+        <v>2</v>
+      </c>
+      <c r="S176" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T176" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U176" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="V176" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W176" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X176" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ176" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX176" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY176" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ176" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA176" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB176" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC176" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD176" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BE176" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="BF176" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BG176" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH176" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="BI176" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ176" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BK176" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL176" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BM176" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN176" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BO176" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BP176" t="n">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="n">
+        <v>7845515</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="n">
+        <v>45893.79166666666</v>
+      </c>
+      <c r="F177" t="n">
+        <v>18</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>1</v>
+      </c>
+      <c r="M177" t="n">
+        <v>1</v>
+      </c>
+      <c r="N177" t="n">
+        <v>2</v>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>['52']</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>['69']</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R177" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S177" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T177" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U177" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V177" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W177" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X177" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ177" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AU177" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV177" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX177" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ177" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA177" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB177" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC177" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD177" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BE177" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF177" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG177" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH177" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI177" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ177" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK177" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BL177" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM177" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN177" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BO177" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BP177" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="n">
+        <v>7845511</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="n">
+        <v>45893.79166666666</v>
+      </c>
+      <c r="F178" t="n">
+        <v>18</v>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Retrô</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>1</v>
+      </c>
+      <c r="M178" t="n">
+        <v>1</v>
+      </c>
+      <c r="N178" t="n">
+        <v>2</v>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>['48']</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>4</v>
+      </c>
+      <c r="R178" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="S178" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T178" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U178" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V178" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W178" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X178" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX178" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY178" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ178" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA178" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB178" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC178" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD178" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BE178" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="BF178" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BG178" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH178" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BI178" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BJ178" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BK178" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BL178" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM178" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN178" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO178" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BP178" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="n">
+        <v>7845520</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="n">
+        <v>45893.79166666666</v>
+      </c>
+      <c r="F179" t="n">
+        <v>18</v>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Botafogo PB</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Tombense</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="n">
+        <v>1</v>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>['77']</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R179" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S179" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T179" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U179" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V179" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="W179" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X179" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y179" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF179" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG179" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AH179" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AI179" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ179" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK179" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AL179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM179" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AN179" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP179" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ179" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AR179" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AU179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX179" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY179" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ179" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA179" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB179" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC179" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD179" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE179" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF179" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG179" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH179" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="BI179" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BJ179" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BK179" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BL179" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BM179" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BN179" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO179" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BP179" t="n">
+        <v>1.33</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP179"/>
+  <dimension ref="A1:BP181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.7</v>
@@ -1568,7 +1568,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
@@ -5492,7 +5492,7 @@
         <v>2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR23" t="n">
         <v>2.61</v>
@@ -5925,7 +5925,7 @@
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ25" t="n">
         <v>1.67</v>
@@ -7672,7 +7672,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR33" t="n">
         <v>2.49</v>
@@ -8977,7 +8977,7 @@
         <v>1</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ39" t="n">
         <v>0.75</v>
@@ -9634,7 +9634,7 @@
         <v>2</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR42" t="n">
         <v>1.28</v>
@@ -9849,7 +9849,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.75</v>
@@ -10939,7 +10939,7 @@
         <v>2</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ48" t="n">
         <v>1</v>
@@ -11378,7 +11378,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR50" t="n">
         <v>1.68</v>
@@ -13991,10 +13991,10 @@
         <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR62" t="n">
         <v>1.8</v>
@@ -14212,7 +14212,7 @@
         <v>2</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR63" t="n">
         <v>1.45</v>
@@ -15953,7 +15953,7 @@
         <v>0.33</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.11</v>
@@ -19662,7 +19662,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR88" t="n">
         <v>1.28</v>
@@ -19877,7 +19877,7 @@
         <v>0</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.11</v>
@@ -20095,7 +20095,7 @@
         <v>1.25</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.7</v>
@@ -20531,7 +20531,7 @@
         <v>1.25</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ92" t="n">
         <v>0.75</v>
@@ -20970,7 +20970,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR94" t="n">
         <v>2.52</v>
@@ -21406,7 +21406,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR96" t="n">
         <v>1.79</v>
@@ -23147,7 +23147,7 @@
         <v>1.2</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.44</v>
@@ -24894,7 +24894,7 @@
         <v>2</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR112" t="n">
         <v>1.39</v>
@@ -25112,7 +25112,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR113" t="n">
         <v>1.77</v>
@@ -25981,7 +25981,7 @@
         <v>1.4</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ117" t="n">
         <v>1.13</v>
@@ -27943,7 +27943,7 @@
         <v>0.83</v>
       </c>
       <c r="AP126" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ126" t="n">
         <v>1.11</v>
@@ -29251,7 +29251,7 @@
         <v>1.33</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.67</v>
@@ -30126,7 +30126,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR136" t="n">
         <v>1.45</v>
@@ -30780,7 +30780,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ139" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR139" t="n">
         <v>1.7</v>
@@ -31431,7 +31431,7 @@
         <v>0.83</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.75</v>
@@ -33614,7 +33614,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AR152" t="n">
         <v>1.61</v>
@@ -34050,7 +34050,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="AR154" t="n">
         <v>1.4</v>
@@ -34265,7 +34265,7 @@
         <v>1.14</v>
       </c>
       <c r="AP155" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ155" t="n">
         <v>0.89</v>
@@ -36227,7 +36227,7 @@
         <v>1.14</v>
       </c>
       <c r="AP164" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AQ164" t="n">
         <v>1.13</v>
@@ -37986,7 +37986,7 @@
         <v>2.78</v>
       </c>
       <c r="AU172" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV172" t="n">
         <v>3</v>
@@ -37995,13 +37995,13 @@
         <v>11</v>
       </c>
       <c r="AX172" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY172" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ172" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA172" t="n">
         <v>14</v>
@@ -38210,13 +38210,13 @@
         <v>2</v>
       </c>
       <c r="AW173" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AX173" t="n">
         <v>3</v>
       </c>
       <c r="AY173" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AZ173" t="n">
         <v>5</v>
@@ -38425,19 +38425,19 @@
         <v>5</v>
       </c>
       <c r="AV174" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW174" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX174" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY174" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ174" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BA174" t="n">
         <v>1</v>
@@ -38640,7 +38640,7 @@
         <v>2.63</v>
       </c>
       <c r="AU175" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AV175" t="n">
         <v>4</v>
@@ -38649,13 +38649,13 @@
         <v>19</v>
       </c>
       <c r="AX175" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY175" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ175" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA175" t="n">
         <v>13</v>
@@ -38764,7 +38764,7 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>['19', '44']</t>
+          <t>['18', '44']</t>
         </is>
       </c>
       <c r="Q176" t="n">
@@ -39076,22 +39076,22 @@
         <v>3.02</v>
       </c>
       <c r="AU177" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AV177" t="n">
         <v>3</v>
       </c>
       <c r="AW177" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX177" t="n">
         <v>12</v>
       </c>
-      <c r="AX177" t="n">
-        <v>11</v>
-      </c>
       <c r="AY177" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ177" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA177" t="n">
         <v>6</v>
@@ -39576,6 +39576,442 @@
       </c>
       <c r="BP179" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="n">
+        <v>7845519</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="n">
+        <v>45894.8125</v>
+      </c>
+      <c r="F180" t="n">
+        <v>18</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>CSA</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>1</v>
+      </c>
+      <c r="M180" t="n">
+        <v>2</v>
+      </c>
+      <c r="N180" t="n">
+        <v>3</v>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>['90+6']</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>['57', '81']</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="R180" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S180" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="T180" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U180" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V180" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="W180" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X180" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW180" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY180" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ180" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA180" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB180" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC180" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD180" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BE180" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF180" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG180" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BH180" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BI180" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ180" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BK180" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BL180" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BM180" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BN180" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BO180" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BP180" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="n">
+        <v>7845513</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="n">
+        <v>45894.8125</v>
+      </c>
+      <c r="F181" t="n">
+        <v>18</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+      <c r="I181" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>1</v>
+      </c>
+      <c r="L181" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="n">
+        <v>1</v>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>['1']</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R181" t="n">
+        <v>2</v>
+      </c>
+      <c r="S181" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="T181" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U181" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V181" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W181" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X181" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX181" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY181" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ181" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA181" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE181" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF181" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG181" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH181" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BI181" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ181" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK181" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL181" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM181" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BN181" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BO181" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BP181" t="n">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -39636,7 +39636,7 @@
       </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>['57', '81']</t>
+          <t>['58', '80']</t>
         </is>
       </c>
       <c r="Q180" t="n">
@@ -39730,22 +39730,22 @@
         <v>3.49</v>
       </c>
       <c r="AU180" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV180" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW180" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AX180" t="n">
         <v>2</v>
       </c>
       <c r="AY180" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AZ180" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BA180" t="n">
         <v>10</v>
@@ -39951,19 +39951,19 @@
         <v>2</v>
       </c>
       <c r="AV181" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW181" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AX181" t="n">
         <v>5</v>
       </c>
       <c r="AY181" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AZ181" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA181" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -39300,16 +39300,16 @@
         <v>8</v>
       </c>
       <c r="AW178" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX178" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY178" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ178" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BA178" t="n">
         <v>4</v>
@@ -39512,19 +39512,19 @@
         <v>2.52</v>
       </c>
       <c r="AU179" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV179" t="n">
         <v>4</v>
       </c>
       <c r="AW179" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AX179" t="n">
         <v>3</v>
       </c>
       <c r="AY179" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AZ179" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP181"/>
+  <dimension ref="A1:BP191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3091,10 +3091,10 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3527,10 +3527,10 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3745,10 +3745,10 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR15" t="n">
         <v>0</v>
@@ -3963,10 +3963,10 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4181,10 +4181,10 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4399,10 +4399,10 @@
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4617,10 +4617,10 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -5053,10 +5053,10 @@
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.78</v>
@@ -5710,7 +5710,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR24" t="n">
         <v>0.96</v>
@@ -6364,7 +6364,7 @@
         <v>2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR27" t="n">
         <v>1</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.89</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.7</v>
@@ -7236,7 +7236,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR31" t="n">
         <v>0.73</v>
@@ -7451,10 +7451,10 @@
         <v>3</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR32" t="n">
         <v>1.66</v>
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ33" t="n">
         <v>0.7</v>
@@ -7887,10 +7887,10 @@
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR34" t="n">
         <v>1.38</v>
@@ -8105,7 +8105,7 @@
         <v>1</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.7</v>
@@ -8323,10 +8323,10 @@
         <v>1</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR36" t="n">
         <v>1.21</v>
@@ -8541,10 +8541,10 @@
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR37" t="n">
         <v>1.25</v>
@@ -8759,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ38" t="n">
         <v>1.56</v>
@@ -8980,7 +8980,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR39" t="n">
         <v>1.37</v>
@@ -9198,7 +9198,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR40" t="n">
         <v>1.51</v>
@@ -9416,7 +9416,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR41" t="n">
         <v>1.73</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.7</v>
@@ -9852,7 +9852,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR43" t="n">
         <v>1.92</v>
@@ -10067,7 +10067,7 @@
         <v>1</v>
       </c>
       <c r="AP44" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ44" t="n">
         <v>1.3</v>
@@ -10285,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ45" t="n">
         <v>0.89</v>
@@ -10724,7 +10724,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR47" t="n">
         <v>0.91</v>
@@ -11596,7 +11596,7 @@
         <v>2</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR51" t="n">
         <v>1.33</v>
@@ -11811,10 +11811,10 @@
         <v>0.5</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR52" t="n">
         <v>1.58</v>
@@ -12029,10 +12029,10 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR53" t="n">
         <v>1.25</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.67</v>
@@ -12465,7 +12465,7 @@
         <v>1</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ55" t="n">
         <v>1.56</v>
@@ -12686,7 +12686,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR56" t="n">
         <v>1.33</v>
@@ -12901,10 +12901,10 @@
         <v>0.5</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR57" t="n">
         <v>2.71</v>
@@ -13122,7 +13122,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR58" t="n">
         <v>1.16</v>
@@ -13340,7 +13340,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR59" t="n">
         <v>1.72</v>
@@ -13555,10 +13555,10 @@
         <v>2</v>
       </c>
       <c r="AP60" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR60" t="n">
         <v>2.4</v>
@@ -13773,7 +13773,7 @@
         <v>0.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ61" t="n">
         <v>0.7</v>
@@ -14209,7 +14209,7 @@
         <v>2.33</v>
       </c>
       <c r="AP63" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.78</v>
@@ -14430,7 +14430,7 @@
         <v>2</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR64" t="n">
         <v>1.23</v>
@@ -14866,7 +14866,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR66" t="n">
         <v>1.21</v>
@@ -15081,7 +15081,7 @@
         <v>0.67</v>
       </c>
       <c r="AP67" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ67" t="n">
         <v>0.3</v>
@@ -15517,7 +15517,7 @@
         <v>1.33</v>
       </c>
       <c r="AP69" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ69" t="n">
         <v>1</v>
@@ -15735,10 +15735,10 @@
         <v>2</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR70" t="n">
         <v>1.26</v>
@@ -15956,7 +15956,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR71" t="n">
         <v>1.82</v>
@@ -16171,7 +16171,7 @@
         <v>1</v>
       </c>
       <c r="AP72" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ72" t="n">
         <v>1.67</v>
@@ -16392,7 +16392,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR73" t="n">
         <v>1.45</v>
@@ -16610,7 +16610,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR74" t="n">
         <v>0.91</v>
@@ -16825,10 +16825,10 @@
         <v>0</v>
       </c>
       <c r="AP75" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR75" t="n">
         <v>1.4</v>
@@ -17043,7 +17043,7 @@
         <v>1.67</v>
       </c>
       <c r="AP76" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.56</v>
@@ -17261,7 +17261,7 @@
         <v>0.67</v>
       </c>
       <c r="AP77" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ77" t="n">
         <v>0.7</v>
@@ -17479,10 +17479,10 @@
         <v>2</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR78" t="n">
         <v>2.41</v>
@@ -17700,7 +17700,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR79" t="n">
         <v>1.78</v>
@@ -17915,7 +17915,7 @@
         <v>0.33</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.89</v>
@@ -18136,7 +18136,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR81" t="n">
         <v>1.51</v>
@@ -18351,7 +18351,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.3</v>
@@ -18572,7 +18572,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR83" t="n">
         <v>1.29</v>
@@ -18787,10 +18787,10 @@
         <v>0</v>
       </c>
       <c r="AP84" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR84" t="n">
         <v>1.57</v>
@@ -19008,7 +19008,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR85" t="n">
         <v>1.31</v>
@@ -19226,7 +19226,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR86" t="n">
         <v>1.5</v>
@@ -19441,7 +19441,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.3</v>
@@ -19659,7 +19659,7 @@
         <v>0.25</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ88" t="n">
         <v>0.7</v>
@@ -19880,7 +19880,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR89" t="n">
         <v>1.81</v>
@@ -20313,7 +20313,7 @@
         <v>1.25</v>
       </c>
       <c r="AP91" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ91" t="n">
         <v>1</v>
@@ -20534,7 +20534,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR92" t="n">
         <v>1.69</v>
@@ -20752,7 +20752,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR93" t="n">
         <v>1.52</v>
@@ -20967,7 +20967,7 @@
         <v>2.5</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ94" t="n">
         <v>1.78</v>
@@ -21621,7 +21621,7 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ97" t="n">
         <v>0.89</v>
@@ -21839,7 +21839,7 @@
         <v>1</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.67</v>
@@ -22060,7 +22060,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR99" t="n">
         <v>1.19</v>
@@ -22275,7 +22275,7 @@
         <v>1.25</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ100" t="n">
         <v>1.56</v>
@@ -22496,7 +22496,7 @@
         <v>2</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR101" t="n">
         <v>1.4</v>
@@ -22711,7 +22711,7 @@
         <v>1</v>
       </c>
       <c r="AP102" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.7</v>
@@ -22932,7 +22932,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR103" t="n">
         <v>1.33</v>
@@ -23150,7 +23150,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR104" t="n">
         <v>1.71</v>
@@ -23365,7 +23365,7 @@
         <v>1.4</v>
       </c>
       <c r="AP105" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.3</v>
@@ -23586,7 +23586,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR106" t="n">
         <v>1.53</v>
@@ -23801,10 +23801,10 @@
         <v>0</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR107" t="n">
         <v>1.54</v>
@@ -24019,7 +24019,7 @@
         <v>1</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ108" t="n">
         <v>1</v>
@@ -24237,10 +24237,10 @@
         <v>0.4</v>
       </c>
       <c r="AP109" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR109" t="n">
         <v>1.16</v>
@@ -24455,7 +24455,7 @@
         <v>0.6</v>
       </c>
       <c r="AP110" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.3</v>
@@ -24676,7 +24676,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR111" t="n">
         <v>1.46</v>
@@ -25327,7 +25327,7 @@
         <v>1.33</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ114" t="n">
         <v>1.3</v>
@@ -25545,7 +25545,7 @@
         <v>1.4</v>
       </c>
       <c r="AP115" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.89</v>
@@ -25766,7 +25766,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR116" t="n">
         <v>1.53</v>
@@ -25984,7 +25984,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR117" t="n">
         <v>1.63</v>
@@ -26635,7 +26635,7 @@
         <v>1</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ120" t="n">
         <v>1.56</v>
@@ -26856,7 +26856,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR121" t="n">
         <v>1.34</v>
@@ -27074,7 +27074,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR122" t="n">
         <v>1.43</v>
@@ -27289,7 +27289,7 @@
         <v>1</v>
       </c>
       <c r="AP123" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ123" t="n">
         <v>1</v>
@@ -27507,7 +27507,7 @@
         <v>1</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.7</v>
@@ -27728,7 +27728,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR125" t="n">
         <v>1.53</v>
@@ -27946,7 +27946,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR126" t="n">
         <v>1.91</v>
@@ -28161,7 +28161,7 @@
         <v>0.5</v>
       </c>
       <c r="AP127" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ127" t="n">
         <v>0.3</v>
@@ -28379,10 +28379,10 @@
         <v>1.33</v>
       </c>
       <c r="AP128" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ128" t="n">
         <v>1.56</v>
-      </c>
-      <c r="AQ128" t="n">
-        <v>1.75</v>
       </c>
       <c r="AR128" t="n">
         <v>1.32</v>
@@ -28597,10 +28597,10 @@
         <v>0.17</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR129" t="n">
         <v>1.17</v>
@@ -28815,10 +28815,10 @@
         <v>1.5</v>
       </c>
       <c r="AP130" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR130" t="n">
         <v>1.45</v>
@@ -29033,10 +29033,10 @@
         <v>1</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR131" t="n">
         <v>1.45</v>
@@ -29469,7 +29469,7 @@
         <v>1.57</v>
       </c>
       <c r="AP133" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.3</v>
@@ -29908,7 +29908,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR135" t="n">
         <v>1.59</v>
@@ -30562,7 +30562,7 @@
         <v>2</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR138" t="n">
         <v>1.37</v>
@@ -30995,7 +30995,7 @@
         <v>1</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ140" t="n">
         <v>1</v>
@@ -31434,7 +31434,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR142" t="n">
         <v>2.05</v>
@@ -31649,10 +31649,10 @@
         <v>0.83</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR143" t="n">
         <v>1.39</v>
@@ -31867,10 +31867,10 @@
         <v>0.86</v>
       </c>
       <c r="AP144" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR144" t="n">
         <v>1.63</v>
@@ -32303,7 +32303,7 @@
         <v>0.86</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.7</v>
@@ -32521,10 +32521,10 @@
         <v>1.29</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR147" t="n">
         <v>1.28</v>
@@ -32739,10 +32739,10 @@
         <v>0.57</v>
       </c>
       <c r="AP148" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ148" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR148" t="n">
         <v>1.51</v>
@@ -32957,10 +32957,10 @@
         <v>0</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ149" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR149" t="n">
         <v>1.35</v>
@@ -33175,7 +33175,7 @@
         <v>0.86</v>
       </c>
       <c r="AP150" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ150" t="n">
         <v>0.7</v>
@@ -33396,7 +33396,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR151" t="n">
         <v>1.41</v>
@@ -34701,7 +34701,7 @@
         <v>1.57</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AQ157" t="n">
         <v>1.56</v>
@@ -34919,7 +34919,7 @@
         <v>0.38</v>
       </c>
       <c r="AP158" t="n">
-        <v>2.13</v>
+        <v>2.22</v>
       </c>
       <c r="AQ158" t="n">
         <v>0.3</v>
@@ -35140,7 +35140,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AR159" t="n">
         <v>1.31</v>
@@ -35358,7 +35358,7 @@
         <v>2</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR160" t="n">
         <v>1.35</v>
@@ -35791,10 +35791,10 @@
         <v>0.13</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AQ162" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="AR162" t="n">
         <v>1.39</v>
@@ -36009,10 +36009,10 @@
         <v>0.5</v>
       </c>
       <c r="AP163" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AQ163" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AR163" t="n">
         <v>2.36</v>
@@ -36230,7 +36230,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ164" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AR164" t="n">
         <v>2.07</v>
@@ -36445,10 +36445,10 @@
         <v>0.86</v>
       </c>
       <c r="AP165" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AR165" t="n">
         <v>1.62</v>
@@ -36666,7 +36666,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AR166" t="n">
         <v>1.79</v>
@@ -36881,10 +36881,10 @@
         <v>1.43</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="AR167" t="n">
         <v>1.31</v>
@@ -37099,7 +37099,7 @@
         <v>0.88</v>
       </c>
       <c r="AP168" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.7</v>
@@ -37317,7 +37317,7 @@
         <v>0.75</v>
       </c>
       <c r="AP169" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AQ169" t="n">
         <v>0.7</v>
@@ -37535,10 +37535,10 @@
         <v>1.5</v>
       </c>
       <c r="AP170" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR170" t="n">
         <v>1.43</v>
@@ -37753,10 +37753,10 @@
         <v>0.71</v>
       </c>
       <c r="AP171" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AQ171" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AR171" t="n">
         <v>1.32</v>
@@ -40012,6 +40012,2186 @@
       </c>
       <c r="BP181" t="n">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="n">
+        <v>7845526</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="n">
+        <v>45899.70833333334</v>
+      </c>
+      <c r="F182" t="n">
+        <v>19</v>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Maringá</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Caxias</t>
+        </is>
+      </c>
+      <c r="I182" t="n">
+        <v>1</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>1</v>
+      </c>
+      <c r="L182" t="n">
+        <v>3</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="n">
+        <v>3</v>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>['7', '64', '75']</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="R182" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="S182" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="T182" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U182" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V182" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W182" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X182" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA182" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AG182" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AH182" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI182" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK182" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM182" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AN182" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO182" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AP182" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ182" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR182" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AS182" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT182" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="AU182" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW182" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX182" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY182" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ182" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA182" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB182" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC182" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD182" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BE182" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF182" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BG182" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BH182" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="BI182" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BJ182" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BK182" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BL182" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BM182" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BN182" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BO182" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BP182" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="n">
+        <v>7845528</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="n">
+        <v>45899.70833333334</v>
+      </c>
+      <c r="F183" t="n">
+        <v>19</v>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>CSA</t>
+        </is>
+      </c>
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>2</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="n">
+        <v>2</v>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>['49', '88']</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R183" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S183" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T183" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="U183" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V183" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W183" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X183" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AA183" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI183" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AK183" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM183" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN183" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO183" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP183" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ183" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR183" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS183" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AT183" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AU183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV183" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW183" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX183" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY183" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ183" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA183" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB183" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC183" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD183" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BE183" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF183" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG183" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH183" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI183" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ183" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK183" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="BL183" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BM183" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN183" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO183" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BP183" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="n">
+        <v>7845527</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="n">
+        <v>45899.70833333334</v>
+      </c>
+      <c r="F184" t="n">
+        <v>19</v>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Ypiranga Erechim</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Figueirense</t>
+        </is>
+      </c>
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" t="n">
+        <v>1</v>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>['78']</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="R184" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S184" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="T184" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U184" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="V184" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W184" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X184" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA184" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF184" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AG184" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH184" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI184" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ184" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK184" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM184" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AN184" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO184" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AP184" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AQ184" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR184" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS184" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT184" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU184" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV184" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW184" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX184" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY184" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ184" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA184" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB184" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC184" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD184" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BE184" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF184" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BG184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH184" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI184" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ184" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BK184" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BL184" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM184" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BN184" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BO184" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BP184" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="n">
+        <v>7845525</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="n">
+        <v>45899.70833333334</v>
+      </c>
+      <c r="F185" t="n">
+        <v>19</v>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Anápolis</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Botafogo PB</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="n">
+        <v>2</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" t="n">
+        <v>2</v>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>['-1', '-1']</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="R185" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S185" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="T185" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U185" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="V185" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W185" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X185" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z185" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA185" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AC185" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG185" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK185" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM185" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN185" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO185" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP185" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AQ185" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AR185" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS185" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT185" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AU185" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV185" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW185" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX185" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY185" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ185" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA185" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB185" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC185" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD185" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BE185" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF185" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BG185" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BH185" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="BI185" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BJ185" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BK185" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BL185" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BM185" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BN185" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BO185" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BP185" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="n">
+        <v>7845529</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="n">
+        <v>45899.70833333334</v>
+      </c>
+      <c r="F186" t="n">
+        <v>19</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Floresta</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>2</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="n">
+        <v>2</v>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>['71', '90+3']</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R186" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="S186" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="T186" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U186" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V186" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W186" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X186" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z186" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AA186" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB186" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC186" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD186" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF186" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG186" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AH186" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AI186" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AJ186" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AK186" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM186" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AN186" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AO186" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP186" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AQ186" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR186" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS186" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AT186" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU186" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW186" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX186" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY186" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ186" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA186" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB186" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC186" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD186" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BE186" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF186" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BG186" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH186" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI186" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BJ186" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BK186" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL186" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BM186" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BN186" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO186" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP186" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="n">
+        <v>7845523</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="n">
+        <v>45899.70833333334</v>
+      </c>
+      <c r="F187" t="n">
+        <v>19</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Retrô</t>
+        </is>
+      </c>
+      <c r="I187" t="n">
+        <v>1</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>1</v>
+      </c>
+      <c r="L187" t="n">
+        <v>1</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="n">
+        <v>1</v>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R187" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S187" t="n">
+        <v>6</v>
+      </c>
+      <c r="T187" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="U187" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="V187" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="W187" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X187" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AA187" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AG187" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH187" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI187" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ187" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK187" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM187" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AN187" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO187" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AP187" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ187" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR187" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AS187" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AT187" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AU187" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV187" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW187" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX187" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY187" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ187" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA187" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB187" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC187" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD187" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BE187" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF187" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG187" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH187" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BI187" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ187" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BK187" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BL187" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM187" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN187" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO187" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BP187" t="n">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="n">
+        <v>7845522</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="n">
+        <v>45899.70833333334</v>
+      </c>
+      <c r="F188" t="n">
+        <v>19</v>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="n">
+        <v>1</v>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>['59']</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R188" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S188" t="n">
+        <v>4</v>
+      </c>
+      <c r="T188" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U188" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V188" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="W188" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X188" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI188" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AK188" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM188" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AN188" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO188" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AP188" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ188" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR188" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS188" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AT188" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AU188" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW188" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX188" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY188" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ188" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA188" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB188" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC188" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD188" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BE188" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF188" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG188" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH188" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BI188" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ188" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BK188" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL188" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BM188" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BN188" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BO188" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BP188" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="n">
+        <v>7845521</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="n">
+        <v>45899.70833333334</v>
+      </c>
+      <c r="F189" t="n">
+        <v>19</v>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Ituano</t>
+        </is>
+      </c>
+      <c r="I189" t="n">
+        <v>1</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>1</v>
+      </c>
+      <c r="L189" t="n">
+        <v>3</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="n">
+        <v>3</v>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>['25', '90+2', '90+5']</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R189" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S189" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T189" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U189" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V189" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W189" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X189" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y189" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z189" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA189" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB189" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC189" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD189" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AE189" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AF189" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AG189" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH189" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ189" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AK189" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM189" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN189" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO189" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AP189" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ189" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR189" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS189" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT189" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU189" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV189" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW189" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX189" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY189" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ189" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA189" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB189" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC189" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD189" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BE189" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF189" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG189" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH189" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="BI189" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BJ189" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BK189" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BL189" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BM189" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BN189" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BO189" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BP189" t="n">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="n">
+        <v>7845524</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="n">
+        <v>45899.70833333334</v>
+      </c>
+      <c r="F190" t="n">
+        <v>19</v>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Tombense</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>1</v>
+      </c>
+      <c r="K190" t="n">
+        <v>1</v>
+      </c>
+      <c r="L190" t="n">
+        <v>2</v>
+      </c>
+      <c r="M190" t="n">
+        <v>2</v>
+      </c>
+      <c r="N190" t="n">
+        <v>4</v>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>['76', '85']</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>['28', '72']</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R190" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="S190" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T190" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U190" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V190" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="W190" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X190" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y190" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z190" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="AA190" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AB190" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC190" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD190" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AE190" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF190" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AG190" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH190" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI190" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ190" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AK190" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM190" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN190" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO190" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AP190" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ190" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AR190" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AS190" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT190" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU190" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV190" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW190" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX190" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY190" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ190" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA190" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB190" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC190" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD190" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BE190" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF190" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BG190" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH190" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI190" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ190" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK190" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BL190" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM190" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BN190" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO190" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP190" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="n">
+        <v>7845530</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="n">
+        <v>45899.70833333334</v>
+      </c>
+      <c r="F191" t="n">
+        <v>19</v>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Itabaiana</t>
+        </is>
+      </c>
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="n">
+        <v>1</v>
+      </c>
+      <c r="K191" t="n">
+        <v>1</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" t="n">
+        <v>1</v>
+      </c>
+      <c r="N191" t="n">
+        <v>1</v>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>['45+6']</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R191" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S191" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="T191" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U191" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V191" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="W191" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X191" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y191" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z191" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AH191" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AI191" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AJ191" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AK191" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM191" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AN191" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AO191" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AP191" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AQ191" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AR191" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS191" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AT191" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AU191" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV191" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW191" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX191" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY191" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ191" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA191" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB191" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC191" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD191" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE191" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF191" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG191" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BH191" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BI191" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BJ191" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="BK191" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BL191" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BM191" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BN191" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BO191" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BP191" t="n">
+        <v>1.59</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -40702,13 +40702,13 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
       </c>
       <c r="K185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L185" t="n">
         <v>2</v>
@@ -40721,7 +40721,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['4', '9011']</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -40820,7 +40820,7 @@
         <v>2.71</v>
       </c>
       <c r="AU185" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV185" t="n">
         <v>3</v>
@@ -40832,7 +40832,7 @@
         <v>13</v>
       </c>
       <c r="AY185" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ185" t="n">
         <v>16</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -40721,7 +40721,7 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>['4', '9011']</t>
+          <t>['4', '90+11']</t>
         </is>
       </c>
       <c r="P185" t="inlineStr">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -40169,19 +40169,19 @@
         <v>7</v>
       </c>
       <c r="AV182" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW182" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX182" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY182" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ182" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA182" t="n">
         <v>4</v>
@@ -40384,22 +40384,22 @@
         <v>2.46</v>
       </c>
       <c r="AU183" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV183" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AW183" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AX183" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY183" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ183" t="n">
         <v>8</v>
-      </c>
-      <c r="AZ183" t="n">
-        <v>5</v>
       </c>
       <c r="BA183" t="n">
         <v>5</v>
@@ -40602,22 +40602,22 @@
         <v>2.51</v>
       </c>
       <c r="AU184" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV184" t="n">
         <v>4</v>
       </c>
       <c r="AW184" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AX184" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY184" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ184" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA184" t="n">
         <v>11</v>
@@ -40820,22 +40820,22 @@
         <v>2.71</v>
       </c>
       <c r="AU185" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV185" t="n">
         <v>3</v>
       </c>
       <c r="AW185" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AX185" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY185" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AZ185" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA185" t="n">
         <v>4</v>
@@ -41038,22 +41038,22 @@
         <v>2.7</v>
       </c>
       <c r="AU186" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV186" t="n">
         <v>0</v>
       </c>
       <c r="AW186" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY186" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA186" t="n">
         <v>7</v>
@@ -41262,16 +41262,16 @@
         <v>1</v>
       </c>
       <c r="AW187" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX187" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY187" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ187" t="n">
         <v>6</v>
-      </c>
-      <c r="AY187" t="n">
-        <v>17</v>
-      </c>
-      <c r="AZ187" t="n">
-        <v>7</v>
       </c>
       <c r="BA187" t="n">
         <v>6</v>
@@ -41477,19 +41477,19 @@
         <v>3</v>
       </c>
       <c r="AV188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW188" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX188" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY188" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ188" t="n">
         <v>6</v>
-      </c>
-      <c r="AX188" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY188" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ188" t="n">
-        <v>4</v>
       </c>
       <c r="BA188" t="n">
         <v>7</v>
@@ -41695,19 +41695,19 @@
         <v>10</v>
       </c>
       <c r="AV189" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AW189" t="n">
         <v>12</v>
       </c>
       <c r="AX189" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY189" t="n">
         <v>22</v>
       </c>
       <c r="AZ189" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA189" t="n">
         <v>7</v>
@@ -41916,16 +41916,16 @@
         <v>8</v>
       </c>
       <c r="AW190" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX190" t="n">
         <v>9</v>
       </c>
-      <c r="AX190" t="n">
-        <v>5</v>
-      </c>
       <c r="AY190" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AZ190" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="BA190" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -42134,13 +42134,13 @@
         <v>7</v>
       </c>
       <c r="AW191" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX191" t="n">
         <v>11</v>
       </c>
       <c r="AY191" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ191" t="n">
         <v>18</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -2004,7 +2004,7 @@
         <v>2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.11</v>
@@ -5928,7 +5928,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AR25" t="n">
         <v>1.88</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.89</v>
@@ -10285,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.3</v>
@@ -12468,7 +12468,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AR55" t="n">
         <v>1.22</v>
@@ -15953,7 +15953,7 @@
         <v>2</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.56</v>
@@ -16174,7 +16174,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AR72" t="n">
         <v>1.48</v>
@@ -19441,7 +19441,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.3</v>
@@ -21842,7 +21842,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AR98" t="n">
         <v>1.45</v>
@@ -24019,7 +24019,7 @@
         <v>0.4</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ108" t="n">
         <v>1</v>
@@ -26420,7 +26420,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AR119" t="n">
         <v>1.75</v>
@@ -28597,7 +28597,7 @@
         <v>0.17</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.4</v>
@@ -29472,7 +29472,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AR133" t="n">
         <v>1.59</v>
@@ -32957,7 +32957,7 @@
         <v>0</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.4</v>
@@ -34486,7 +34486,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AR156" t="n">
         <v>1.55</v>
@@ -36663,7 +36663,7 @@
         <v>1.43</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ166" t="n">
         <v>1.4</v>
@@ -39500,7 +39500,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AR179" t="n">
         <v>1.77</v>
@@ -41677,7 +41677,7 @@
         <v>0.75</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AQ189" t="n">
         <v>0.67</v>
@@ -42782,31 +42782,31 @@
         <v>2.5</v>
       </c>
       <c r="AU194" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AV194" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AW194" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="AX194" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="AY194" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AZ194" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA194" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BB194" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="BC194" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BD194" t="n">
         <v>0</v>
@@ -42885,19 +42885,19 @@
         <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
       </c>
       <c r="P195" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22']</t>
         </is>
       </c>
       <c r="Q195" t="n">
@@ -42985,10 +42985,10 @@
         <v>1.89</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AR195" t="n">
         <v>1.3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP195"/>
+  <dimension ref="A1:BP199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -2655,10 +2655,10 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.89</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.4</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.67</v>
@@ -4402,7 +4402,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ23" t="n">
         <v>1</v>
@@ -6364,7 +6364,7 @@
         <v>2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR27" t="n">
         <v>1</v>
@@ -7018,7 +7018,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR30" t="n">
         <v>1.85</v>
@@ -7233,10 +7233,10 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR31" t="n">
         <v>0.73</v>
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.7</v>
@@ -8977,10 +8977,10 @@
         <v>1</v>
       </c>
       <c r="AP39" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR39" t="n">
         <v>1.45</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.7</v>
@@ -9852,7 +9852,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR43" t="n">
         <v>1.92</v>
@@ -10506,7 +10506,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR46" t="n">
         <v>1.03</v>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.4</v>
@@ -10939,7 +10939,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.3</v>
@@ -11814,7 +11814,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR52" t="n">
         <v>1.25</v>
@@ -12247,10 +12247,10 @@
         <v>1</v>
       </c>
       <c r="AP54" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR54" t="n">
         <v>1.23</v>
@@ -13991,7 +13991,7 @@
         <v>2.33</v>
       </c>
       <c r="AP62" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.7</v>
@@ -14645,7 +14645,7 @@
         <v>1.67</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.3</v>
@@ -15084,7 +15084,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR67" t="n">
         <v>1.47</v>
@@ -15956,7 +15956,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR71" t="n">
         <v>1.26</v>
@@ -16392,7 +16392,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR73" t="n">
         <v>1.45</v>
@@ -16607,7 +16607,7 @@
         <v>2.33</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.4</v>
@@ -17046,7 +17046,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR76" t="n">
         <v>2.25</v>
@@ -17915,7 +17915,7 @@
         <v>0.33</v>
       </c>
       <c r="AP80" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.89</v>
@@ -18351,7 +18351,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.3</v>
@@ -18572,7 +18572,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR83" t="n">
         <v>1.29</v>
@@ -19223,7 +19223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ86" t="n">
         <v>1</v>
@@ -20098,7 +20098,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR90" t="n">
         <v>1.87</v>
@@ -20313,7 +20313,7 @@
         <v>1.25</v>
       </c>
       <c r="AP91" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ91" t="n">
         <v>1</v>
@@ -22057,7 +22057,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ99" t="n">
         <v>1</v>
@@ -22278,7 +22278,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR100" t="n">
         <v>1.21</v>
@@ -22711,10 +22711,10 @@
         <v>1</v>
       </c>
       <c r="AP102" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR102" t="n">
         <v>1.38</v>
@@ -23583,10 +23583,10 @@
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR106" t="n">
         <v>1.53</v>
@@ -24455,7 +24455,7 @@
         <v>0.6</v>
       </c>
       <c r="AP110" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.3</v>
@@ -24676,7 +24676,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR111" t="n">
         <v>1.46</v>
@@ -26199,7 +26199,7 @@
         <v>0.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.7</v>
@@ -26856,7 +26856,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR121" t="n">
         <v>2.47</v>
@@ -27507,7 +27507,7 @@
         <v>0</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.4</v>
@@ -27725,10 +27725,10 @@
         <v>1</v>
       </c>
       <c r="AP125" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR125" t="n">
         <v>1.29</v>
@@ -28382,7 +28382,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR128" t="n">
         <v>1.32</v>
@@ -28818,7 +28818,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR130" t="n">
         <v>1.45</v>
@@ -29033,7 +29033,7 @@
         <v>1.5</v>
       </c>
       <c r="AP131" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.27</v>
@@ -29905,7 +29905,7 @@
         <v>1</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ135" t="n">
         <v>0.67</v>
@@ -30341,7 +30341,7 @@
         <v>2.17</v>
       </c>
       <c r="AP137" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.7</v>
@@ -31216,7 +31216,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR141" t="n">
         <v>1.59</v>
@@ -31649,10 +31649,10 @@
         <v>0.83</v>
       </c>
       <c r="AP143" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR143" t="n">
         <v>1.39</v>
@@ -32088,7 +32088,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR145" t="n">
         <v>2.4</v>
@@ -32739,7 +32739,7 @@
         <v>0.57</v>
       </c>
       <c r="AP148" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ148" t="n">
         <v>0.4</v>
@@ -33829,7 +33829,7 @@
         <v>1.5</v>
       </c>
       <c r="AP153" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.3</v>
@@ -34483,7 +34483,7 @@
         <v>1.57</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.8</v>
@@ -34922,7 +34922,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR158" t="n">
         <v>1.46</v>
@@ -35140,7 +35140,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR159" t="n">
         <v>1.31</v>
@@ -35791,7 +35791,7 @@
         <v>0.13</v>
       </c>
       <c r="AP162" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ162" t="n">
         <v>0.4</v>
@@ -36448,7 +36448,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR165" t="n">
         <v>1.62</v>
@@ -37099,7 +37099,7 @@
         <v>0.75</v>
       </c>
       <c r="AP168" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.7</v>
@@ -37320,7 +37320,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ169" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR169" t="n">
         <v>2.24</v>
@@ -37971,10 +37971,10 @@
         <v>1.38</v>
       </c>
       <c r="AP172" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AR172" t="n">
         <v>1.44</v>
@@ -38410,7 +38410,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AR174" t="n">
         <v>1.96</v>
@@ -38843,7 +38843,7 @@
         <v>0.67</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.7</v>
@@ -40151,7 +40151,7 @@
         <v>1.13</v>
       </c>
       <c r="AP182" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AQ182" t="n">
         <v>1</v>
@@ -40369,7 +40369,7 @@
         <v>1.63</v>
       </c>
       <c r="AP183" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.4</v>
@@ -40808,7 +40808,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AR185" t="n">
         <v>1.49</v>
@@ -41898,7 +41898,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AR190" t="n">
         <v>1.24</v>
@@ -42331,10 +42331,10 @@
         <v>1.89</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AR192" t="n">
         <v>1.49</v>
@@ -42549,10 +42549,10 @@
         <v>1.58</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AR193" t="n">
         <v>1.58</v>
@@ -42767,10 +42767,10 @@
         <v>1.95</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AR194" t="n">
         <v>1.17</v>
@@ -42985,10 +42985,10 @@
         <v>1.89</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AR195" t="n">
         <v>1.3</v>
@@ -43064,6 +43064,878 @@
       </c>
       <c r="BP195" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="n">
+        <v>8260249</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="n">
+        <v>45913.70833333334</v>
+      </c>
+      <c r="F196" t="n">
+        <v>2</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>2</v>
+      </c>
+      <c r="K196" t="n">
+        <v>2</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" t="n">
+        <v>2</v>
+      </c>
+      <c r="N196" t="n">
+        <v>2</v>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>['22', '24']</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R196" t="n">
+        <v>2</v>
+      </c>
+      <c r="S196" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T196" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U196" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V196" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W196" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X196" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Y196" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z196" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB196" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AC196" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD196" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE196" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF196" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AG196" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH196" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI196" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ196" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AK196" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL196" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM196" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN196" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP196" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ196" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR196" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AS196" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AT196" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU196" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV196" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW196" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY196" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ196" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA196" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB196" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC196" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD196" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BE196" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF196" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG196" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH196" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI196" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BJ196" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BK196" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BL196" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BM196" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BN196" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BO196" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BP196" t="n">
+        <v>1.74</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="n">
+        <v>8260181</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="n">
+        <v>45913.8125</v>
+      </c>
+      <c r="F197" t="n">
+        <v>2</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Caxias</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R197" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S197" t="n">
+        <v>4</v>
+      </c>
+      <c r="T197" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="U197" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V197" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W197" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X197" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="Y197" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z197" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AA197" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB197" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AC197" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD197" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE197" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF197" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AG197" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AH197" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI197" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ197" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AK197" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL197" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM197" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN197" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AP197" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ197" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR197" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AS197" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT197" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU197" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV197" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW197" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX197" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY197" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ197" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA197" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB197" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC197" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD197" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BE197" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF197" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH197" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI197" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BJ197" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BK197" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BL197" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BM197" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BN197" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BO197" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BP197" t="n">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="n">
+        <v>8260183</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="n">
+        <v>45914.6875</v>
+      </c>
+      <c r="F198" t="n">
+        <v>2</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Floresta</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="R198" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S198" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T198" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U198" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V198" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W198" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X198" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y198" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z198" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA198" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AB198" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AC198" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD198" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AE198" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AF198" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG198" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH198" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI198" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AJ198" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AK198" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL198" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM198" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AN198" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP198" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AQ198" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR198" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS198" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AT198" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU198" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY198" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ198" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA198" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB198" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC198" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD198" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE198" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF198" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG198" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH198" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BI198" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ198" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK198" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL198" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM198" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BN198" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO198" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP198" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="n">
+        <v>8260235</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="n">
+        <v>45914.79166666666</v>
+      </c>
+      <c r="F199" t="n">
+        <v>2</v>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>1</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="n">
+        <v>1</v>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R199" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S199" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T199" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U199" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V199" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="W199" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X199" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y199" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z199" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA199" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB199" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AC199" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD199" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE199" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF199" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG199" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH199" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AI199" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ199" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AK199" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL199" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM199" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN199" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AP199" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ199" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR199" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AS199" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AT199" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU199" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW199" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX199" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY199" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ199" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA199" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB199" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC199" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD199" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BE199" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF199" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BG199" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BH199" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI199" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ199" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BK199" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BL199" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BM199" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BN199" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BO199" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BP199" t="n">
+        <v>1.53</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -43654,22 +43654,22 @@
         <v>2.67</v>
       </c>
       <c r="AU198" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW198" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX198" t="n">
         <v>3</v>
       </c>
-      <c r="AV198" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW198" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX198" t="n">
+      <c r="AY198" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ198" t="n">
         <v>4</v>
-      </c>
-      <c r="AY198" t="n">
-        <v>16</v>
-      </c>
-      <c r="AZ198" t="n">
-        <v>5</v>
       </c>
       <c r="BA198" t="n">
         <v>11</v>
@@ -43773,7 +43773,7 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>['89']</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="P199" t="inlineStr">
@@ -43872,19 +43872,19 @@
         <v>2.67</v>
       </c>
       <c r="AU199" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV199" t="n">
         <v>1</v>
       </c>
       <c r="AW199" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX199" t="n">
         <v>4</v>
       </c>
       <c r="AY199" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ199" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP199"/>
+  <dimension ref="A1:BP201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.89</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.67</v>
@@ -3966,7 +3966,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -5274,7 +5274,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR22" t="n">
         <v>2.61</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ23" t="n">
         <v>1</v>
@@ -8977,7 +8977,7 @@
         <v>1</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ39" t="n">
         <v>1.4</v>
@@ -9198,7 +9198,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR40" t="n">
         <v>1.73</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.7</v>
@@ -10939,7 +10939,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.3</v>
@@ -11596,7 +11596,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR51" t="n">
         <v>1.68</v>
@@ -12686,7 +12686,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR56" t="n">
         <v>1.33</v>
@@ -13991,10 +13991,10 @@
         <v>2.33</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR62" t="n">
         <v>1.45</v>
@@ -14430,7 +14430,7 @@
         <v>2</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR64" t="n">
         <v>1.23</v>
@@ -14645,7 +14645,7 @@
         <v>1.67</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.3</v>
@@ -19008,7 +19008,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR85" t="n">
         <v>1.31</v>
@@ -19223,7 +19223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ86" t="n">
         <v>1</v>
@@ -20313,7 +20313,7 @@
         <v>1.25</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ91" t="n">
         <v>1</v>
@@ -21188,7 +21188,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR95" t="n">
         <v>2.52</v>
@@ -22711,7 +22711,7 @@
         <v>1</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.73</v>
@@ -23150,7 +23150,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR104" t="n">
         <v>1.71</v>
@@ -23583,7 +23583,7 @@
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ106" t="n">
         <v>1.3</v>
@@ -25112,7 +25112,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR113" t="n">
         <v>1.77</v>
@@ -27507,7 +27507,7 @@
         <v>0</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.4</v>
@@ -29033,10 +29033,10 @@
         <v>1.5</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR131" t="n">
         <v>1.45</v>
@@ -29905,7 +29905,7 @@
         <v>1</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ135" t="n">
         <v>0.67</v>
@@ -30344,7 +30344,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR137" t="n">
         <v>1.45</v>
@@ -32524,7 +32524,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR147" t="n">
         <v>1.28</v>
@@ -32739,7 +32739,7 @@
         <v>0.57</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ148" t="n">
         <v>0.4</v>
@@ -33614,7 +33614,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR152" t="n">
         <v>1.61</v>
@@ -34483,7 +34483,7 @@
         <v>1.57</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.8</v>
@@ -37099,7 +37099,7 @@
         <v>0.75</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.7</v>
@@ -37538,7 +37538,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR170" t="n">
         <v>1.43</v>
@@ -38843,7 +38843,7 @@
         <v>0.67</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.7</v>
@@ -39936,7 +39936,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AR181" t="n">
         <v>1.97</v>
@@ -40151,7 +40151,7 @@
         <v>1.13</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AQ182" t="n">
         <v>1</v>
@@ -41244,7 +41244,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AR187" t="n">
         <v>2.41</v>
@@ -42334,7 +42334,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AR192" t="n">
         <v>1.49</v>
@@ -42552,7 +42552,7 @@
         <v>1.52</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR193" t="n">
         <v>1.58</v>
@@ -42770,7 +42770,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AR194" t="n">
         <v>1.17</v>
@@ -42988,7 +42988,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AR195" t="n">
         <v>1.3</v>
@@ -43203,7 +43203,7 @@
         <v>1.4</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AQ196" t="n">
         <v>1.48</v>
@@ -43421,7 +43421,7 @@
         <v>1.55</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="AQ197" t="n">
         <v>1.52</v>
@@ -43639,7 +43639,7 @@
         <v>1.4</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ198" t="n">
         <v>1.38</v>
@@ -43857,7 +43857,7 @@
         <v>1.4</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.33</v>
@@ -43935,6 +43935,442 @@
         <v>2.3</v>
       </c>
       <c r="BP199" t="n">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="n">
+        <v>8260240</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="n">
+        <v>45920.70833333334</v>
+      </c>
+      <c r="F200" t="n">
+        <v>3</v>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>1</v>
+      </c>
+      <c r="K200" t="n">
+        <v>1</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
+        <v>1</v>
+      </c>
+      <c r="N200" t="n">
+        <v>1</v>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>['19']</t>
+        </is>
+      </c>
+      <c r="Q200" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R200" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S200" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T200" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U200" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="V200" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="W200" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X200" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Y200" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z200" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AA200" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AB200" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AC200" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD200" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AE200" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF200" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG200" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH200" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI200" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ200" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AK200" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL200" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM200" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN200" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AO200" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AP200" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AQ200" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AR200" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AS200" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AT200" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU200" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV200" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW200" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX200" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY200" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ200" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA200" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB200" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC200" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK200" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL200" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM200" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BN200" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO200" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="n">
+        <v>8260180</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="n">
+        <v>45920.8125</v>
+      </c>
+      <c r="F201" t="n">
+        <v>3</v>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Caxias</t>
+        </is>
+      </c>
+      <c r="I201" t="n">
+        <v>1</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>1</v>
+      </c>
+      <c r="L201" t="n">
+        <v>1</v>
+      </c>
+      <c r="M201" t="n">
+        <v>1</v>
+      </c>
+      <c r="N201" t="n">
+        <v>2</v>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>['43']</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="Q201" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R201" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S201" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="T201" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U201" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V201" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W201" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X201" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y201" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z201" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA201" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB201" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AC201" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD201" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AE201" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF201" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG201" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH201" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI201" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ201" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AK201" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL201" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AM201" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN201" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AP201" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ201" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AR201" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS201" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AT201" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU201" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW201" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX201" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY201" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ201" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA201" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB201" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC201" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD201" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE201" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF201" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BG201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH201" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI201" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ201" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK201" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BL201" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BM201" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BN201" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BO201" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BP201" t="n">
         <v>1.53</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP201"/>
+  <dimension ref="A1:BP202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.4</v>
@@ -4402,7 +4402,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR27" t="n">
         <v>1</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.4</v>
@@ -9852,7 +9852,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR43" t="n">
         <v>1.92</v>
@@ -11811,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.3</v>
@@ -15956,7 +15956,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR71" t="n">
         <v>1.26</v>
@@ -16825,7 +16825,7 @@
         <v>0</v>
       </c>
       <c r="AP75" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.4</v>
@@ -18572,7 +18572,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR83" t="n">
         <v>1.29</v>
@@ -22275,7 +22275,7 @@
         <v>1.25</v>
       </c>
       <c r="AP100" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ100" t="n">
         <v>1.4</v>
@@ -24676,7 +24676,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR111" t="n">
         <v>1.46</v>
@@ -25545,7 +25545,7 @@
         <v>1.4</v>
       </c>
       <c r="AP115" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.89</v>
@@ -28382,7 +28382,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR128" t="n">
         <v>1.32</v>
@@ -29251,7 +29251,7 @@
         <v>1.57</v>
       </c>
       <c r="AP132" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.3</v>
@@ -34701,7 +34701,7 @@
         <v>0.38</v>
       </c>
       <c r="AP157" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ157" t="n">
         <v>0.3</v>
@@ -35140,7 +35140,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR159" t="n">
         <v>1.31</v>
@@ -41895,10 +41895,10 @@
         <v>1.75</v>
       </c>
       <c r="AP190" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AR190" t="n">
         <v>1.24</v>
@@ -42549,7 +42549,7 @@
         <v>1.58</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ193" t="n">
         <v>1.5</v>
@@ -42767,7 +42767,7 @@
         <v>1.95</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AQ194" t="n">
         <v>1.82</v>
@@ -43424,7 +43424,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR197" t="n">
         <v>1.28</v>
@@ -43642,7 +43642,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AR198" t="n">
         <v>1.52</v>
@@ -44372,6 +44372,224 @@
       </c>
       <c r="BP201" t="n">
         <v>1.53</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="n">
+        <v>8260182</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="n">
+        <v>45921.6875</v>
+      </c>
+      <c r="F202" t="n">
+        <v>3</v>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Floresta</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q202" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R202" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S202" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="T202" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U202" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V202" t="n">
+        <v>4</v>
+      </c>
+      <c r="W202" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X202" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y202" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z202" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AA202" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AB202" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AC202" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD202" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AE202" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AF202" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG202" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH202" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI202" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ202" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK202" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL202" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AM202" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN202" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AP202" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ202" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR202" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AS202" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AT202" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU202" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV202" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW202" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX202" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY202" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ202" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA202" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB202" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC202" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO202" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP202" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP202"/>
+  <dimension ref="A1:BP203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
@@ -8759,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ38" t="n">
         <v>0.67</v>
@@ -8980,7 +8980,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR39" t="n">
         <v>1.45</v>
@@ -9849,7 +9849,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.45</v>
@@ -12250,7 +12250,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR54" t="n">
         <v>1.23</v>
@@ -15735,7 +15735,7 @@
         <v>0.33</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ70" t="n">
         <v>1</v>
@@ -17046,7 +17046,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR76" t="n">
         <v>2.25</v>
@@ -19877,7 +19877,7 @@
         <v>0</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.4</v>
@@ -20749,7 +20749,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ93" t="n">
         <v>0.67</v>
@@ -22278,7 +22278,7 @@
         <v>2</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR100" t="n">
         <v>1.21</v>
@@ -25763,7 +25763,7 @@
         <v>1.4</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ116" t="n">
         <v>1</v>
@@ -26856,7 +26856,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR121" t="n">
         <v>2.47</v>
@@ -29469,7 +29469,7 @@
         <v>1.33</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.8</v>
@@ -31216,7 +31216,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR141" t="n">
         <v>1.59</v>
@@ -34047,7 +34047,7 @@
         <v>1.14</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.89</v>
@@ -34922,7 +34922,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR158" t="n">
         <v>1.46</v>
@@ -37974,7 +37974,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AR172" t="n">
         <v>1.44</v>
@@ -39715,7 +39715,7 @@
         <v>0.78</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ180" t="n">
         <v>0.7</v>
@@ -42331,7 +42331,7 @@
         <v>1.89</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AQ192" t="n">
         <v>1.95</v>
@@ -42985,7 +42985,7 @@
         <v>1.89</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AQ195" t="n">
         <v>1.77</v>
@@ -43206,7 +43206,7 @@
         <v>1.77</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AR196" t="n">
         <v>1.43</v>
@@ -43860,7 +43860,7 @@
         <v>1.95</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AR199" t="n">
         <v>1.39</v>
@@ -44090,22 +44090,22 @@
         <v>2.91</v>
       </c>
       <c r="AU200" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AV200" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW200" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AX200" t="n">
         <v>5</v>
       </c>
       <c r="AY200" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ200" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA200" t="n">
         <v>11</v>
@@ -44308,22 +44308,22 @@
         <v>2.84</v>
       </c>
       <c r="AU201" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV201" t="n">
         <v>3</v>
       </c>
-      <c r="AV201" t="n">
-        <v>1</v>
-      </c>
       <c r="AW201" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX201" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AY201" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AZ201" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="BA201" t="n">
         <v>8</v>
@@ -44526,19 +44526,19 @@
         <v>2.7</v>
       </c>
       <c r="AU202" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV202" t="n">
         <v>0</v>
       </c>
       <c r="AW202" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX202" t="n">
         <v>9</v>
       </c>
       <c r="AY202" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ202" t="n">
         <v>9</v>
@@ -44590,6 +44590,224 @@
       </c>
       <c r="BP202" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="n">
+        <v>8260250</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="n">
+        <v>45921.79166666666</v>
+      </c>
+      <c r="F203" t="n">
+        <v>3</v>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>1</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="n">
+        <v>1</v>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q203" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R203" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S203" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="T203" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U203" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V203" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="W203" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X203" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y203" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z203" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA203" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB203" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="AC203" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD203" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AE203" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AF203" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AG203" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AH203" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AI203" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ203" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK203" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AL203" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AM203" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AN203" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP203" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ203" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR203" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS203" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AT203" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU203" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV203" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW203" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX203" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY203" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ203" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA203" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB203" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC203" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD203" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE203" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF203" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BG203" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH203" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI203" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BJ203" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK203" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BL203" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BM203" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BN203" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BO203" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BP203" t="n">
+        <v>1.58</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP203"/>
+  <dimension ref="A1:BP205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2004,7 +2004,7 @@
         <v>2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.4</v>
@@ -4617,10 +4617,10 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR25" t="n">
         <v>1.88</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.89</v>
@@ -7236,7 +7236,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR31" t="n">
         <v>0.73</v>
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.7</v>
@@ -10285,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.3</v>
@@ -11814,7 +11814,7 @@
         <v>2</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR52" t="n">
         <v>1.25</v>
@@ -12247,7 +12247,7 @@
         <v>1</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.27</v>
@@ -12468,7 +12468,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR55" t="n">
         <v>1.22</v>
@@ -15953,7 +15953,7 @@
         <v>2</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.45</v>
@@ -16174,7 +16174,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR72" t="n">
         <v>1.48</v>
@@ -16392,7 +16392,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR73" t="n">
         <v>1.45</v>
@@ -17915,7 +17915,7 @@
         <v>0.33</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.89</v>
@@ -18351,7 +18351,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.3</v>
@@ -19441,7 +19441,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.3</v>
@@ -21842,7 +21842,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR98" t="n">
         <v>1.45</v>
@@ -23586,7 +23586,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR106" t="n">
         <v>1.53</v>
@@ -24019,7 +24019,7 @@
         <v>0.4</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ108" t="n">
         <v>1</v>
@@ -24455,7 +24455,7 @@
         <v>0.6</v>
       </c>
       <c r="AP110" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.3</v>
@@ -26420,7 +26420,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR119" t="n">
         <v>1.75</v>
@@ -27725,7 +27725,7 @@
         <v>1</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.73</v>
@@ -28597,7 +28597,7 @@
         <v>0.17</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.4</v>
@@ -28818,7 +28818,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR130" t="n">
         <v>1.45</v>
@@ -29472,7 +29472,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR133" t="n">
         <v>1.59</v>
@@ -31649,10 +31649,10 @@
         <v>0.83</v>
       </c>
       <c r="AP143" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR143" t="n">
         <v>1.39</v>
@@ -32957,7 +32957,7 @@
         <v>0</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.4</v>
@@ -34486,7 +34486,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR156" t="n">
         <v>1.55</v>
@@ -35791,7 +35791,7 @@
         <v>0.13</v>
       </c>
       <c r="AP162" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ162" t="n">
         <v>0.4</v>
@@ -36448,7 +36448,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR165" t="n">
         <v>1.62</v>
@@ -36663,7 +36663,7 @@
         <v>1.43</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ166" t="n">
         <v>1.4</v>
@@ -39500,7 +39500,7 @@
         <v>1.55</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AR179" t="n">
         <v>1.77</v>
@@ -40369,7 +40369,7 @@
         <v>1.63</v>
       </c>
       <c r="AP183" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.4</v>
@@ -40808,7 +40808,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AR185" t="n">
         <v>1.49</v>
@@ -41677,7 +41677,7 @@
         <v>0.75</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="AQ189" t="n">
         <v>0.67</v>
@@ -42331,10 +42331,10 @@
         <v>1.89</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AR192" t="n">
         <v>1.49</v>
@@ -42985,10 +42985,10 @@
         <v>1.89</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AR195" t="n">
         <v>1.3</v>
@@ -43203,10 +43203,10 @@
         <v>1.4</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AR196" t="n">
         <v>1.43</v>
@@ -43857,10 +43857,10 @@
         <v>1.4</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AR199" t="n">
         <v>1.39</v>
@@ -44075,10 +44075,10 @@
         <v>1.9</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AR200" t="n">
         <v>1.51</v>
@@ -44729,10 +44729,10 @@
         <v>1.33</v>
       </c>
       <c r="AP203" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AR203" t="n">
         <v>1.42</v>
@@ -44808,6 +44808,442 @@
       </c>
       <c r="BP203" t="n">
         <v>1.58</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="n">
+        <v>8260238</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="n">
+        <v>45927.70833333334</v>
+      </c>
+      <c r="F204" t="n">
+        <v>4</v>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
+        <v>1</v>
+      </c>
+      <c r="M204" t="n">
+        <v>1</v>
+      </c>
+      <c r="N204" t="n">
+        <v>2</v>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>['90+4']</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="Q204" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R204" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S204" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T204" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U204" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V204" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="W204" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X204" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y204" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z204" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA204" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AB204" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC204" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD204" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AE204" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF204" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG204" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AH204" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI204" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AJ204" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AK204" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AL204" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM204" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AN204" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AP204" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ204" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AR204" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AS204" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AT204" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU204" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV204" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW204" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY204" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ204" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA204" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB204" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC204" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD204" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE204" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="BF204" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG204" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BH204" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BI204" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ204" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BK204" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BL204" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BM204" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BN204" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO204" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BP204" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="n">
+        <v>8260251</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="n">
+        <v>45927.8125</v>
+      </c>
+      <c r="F205" t="n">
+        <v>4</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="I205" t="n">
+        <v>1</v>
+      </c>
+      <c r="J205" t="n">
+        <v>1</v>
+      </c>
+      <c r="K205" t="n">
+        <v>2</v>
+      </c>
+      <c r="L205" t="n">
+        <v>3</v>
+      </c>
+      <c r="M205" t="n">
+        <v>2</v>
+      </c>
+      <c r="N205" t="n">
+        <v>5</v>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>['42', '78', '90+7']</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>['32', '87']</t>
+        </is>
+      </c>
+      <c r="Q205" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R205" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S205" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="T205" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U205" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V205" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="W205" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X205" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y205" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z205" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AA205" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB205" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AC205" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AD205" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AE205" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF205" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AG205" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AH205" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI205" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ205" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AK205" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AL205" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AM205" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN205" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO205" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AP205" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ205" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR205" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AS205" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT205" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU205" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW205" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX205" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY205" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ205" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA205" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB205" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC205" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD205" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BE205" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="BF205" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BG205" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH205" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI205" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BJ205" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BK205" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BL205" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BM205" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BN205" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BO205" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="BP205" t="n">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP205"/>
+  <dimension ref="A1:BP206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.3</v>
@@ -2658,7 +2658,7 @@
         <v>2.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -7018,7 +7018,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR30" t="n">
         <v>1.85</v>
@@ -9413,7 +9413,7 @@
         <v>3</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ41" t="n">
         <v>1.4</v>
@@ -10506,7 +10506,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR46" t="n">
         <v>1.03</v>
@@ -12683,7 +12683,7 @@
         <v>1.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ56" t="n">
         <v>1.25</v>
@@ -15084,7 +15084,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR67" t="n">
         <v>1.47</v>
@@ -18133,7 +18133,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.67</v>
@@ -20098,7 +20098,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR90" t="n">
         <v>1.87</v>
@@ -20967,7 +20967,7 @@
         <v>0.75</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.7</v>
@@ -22714,7 +22714,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR102" t="n">
         <v>1.38</v>
@@ -25109,7 +25109,7 @@
         <v>2.6</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ113" t="n">
         <v>1.82</v>
@@ -27728,7 +27728,7 @@
         <v>2</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR125" t="n">
         <v>1.29</v>
@@ -30777,7 +30777,7 @@
         <v>0.43</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ139" t="n">
         <v>0.7</v>
@@ -32088,7 +32088,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR145" t="n">
         <v>2.4</v>
@@ -32303,7 +32303,7 @@
         <v>0.43</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.3</v>
@@ -36881,7 +36881,7 @@
         <v>0.88</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ167" t="n">
         <v>1</v>
@@ -37320,7 +37320,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ169" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR169" t="n">
         <v>2.24</v>
@@ -38410,7 +38410,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ174" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="AR174" t="n">
         <v>1.96</v>
@@ -39497,7 +39497,7 @@
         <v>1.75</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AQ179" t="n">
         <v>1.73</v>
@@ -42549,7 +42549,7 @@
         <v>1.58</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AQ193" t="n">
         <v>1.5</v>
@@ -42767,7 +42767,7 @@
         <v>1.95</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AQ194" t="n">
         <v>1.82</v>
@@ -43424,7 +43424,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR197" t="n">
         <v>1.28</v>
@@ -43642,7 +43642,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AR198" t="n">
         <v>1.52</v>
@@ -44511,10 +44511,10 @@
         <v>1.52</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR202" t="n">
         <v>1.13</v>
@@ -45244,6 +45244,224 @@
       </c>
       <c r="BP205" t="n">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="n">
+        <v>8260248</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="n">
+        <v>45928.6875</v>
+      </c>
+      <c r="F206" t="n">
+        <v>4</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Floresta</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" t="n">
+        <v>0</v>
+      </c>
+      <c r="M206" t="n">
+        <v>1</v>
+      </c>
+      <c r="N206" t="n">
+        <v>1</v>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="Q206" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R206" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="S206" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="T206" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U206" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V206" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="W206" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X206" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y206" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z206" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA206" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB206" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AC206" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD206" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AE206" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF206" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AG206" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH206" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AI206" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AJ206" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK206" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL206" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AM206" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AN206" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AP206" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AQ206" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR206" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS206" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT206" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU206" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV206" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW206" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX206" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY206" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ206" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA206" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB206" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC206" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD206" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BE206" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="BF206" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BG206" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH206" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BI206" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ206" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BK206" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL206" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BM206" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BN206" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO206" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BP206" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP206"/>
+  <dimension ref="A1:BP207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.92</v>
@@ -4184,7 +4184,7 @@
         <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -7233,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AQ31" t="n">
         <v>1.18</v>
@@ -9416,7 +9416,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR41" t="n">
         <v>1.51</v>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.4</v>
@@ -13558,7 +13558,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR60" t="n">
         <v>2.4</v>
@@ -16607,10 +16607,10 @@
         <v>2.33</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR74" t="n">
         <v>0.91</v>
@@ -20534,7 +20534,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR92" t="n">
         <v>1.52</v>
@@ -22057,7 +22057,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AQ99" t="n">
         <v>1</v>
@@ -25984,7 +25984,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR117" t="n">
         <v>1.53</v>
@@ -26199,7 +26199,7 @@
         <v>0.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.7</v>
@@ -30341,7 +30341,7 @@
         <v>2.17</v>
       </c>
       <c r="AP137" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.82</v>
@@ -33396,7 +33396,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR151" t="n">
         <v>1.41</v>
@@ -33829,7 +33829,7 @@
         <v>1.5</v>
       </c>
       <c r="AP153" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.3</v>
@@ -36666,7 +36666,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR166" t="n">
         <v>1.31</v>
@@ -37971,7 +37971,7 @@
         <v>1.38</v>
       </c>
       <c r="AP172" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AQ172" t="n">
         <v>1.27</v>
@@ -40372,7 +40372,7 @@
         <v>2</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AR183" t="n">
         <v>1.42</v>
@@ -42552,7 +42552,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AR193" t="n">
         <v>1.58</v>
@@ -42770,7 +42770,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AR194" t="n">
         <v>1.17</v>
@@ -43421,7 +43421,7 @@
         <v>1.55</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AQ197" t="n">
         <v>1.43</v>
@@ -43639,7 +43639,7 @@
         <v>1.4</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AQ198" t="n">
         <v>1.43</v>
@@ -44293,10 +44293,10 @@
         <v>1.86</v>
       </c>
       <c r="AP201" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AR201" t="n">
         <v>1.54</v>
@@ -44965,19 +44965,19 @@
         <v>3</v>
       </c>
       <c r="AV204" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW204" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX204" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY204" t="n">
         <v>6</v>
       </c>
-      <c r="AX204" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY204" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ204" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA204" t="n">
         <v>4</v>
@@ -45180,22 +45180,22 @@
         <v>2.68</v>
       </c>
       <c r="AU205" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV205" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AW205" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX205" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AY205" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AZ205" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BA205" t="n">
         <v>6</v>
@@ -45462,6 +45462,224 @@
       </c>
       <c r="BP206" t="n">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="n">
+        <v>8260247</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="n">
+        <v>45928.79166666666</v>
+      </c>
+      <c r="F207" t="n">
+        <v>4</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Caxias</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" t="n">
+        <v>1</v>
+      </c>
+      <c r="N207" t="n">
+        <v>1</v>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="Q207" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R207" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="S207" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="T207" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U207" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V207" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W207" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X207" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="Y207" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z207" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AA207" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB207" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AC207" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD207" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AE207" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AF207" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AG207" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH207" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI207" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AJ207" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AK207" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL207" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AM207" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN207" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP207" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AQ207" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AR207" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AS207" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AT207" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AU207" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV207" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW207" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX207" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY207" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ207" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA207" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB207" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC207" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD207" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE207" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF207" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BG207" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH207" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BI207" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ207" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BK207" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BL207" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BM207" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN207" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BO207" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BP207" t="n">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -45304,7 +45304,7 @@
       </c>
       <c r="P206" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="Q206" t="n">
@@ -45401,19 +45401,19 @@
         <v>5</v>
       </c>
       <c r="AV206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW206" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX206" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY206" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ206" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BA206" t="n">
         <v>11</v>
@@ -45522,7 +45522,7 @@
       </c>
       <c r="P207" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>['72']</t>
         </is>
       </c>
       <c r="Q207" t="n">
@@ -45622,16 +45622,16 @@
         <v>2</v>
       </c>
       <c r="AW207" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX207" t="n">
         <v>7</v>
       </c>
-      <c r="AX207" t="n">
-        <v>8</v>
-      </c>
       <c r="AY207" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ207" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA207" t="n">
         <v>7</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP207"/>
+  <dimension ref="A1:BP211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ9" t="n">
         <v>1.3</v>
@@ -3966,7 +3966,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4181,10 +4181,10 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.18</v>
@@ -5274,7 +5274,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR22" t="n">
         <v>2.61</v>
@@ -5928,7 +5928,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR25" t="n">
         <v>1.88</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ28" t="n">
         <v>0.89</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.4</v>
@@ -8759,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ38" t="n">
         <v>0.67</v>
@@ -9198,7 +9198,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR40" t="n">
         <v>1.73</v>
@@ -9413,10 +9413,10 @@
         <v>3</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR41" t="n">
         <v>1.51</v>
@@ -9849,7 +9849,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.45</v>
@@ -10285,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.3</v>
@@ -11596,7 +11596,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR51" t="n">
         <v>1.68</v>
@@ -11811,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.18</v>
@@ -12468,7 +12468,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR55" t="n">
         <v>1.22</v>
@@ -12683,10 +12683,10 @@
         <v>1.5</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR56" t="n">
         <v>1.33</v>
@@ -13558,7 +13558,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR60" t="n">
         <v>2.4</v>
@@ -13994,7 +13994,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR62" t="n">
         <v>1.45</v>
@@ -14430,7 +14430,7 @@
         <v>2</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR64" t="n">
         <v>1.23</v>
@@ -15735,7 +15735,7 @@
         <v>0.33</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ70" t="n">
         <v>1</v>
@@ -15953,7 +15953,7 @@
         <v>2</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ71" t="n">
         <v>1.45</v>
@@ -16174,7 +16174,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR72" t="n">
         <v>1.48</v>
@@ -16610,7 +16610,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR74" t="n">
         <v>0.91</v>
@@ -16825,7 +16825,7 @@
         <v>0</v>
       </c>
       <c r="AP75" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.4</v>
@@ -18133,7 +18133,7 @@
         <v>0.67</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.67</v>
@@ -19008,7 +19008,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR85" t="n">
         <v>1.31</v>
@@ -19441,7 +19441,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ87" t="n">
         <v>0.3</v>
@@ -19877,7 +19877,7 @@
         <v>0</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.4</v>
@@ -20534,7 +20534,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR92" t="n">
         <v>1.52</v>
@@ -20749,7 +20749,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ93" t="n">
         <v>0.67</v>
@@ -20967,7 +20967,7 @@
         <v>0.75</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.7</v>
@@ -21188,7 +21188,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR95" t="n">
         <v>2.52</v>
@@ -21842,7 +21842,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR98" t="n">
         <v>1.45</v>
@@ -22275,7 +22275,7 @@
         <v>1.25</v>
       </c>
       <c r="AP100" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ100" t="n">
         <v>1.27</v>
@@ -23150,7 +23150,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR104" t="n">
         <v>1.71</v>
@@ -24019,7 +24019,7 @@
         <v>0.4</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ108" t="n">
         <v>1</v>
@@ -25109,10 +25109,10 @@
         <v>2.6</v>
       </c>
       <c r="AP113" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR113" t="n">
         <v>1.77</v>
@@ -25545,7 +25545,7 @@
         <v>1.4</v>
       </c>
       <c r="AP115" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.89</v>
@@ -25763,7 +25763,7 @@
         <v>1.4</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ116" t="n">
         <v>1</v>
@@ -25984,7 +25984,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR117" t="n">
         <v>1.53</v>
@@ -26420,7 +26420,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR119" t="n">
         <v>1.75</v>
@@ -28597,7 +28597,7 @@
         <v>0.17</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.4</v>
@@ -29036,7 +29036,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR131" t="n">
         <v>1.45</v>
@@ -29251,7 +29251,7 @@
         <v>1.57</v>
       </c>
       <c r="AP132" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.3</v>
@@ -29469,10 +29469,10 @@
         <v>1.33</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR133" t="n">
         <v>1.59</v>
@@ -30344,7 +30344,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR137" t="n">
         <v>1.45</v>
@@ -30777,7 +30777,7 @@
         <v>0.43</v>
       </c>
       <c r="AP139" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ139" t="n">
         <v>0.7</v>
@@ -32303,7 +32303,7 @@
         <v>0.43</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ146" t="n">
         <v>0.3</v>
@@ -32524,7 +32524,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR147" t="n">
         <v>1.28</v>
@@ -32957,7 +32957,7 @@
         <v>0</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ149" t="n">
         <v>0.4</v>
@@ -33396,7 +33396,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR151" t="n">
         <v>1.41</v>
@@ -33614,7 +33614,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR152" t="n">
         <v>1.61</v>
@@ -34047,7 +34047,7 @@
         <v>1.14</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.89</v>
@@ -34486,7 +34486,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR156" t="n">
         <v>1.55</v>
@@ -34701,7 +34701,7 @@
         <v>0.38</v>
       </c>
       <c r="AP157" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ157" t="n">
         <v>0.3</v>
@@ -36663,10 +36663,10 @@
         <v>1.43</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR166" t="n">
         <v>1.31</v>
@@ -36881,7 +36881,7 @@
         <v>0.88</v>
       </c>
       <c r="AP167" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ167" t="n">
         <v>1</v>
@@ -37538,7 +37538,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR170" t="n">
         <v>1.43</v>
@@ -39497,10 +39497,10 @@
         <v>1.75</v>
       </c>
       <c r="AP179" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AR179" t="n">
         <v>1.77</v>
@@ -39715,7 +39715,7 @@
         <v>0.78</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ180" t="n">
         <v>0.7</v>
@@ -39936,7 +39936,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AR181" t="n">
         <v>1.97</v>
@@ -40372,7 +40372,7 @@
         <v>2</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR183" t="n">
         <v>1.42</v>
@@ -41244,7 +41244,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR187" t="n">
         <v>2.41</v>
@@ -41677,7 +41677,7 @@
         <v>0.75</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AQ189" t="n">
         <v>0.67</v>
@@ -41895,7 +41895,7 @@
         <v>1.75</v>
       </c>
       <c r="AP190" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AQ190" t="n">
         <v>1.45</v>
@@ -42331,10 +42331,10 @@
         <v>1.89</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AR192" t="n">
         <v>1.49</v>
@@ -42549,10 +42549,10 @@
         <v>1.58</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AR193" t="n">
         <v>1.58</v>
@@ -42767,10 +42767,10 @@
         <v>1.95</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AR194" t="n">
         <v>1.17</v>
@@ -42985,10 +42985,10 @@
         <v>1.89</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AR195" t="n">
         <v>1.3</v>
@@ -43203,10 +43203,10 @@
         <v>1.4</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR196" t="n">
         <v>1.43</v>
@@ -43421,10 +43421,10 @@
         <v>1.55</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR197" t="n">
         <v>1.28</v>
@@ -43639,10 +43639,10 @@
         <v>1.4</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR198" t="n">
         <v>1.52</v>
@@ -43857,10 +43857,10 @@
         <v>1.4</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AR199" t="n">
         <v>1.39</v>
@@ -44075,10 +44075,10 @@
         <v>1.9</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AR200" t="n">
         <v>1.51</v>
@@ -44293,10 +44293,10 @@
         <v>1.86</v>
       </c>
       <c r="AP201" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AR201" t="n">
         <v>1.54</v>
@@ -44511,10 +44511,10 @@
         <v>1.52</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AR202" t="n">
         <v>1.13</v>
@@ -44729,10 +44729,10 @@
         <v>1.33</v>
       </c>
       <c r="AP203" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AR203" t="n">
         <v>1.42</v>
@@ -44947,10 +44947,10 @@
         <v>1.77</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AR204" t="n">
         <v>1.37</v>
@@ -45165,10 +45165,10 @@
         <v>1.55</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="AR205" t="n">
         <v>1.24</v>
@@ -45383,10 +45383,10 @@
         <v>1.36</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AR206" t="n">
         <v>1.54</v>
@@ -45601,10 +45601,10 @@
         <v>1.5</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AR207" t="n">
         <v>1.31</v>
@@ -45680,6 +45680,878 @@
       </c>
       <c r="BP207" t="n">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="n">
+        <v>8260237</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="n">
+        <v>45933.79166666666</v>
+      </c>
+      <c r="F208" t="n">
+        <v>5</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Floresta</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" t="n">
+        <v>1</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" t="n">
+        <v>1</v>
+      </c>
+      <c r="N208" t="n">
+        <v>1</v>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="Q208" t="n">
+        <v>0</v>
+      </c>
+      <c r="R208" t="n">
+        <v>0</v>
+      </c>
+      <c r="S208" t="n">
+        <v>0</v>
+      </c>
+      <c r="T208" t="n">
+        <v>0</v>
+      </c>
+      <c r="U208" t="n">
+        <v>0</v>
+      </c>
+      <c r="V208" t="n">
+        <v>0</v>
+      </c>
+      <c r="W208" t="n">
+        <v>0</v>
+      </c>
+      <c r="X208" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y208" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z208" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA208" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB208" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AC208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE208" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF208" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN208" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO208" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP208" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ208" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR208" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AS208" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AT208" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU208" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV208" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW208" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AX208" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AY208" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA208" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB208" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC208" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO208" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="n">
+        <v>8260234</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="n">
+        <v>45933.79166666666</v>
+      </c>
+      <c r="F209" t="n">
+        <v>5</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Caxias</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>1</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>1</v>
+      </c>
+      <c r="L209" t="n">
+        <v>1</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="n">
+        <v>1</v>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q209" t="n">
+        <v>0</v>
+      </c>
+      <c r="R209" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" t="n">
+        <v>0</v>
+      </c>
+      <c r="T209" t="n">
+        <v>0</v>
+      </c>
+      <c r="U209" t="n">
+        <v>0</v>
+      </c>
+      <c r="V209" t="n">
+        <v>0</v>
+      </c>
+      <c r="W209" t="n">
+        <v>0</v>
+      </c>
+      <c r="X209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y209" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z209" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA209" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG209" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH209" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN209" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO209" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AP209" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ209" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR209" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS209" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AT209" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU209" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV209" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW209" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AX209" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AY209" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA209" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB209" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC209" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO209" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="n">
+        <v>8260243</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="n">
+        <v>45934.70833333334</v>
+      </c>
+      <c r="F210" t="n">
+        <v>5</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>1</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>1</v>
+      </c>
+      <c r="L210" t="n">
+        <v>1</v>
+      </c>
+      <c r="M210" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" t="n">
+        <v>1</v>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>['33']</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q210" t="n">
+        <v>3</v>
+      </c>
+      <c r="R210" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S210" t="n">
+        <v>4</v>
+      </c>
+      <c r="T210" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U210" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V210" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="W210" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X210" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN210" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO210" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AP210" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AQ210" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR210" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AS210" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AT210" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU210" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV210" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW210" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX210" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY210" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ210" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA210" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB210" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC210" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD210" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BE210" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF210" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG210" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BH210" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BI210" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ210" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BK210" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BL210" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BM210" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN210" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BO210" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="BP210" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="n">
+        <v>8260242</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="n">
+        <v>45934.8125</v>
+      </c>
+      <c r="F211" t="n">
+        <v>5</v>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>1</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>1</v>
+      </c>
+      <c r="L211" t="n">
+        <v>2</v>
+      </c>
+      <c r="M211" t="n">
+        <v>1</v>
+      </c>
+      <c r="N211" t="n">
+        <v>3</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>['21', '46']</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R211" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S211" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="T211" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U211" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V211" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="W211" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X211" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN211" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO211" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AP211" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ211" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR211" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AS211" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AT211" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AU211" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV211" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW211" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX211" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY211" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB211" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC211" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD211" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE211" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF211" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG211" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH211" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI211" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BJ211" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="BK211" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BL211" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BM211" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BN211" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO211" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BP211" t="n">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -1132,7 +1132,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -2004,7 +2004,7 @@
         <v>2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AQ8" t="n">
         <v>1</v>
@@ -3966,7 +3966,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ17" t="n">
         <v>1.67</v>
@@ -5274,7 +5274,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AR22" t="n">
         <v>2.61</v>
@@ -5928,7 +5928,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AR25" t="n">
         <v>1.88</v>
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ36" t="n">
         <v>0.4</v>
@@ -8759,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AQ38" t="n">
         <v>0.67</v>
@@ -9198,7 +9198,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AR40" t="n">
         <v>1.73</v>
@@ -9849,7 +9849,7 @@
         <v>1.5</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AQ43" t="n">
         <v>1.45</v>
@@ -11596,7 +11596,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AR51" t="n">
         <v>1.68</v>
@@ -11811,7 +11811,7 @@
         <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ52" t="n">
         <v>1.18</v>
@@ -12468,7 +12468,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AR55" t="n">
         <v>1.22</v>
@@ -12686,7 +12686,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AR56" t="n">
         <v>1.33</v>
@@ -13994,7 +13994,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AR62" t="n">
         <v>1.45</v>
@@ -14430,7 +14430,7 @@
         <v>2</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AR64" t="n">
         <v>1.23</v>
@@ -15735,7 +15735,7 @@
         <v>0.33</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AQ70" t="n">
         <v>1</v>
@@ -16174,7 +16174,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AR72" t="n">
         <v>1.48</v>
@@ -16825,7 +16825,7 @@
         <v>0</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ75" t="n">
         <v>0.4</v>
@@ -19008,7 +19008,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AR85" t="n">
         <v>1.31</v>
@@ -19877,7 +19877,7 @@
         <v>0</v>
       </c>
       <c r="AP89" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.4</v>
@@ -20749,7 +20749,7 @@
         <v>1.25</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AQ93" t="n">
         <v>0.67</v>
@@ -21188,7 +21188,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AR95" t="n">
         <v>2.52</v>
@@ -21842,7 +21842,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AR98" t="n">
         <v>1.45</v>
@@ -22275,7 +22275,7 @@
         <v>1.25</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ100" t="n">
         <v>1.27</v>
@@ -23150,7 +23150,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AR104" t="n">
         <v>1.71</v>
@@ -25112,7 +25112,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AR113" t="n">
         <v>1.77</v>
@@ -25545,7 +25545,7 @@
         <v>1.4</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.89</v>
@@ -25763,7 +25763,7 @@
         <v>1.4</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AQ116" t="n">
         <v>1</v>
@@ -26420,7 +26420,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AR119" t="n">
         <v>1.75</v>
@@ -29036,7 +29036,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AR131" t="n">
         <v>1.45</v>
@@ -29251,7 +29251,7 @@
         <v>1.57</v>
       </c>
       <c r="AP132" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ132" t="n">
         <v>1.3</v>
@@ -29469,10 +29469,10 @@
         <v>1.33</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AR133" t="n">
         <v>1.59</v>
@@ -30344,7 +30344,7 @@
         <v>2.27</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AR137" t="n">
         <v>1.45</v>
@@ -32524,7 +32524,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AR147" t="n">
         <v>1.28</v>
@@ -33614,7 +33614,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AR152" t="n">
         <v>1.61</v>
@@ -34047,7 +34047,7 @@
         <v>1.14</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.89</v>
@@ -34486,7 +34486,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ156" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AR156" t="n">
         <v>1.55</v>
@@ -34701,7 +34701,7 @@
         <v>0.38</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ157" t="n">
         <v>0.3</v>
@@ -37538,7 +37538,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AR170" t="n">
         <v>1.43</v>
@@ -39200,7 +39200,7 @@
       </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>['90+2']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="Q178" t="n">
@@ -39500,7 +39500,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ179" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AR179" t="n">
         <v>1.77</v>
@@ -39715,7 +39715,7 @@
         <v>0.78</v>
       </c>
       <c r="AP180" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AQ180" t="n">
         <v>0.7</v>
@@ -39936,7 +39936,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AR181" t="n">
         <v>1.97</v>
@@ -40067,7 +40067,7 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>['25', '90+2', '90+5']</t>
+          <t>['25', '90+5', '90+2']</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
@@ -40285,7 +40285,7 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>['59']</t>
+          <t>['60']</t>
         </is>
       </c>
       <c r="P183" t="inlineStr">
@@ -40823,19 +40823,19 @@
         <v>6</v>
       </c>
       <c r="AV185" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW185" t="n">
         <v>11</v>
       </c>
       <c r="AX185" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AY185" t="n">
         <v>17</v>
       </c>
       <c r="AZ185" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA185" t="n">
         <v>3</v>
@@ -41244,7 +41244,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AR187" t="n">
         <v>2.41</v>
@@ -41593,7 +41593,7 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>['49', '88']</t>
+          <t>['49', '89']</t>
         </is>
       </c>
       <c r="P189" t="inlineStr">
@@ -41701,13 +41701,13 @@
         <v>10</v>
       </c>
       <c r="AX189" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY189" t="n">
         <v>14</v>
       </c>
       <c r="AZ189" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA189" t="n">
         <v>5</v>
@@ -41895,7 +41895,7 @@
         <v>1.75</v>
       </c>
       <c r="AP190" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AQ190" t="n">
         <v>1.45</v>
@@ -42231,19 +42231,19 @@
         <v>0</v>
       </c>
       <c r="J192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O192" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
       </c>
       <c r="P192" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="Q192" t="n">
@@ -42331,19 +42331,19 @@
         <v>1.89</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR192" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AS192" t="n">
         <v>1.43</v>
       </c>
       <c r="AT192" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="AU192" t="n">
         <v>1</v>
@@ -42449,28 +42449,28 @@
         <v>0</v>
       </c>
       <c r="J193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['58', '65']</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['6', '45+3']</t>
         </is>
       </c>
       <c r="Q193" t="n">
@@ -42664,26 +42664,26 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M194" t="n">
         <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11']</t>
         </is>
       </c>
       <c r="P194" t="inlineStr">
@@ -42767,10 +42767,10 @@
         <v>1.95</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR194" t="n">
         <v>1.17</v>
@@ -42782,31 +42782,31 @@
         <v>2.5</v>
       </c>
       <c r="AU194" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="AV194" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="AW194" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="AX194" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="AY194" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AZ194" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BA194" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="BB194" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BC194" t="n">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BD194" t="n">
         <v>0</v>
@@ -42988,7 +42988,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR195" t="n">
         <v>1.3</v>
@@ -43200,22 +43200,22 @@
         <v>1.95</v>
       </c>
       <c r="AO196" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AR196" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AS196" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AT196" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AU196" t="n">
         <v>9</v>
@@ -43415,25 +43415,25 @@
         <v>1.57</v>
       </c>
       <c r="AN197" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AO197" t="n">
         <v>1.55</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ197" t="n">
         <v>1.5</v>
       </c>
       <c r="AR197" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AS197" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AT197" t="n">
-        <v>2.84</v>
+        <v>2.91</v>
       </c>
       <c r="AU197" t="n">
         <v>3</v>
@@ -43636,22 +43636,22 @@
         <v>1.55</v>
       </c>
       <c r="AO198" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AP198" t="n">
         <v>1.63</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AR198" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AS198" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AT198" t="n">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="AU198" t="n">
         <v>4</v>
@@ -43851,25 +43851,25 @@
         <v>1.95</v>
       </c>
       <c r="AN199" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AO199" t="n">
         <v>1.4</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.42</v>
       </c>
       <c r="AR199" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AS199" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AT199" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="AU199" t="n">
         <v>3</v>
@@ -44072,22 +44072,22 @@
         <v>1.86</v>
       </c>
       <c r="AO200" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR200" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AS200" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AT200" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AU200" t="n">
         <v>5</v>
@@ -44290,22 +44290,22 @@
         <v>1.52</v>
       </c>
       <c r="AO201" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="AP201" t="n">
         <v>1.63</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AR201" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AS201" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AT201" t="n">
-        <v>2.84</v>
+        <v>2.93</v>
       </c>
       <c r="AU201" t="n">
         <v>7</v>
@@ -44505,25 +44505,25 @@
         <v>1.44</v>
       </c>
       <c r="AN202" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AO202" t="n">
         <v>1.52</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AQ202" t="n">
         <v>1.5</v>
       </c>
       <c r="AR202" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AS202" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AT202" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="AU202" t="n">
         <v>5</v>
@@ -44723,25 +44723,25 @@
         <v>1.89</v>
       </c>
       <c r="AN203" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AO203" t="n">
         <v>1.33</v>
       </c>
       <c r="AP203" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.42</v>
       </c>
       <c r="AR203" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AS203" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AT203" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="AU203" t="n">
         <v>6</v>
@@ -44941,25 +44941,25 @@
         <v>1.92</v>
       </c>
       <c r="AN204" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AO204" t="n">
         <v>1.77</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AR204" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AS204" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AT204" t="n">
-        <v>2.92</v>
+        <v>3.01</v>
       </c>
       <c r="AU204" t="n">
         <v>3</v>
@@ -45162,22 +45162,22 @@
         <v>1.27</v>
       </c>
       <c r="AO205" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AP205" t="n">
         <v>1.42</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AR205" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AS205" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AT205" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="AU205" t="n">
         <v>8</v>
@@ -45380,22 +45380,22 @@
         <v>1.5</v>
       </c>
       <c r="AO206" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AP206" t="n">
         <v>1.5</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AR206" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AS206" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AT206" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="AU206" t="n">
         <v>5</v>
@@ -45595,25 +45595,25 @@
         <v>1.67</v>
       </c>
       <c r="AN207" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AO207" t="n">
         <v>1.5</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ207" t="n">
         <v>1.63</v>
       </c>
       <c r="AR207" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AS207" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AT207" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="AU207" t="n">
         <v>7</v>
@@ -45687,7 +45687,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="n">
-        <v>8260237</v>
+        <v>8260243</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -45700,204 +45700,204 @@
         </is>
       </c>
       <c r="E208" s="2" t="n">
-        <v>45933.79166666666</v>
+        <v>45934.70833333334</v>
       </c>
       <c r="F208" t="n">
         <v>5</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Floresta</t>
+          <t>Guarani</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Náutico</t>
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K208" t="n">
         <v>1</v>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M208" t="n">
         <v>1</v>
       </c>
       <c r="N208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+2']</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
         <is>
-          <t>['45+1']</t>
+          <t>['77']</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R208" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S208" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T208" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="U208" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V208" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="W208" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X208" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Y208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z208" t="n">
-        <v>2.62</v>
+        <v>2.23</v>
       </c>
       <c r="AA208" t="n">
-        <v>2.62</v>
+        <v>3.04</v>
       </c>
       <c r="AB208" t="n">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="AC208" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AD208" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AE208" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AF208" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AG208" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH208" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI208" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ208" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK208" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL208" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AM208" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AN208" t="n">
         <v>1.43</v>
       </c>
       <c r="AO208" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AQ208" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AR208" t="n">
-        <v>1.17</v>
+        <v>1.45</v>
       </c>
       <c r="AS208" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AT208" t="n">
-        <v>2.72</v>
+        <v>3.06</v>
       </c>
       <c r="AU208" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV208" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW208" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX208" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY208" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ208" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA208" t="n">
         <v>4</v>
       </c>
-      <c r="AV208" t="n">
+      <c r="BB208" t="n">
         <v>5</v>
       </c>
-      <c r="AW208" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AX208" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AY208" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ208" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA208" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB208" t="n">
-        <v>3</v>
-      </c>
       <c r="BC208" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD208" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="BE208" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="BF208" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BG208" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BH208" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="BI208" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BJ208" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BK208" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BL208" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BM208" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BN208" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BO208" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="BP208" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="209">
@@ -45905,7 +45905,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="n">
-        <v>8260234</v>
+        <v>8260242</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -45918,19 +45918,19 @@
         </is>
       </c>
       <c r="E209" s="2" t="n">
-        <v>45933.79166666666</v>
+        <v>45934.8125</v>
       </c>
       <c r="F209" t="n">
         <v>5</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="I209" t="n">
@@ -45943,179 +45943,179 @@
         <v>1</v>
       </c>
       <c r="L209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N209" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>['38']</t>
+          <t>['21', '46']</t>
         </is>
       </c>
       <c r="P209" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['49']</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R209" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S209" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="T209" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U209" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V209" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="W209" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X209" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z209" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AA209" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB209" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC209" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD209" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE209" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AF209" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG209" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH209" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI209" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ209" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK209" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AL209" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM209" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AN209" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO209" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP209" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AQ209" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AR209" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AS209" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT209" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU209" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV209" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW209" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX209" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY209" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ209" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA209" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB209" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC209" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD209" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BE209" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF209" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG209" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BH209" t="n">
         <v>2.9</v>
       </c>
-      <c r="AB209" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AC209" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD209" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE209" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF209" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG209" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AH209" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI209" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ209" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK209" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL209" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM209" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN209" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AO209" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AP209" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AQ209" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR209" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS209" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AT209" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AU209" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV209" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW209" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AX209" t="n">
-        <v>-4</v>
-      </c>
-      <c r="AY209" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ209" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA209" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB209" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC209" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD209" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE209" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF209" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG209" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH209" t="n">
-        <v>0</v>
-      </c>
       <c r="BI209" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BJ209" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="BK209" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="BL209" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BM209" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BN209" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BO209" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="BP209" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="210">
@@ -46123,7 +46123,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="n">
-        <v>8260243</v>
+        <v>8260237</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -46136,204 +46136,204 @@
         </is>
       </c>
       <c r="E210" s="2" t="n">
-        <v>45934.70833333334</v>
+        <v>45935.6875</v>
       </c>
       <c r="F210" t="n">
         <v>5</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Guarani</t>
+          <t>Floresta</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Náutico</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K210" t="n">
         <v>1</v>
       </c>
       <c r="L210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N210" t="n">
         <v>1</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>['33']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P210" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="Q210" t="n">
+        <v>0</v>
+      </c>
+      <c r="R210" t="n">
+        <v>0</v>
+      </c>
+      <c r="S210" t="n">
+        <v>0</v>
+      </c>
+      <c r="T210" t="n">
+        <v>0</v>
+      </c>
+      <c r="U210" t="n">
+        <v>0</v>
+      </c>
+      <c r="V210" t="n">
+        <v>0</v>
+      </c>
+      <c r="W210" t="n">
+        <v>0</v>
+      </c>
+      <c r="X210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y210" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z210" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA210" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB210" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="AC210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE210" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF210" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM210" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN210" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AO210" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP210" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ210" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR210" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AS210" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AT210" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AU210" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV210" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW210" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX210" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY210" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ210" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA210" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB210" t="n">
         <v>3</v>
       </c>
-      <c r="R210" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="S210" t="n">
-        <v>4</v>
-      </c>
-      <c r="T210" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U210" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V210" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="W210" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X210" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="Y210" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z210" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AA210" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AB210" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC210" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD210" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AE210" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AF210" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG210" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH210" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AI210" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ210" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AK210" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AL210" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AM210" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AN210" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO210" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AP210" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AQ210" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR210" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AS210" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AT210" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AU210" t="n">
-        <v>5</v>
-      </c>
-      <c r="AV210" t="n">
-        <v>2</v>
-      </c>
-      <c r="AW210" t="n">
-        <v>3</v>
-      </c>
-      <c r="AX210" t="n">
+      <c r="BC210" t="n">
         <v>8</v>
       </c>
-      <c r="AY210" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ210" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA210" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB210" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC210" t="n">
-        <v>9</v>
-      </c>
       <c r="BD210" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="BE210" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="BF210" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BG210" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BH210" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="BI210" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BJ210" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="BK210" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BL210" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BM210" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BN210" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BO210" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="BP210" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -46341,7 +46341,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="n">
-        <v>8260242</v>
+        <v>8260234</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -46354,19 +46354,19 @@
         </is>
       </c>
       <c r="E211" s="2" t="n">
-        <v>45934.8125</v>
+        <v>45935.79166666666</v>
       </c>
       <c r="F211" t="n">
         <v>5</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="I211" t="n">
@@ -46379,179 +46379,179 @@
         <v>1</v>
       </c>
       <c r="L211" t="n">
+        <v>1</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="n">
+        <v>1</v>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>['38']</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q211" t="n">
+        <v>0</v>
+      </c>
+      <c r="R211" t="n">
+        <v>0</v>
+      </c>
+      <c r="S211" t="n">
+        <v>0</v>
+      </c>
+      <c r="T211" t="n">
+        <v>0</v>
+      </c>
+      <c r="U211" t="n">
+        <v>0</v>
+      </c>
+      <c r="V211" t="n">
+        <v>0</v>
+      </c>
+      <c r="W211" t="n">
+        <v>0</v>
+      </c>
+      <c r="X211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y211" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z211" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA211" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AB211" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AC211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE211" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF211" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG211" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH211" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM211" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN211" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO211" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AP211" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ211" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR211" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS211" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT211" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU211" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV211" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW211" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX211" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY211" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ211" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA211" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB211" t="n">
         <v>2</v>
       </c>
-      <c r="M211" t="n">
-        <v>1</v>
-      </c>
-      <c r="N211" t="n">
-        <v>3</v>
-      </c>
-      <c r="O211" t="inlineStr">
-        <is>
-          <t>['21', '46']</t>
-        </is>
-      </c>
-      <c r="P211" t="inlineStr">
-        <is>
-          <t>['49']</t>
-        </is>
-      </c>
-      <c r="Q211" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R211" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S211" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="T211" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U211" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="V211" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="W211" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X211" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Y211" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z211" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AA211" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AB211" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AC211" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AD211" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE211" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AF211" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AG211" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AH211" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI211" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ211" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AK211" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL211" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AM211" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AN211" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AO211" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AP211" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AQ211" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AR211" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AS211" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AT211" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AU211" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV211" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW211" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX211" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY211" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ211" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA211" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB211" t="n">
-        <v>8</v>
-      </c>
       <c r="BC211" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD211" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BE211" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BF211" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BG211" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BH211" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BI211" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="BJ211" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="BK211" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="BL211" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BM211" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="BN211" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="BO211" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="BP211" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP211"/>
+  <dimension ref="A1:BP215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.92</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.89</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.4</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.67</v>
@@ -4402,7 +4402,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>3</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ23" t="n">
         <v>1</v>
@@ -6364,7 +6364,7 @@
         <v>2</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR27" t="n">
         <v>1</v>
@@ -7233,10 +7233,10 @@
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR31" t="n">
         <v>0.73</v>
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.7</v>
@@ -8977,10 +8977,10 @@
         <v>1</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR39" t="n">
         <v>1.45</v>
@@ -9631,7 +9631,7 @@
         <v>0</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ42" t="n">
         <v>0.7</v>
@@ -9852,7 +9852,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR43" t="n">
         <v>1.92</v>
@@ -10721,7 +10721,7 @@
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.4</v>
@@ -10939,7 +10939,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.3</v>
@@ -11814,7 +11814,7 @@
         <v>2</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR52" t="n">
         <v>1.25</v>
@@ -12247,10 +12247,10 @@
         <v>1</v>
       </c>
       <c r="AP54" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR54" t="n">
         <v>1.23</v>
@@ -13991,7 +13991,7 @@
         <v>2.33</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.83</v>
@@ -14645,7 +14645,7 @@
         <v>1.67</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.3</v>
@@ -15956,7 +15956,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ71" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR71" t="n">
         <v>1.26</v>
@@ -16392,7 +16392,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ73" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR73" t="n">
         <v>1.45</v>
@@ -16607,7 +16607,7 @@
         <v>2.33</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ74" t="n">
         <v>1.67</v>
@@ -17046,7 +17046,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR76" t="n">
         <v>2.25</v>
@@ -17915,7 +17915,7 @@
         <v>0.33</v>
       </c>
       <c r="AP80" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.89</v>
@@ -18351,7 +18351,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.3</v>
@@ -18572,7 +18572,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR83" t="n">
         <v>1.29</v>
@@ -19223,7 +19223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ86" t="n">
         <v>1</v>
@@ -20313,7 +20313,7 @@
         <v>1.25</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ91" t="n">
         <v>1</v>
@@ -22057,7 +22057,7 @@
         <v>1.75</v>
       </c>
       <c r="AP99" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ99" t="n">
         <v>1</v>
@@ -22278,7 +22278,7 @@
         <v>2</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR100" t="n">
         <v>1.21</v>
@@ -22711,7 +22711,7 @@
         <v>1</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ102" t="n">
         <v>0.92</v>
@@ -23583,10 +23583,10 @@
         <v>1</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR106" t="n">
         <v>1.53</v>
@@ -24455,7 +24455,7 @@
         <v>0.6</v>
       </c>
       <c r="AP110" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.3</v>
@@ -24676,7 +24676,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ111" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR111" t="n">
         <v>1.46</v>
@@ -26199,7 +26199,7 @@
         <v>0.6</v>
       </c>
       <c r="AP118" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ118" t="n">
         <v>0.7</v>
@@ -26856,7 +26856,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR121" t="n">
         <v>2.47</v>
@@ -27507,7 +27507,7 @@
         <v>0</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.4</v>
@@ -27725,7 +27725,7 @@
         <v>1</v>
       </c>
       <c r="AP125" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ125" t="n">
         <v>0.92</v>
@@ -28382,7 +28382,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR128" t="n">
         <v>1.32</v>
@@ -28818,7 +28818,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR130" t="n">
         <v>1.45</v>
@@ -29033,7 +29033,7 @@
         <v>1.5</v>
       </c>
       <c r="AP131" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.08</v>
@@ -29905,7 +29905,7 @@
         <v>1</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ135" t="n">
         <v>0.67</v>
@@ -30341,7 +30341,7 @@
         <v>2.17</v>
       </c>
       <c r="AP137" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.83</v>
@@ -31216,7 +31216,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR141" t="n">
         <v>1.59</v>
@@ -31649,10 +31649,10 @@
         <v>0.83</v>
       </c>
       <c r="AP143" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR143" t="n">
         <v>1.39</v>
@@ -32739,7 +32739,7 @@
         <v>0.57</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ148" t="n">
         <v>0.4</v>
@@ -33829,7 +33829,7 @@
         <v>1.5</v>
       </c>
       <c r="AP153" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.3</v>
@@ -34483,7 +34483,7 @@
         <v>1.57</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.67</v>
@@ -34922,7 +34922,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ158" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR158" t="n">
         <v>1.46</v>
@@ -35140,7 +35140,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ159" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR159" t="n">
         <v>1.31</v>
@@ -35791,7 +35791,7 @@
         <v>0.13</v>
       </c>
       <c r="AP162" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ162" t="n">
         <v>0.4</v>
@@ -36448,7 +36448,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR165" t="n">
         <v>1.62</v>
@@ -37099,7 +37099,7 @@
         <v>0.75</v>
       </c>
       <c r="AP168" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ168" t="n">
         <v>0.7</v>
@@ -37971,10 +37971,10 @@
         <v>1.38</v>
       </c>
       <c r="AP172" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR172" t="n">
         <v>1.44</v>
@@ -38843,7 +38843,7 @@
         <v>0.67</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.7</v>
@@ -40151,7 +40151,7 @@
         <v>1.13</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ182" t="n">
         <v>1</v>
@@ -40369,7 +40369,7 @@
         <v>1.63</v>
       </c>
       <c r="AP183" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.67</v>
@@ -40808,7 +40808,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AR185" t="n">
         <v>1.49</v>
@@ -41898,7 +41898,7 @@
         <v>2</v>
       </c>
       <c r="AQ190" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AR190" t="n">
         <v>1.24</v>
@@ -42331,10 +42331,10 @@
         <v>1.89</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AR192" t="n">
         <v>1.48</v>
@@ -42549,10 +42549,10 @@
         <v>1.58</v>
       </c>
       <c r="AP193" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AR193" t="n">
         <v>1.58</v>
@@ -42767,10 +42767,10 @@
         <v>1.95</v>
       </c>
       <c r="AP194" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AR194" t="n">
         <v>1.17</v>
@@ -42985,10 +42985,10 @@
         <v>1.89</v>
       </c>
       <c r="AP195" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AQ195" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AR195" t="n">
         <v>1.3</v>
@@ -43203,10 +43203,10 @@
         <v>1.35</v>
       </c>
       <c r="AP196" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AR196" t="n">
         <v>1.49</v>
@@ -43421,10 +43421,10 @@
         <v>1.55</v>
       </c>
       <c r="AP197" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AQ197" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR197" t="n">
         <v>1.33</v>
@@ -43639,10 +43639,10 @@
         <v>1.5</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR198" t="n">
         <v>1.57</v>
@@ -43857,10 +43857,10 @@
         <v>1.4</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AQ199" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AR199" t="n">
         <v>1.43</v>
@@ -44075,10 +44075,10 @@
         <v>2</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AR200" t="n">
         <v>1.56</v>
@@ -44293,10 +44293,10 @@
         <v>1.81</v>
       </c>
       <c r="AP201" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AR201" t="n">
         <v>1.59</v>
@@ -44511,10 +44511,10 @@
         <v>1.52</v>
       </c>
       <c r="AP202" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AR202" t="n">
         <v>1.14</v>
@@ -44729,10 +44729,10 @@
         <v>1.33</v>
       </c>
       <c r="AP203" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AQ203" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AR203" t="n">
         <v>1.45</v>
@@ -44947,10 +44947,10 @@
         <v>1.77</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AR204" t="n">
         <v>1.4</v>
@@ -45165,10 +45165,10 @@
         <v>1.5</v>
       </c>
       <c r="AP205" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AR205" t="n">
         <v>1.26</v>
@@ -45383,10 +45383,10 @@
         <v>1.45</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AR206" t="n">
         <v>1.55</v>
@@ -45601,10 +45601,10 @@
         <v>1.5</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AR207" t="n">
         <v>1.35</v>
@@ -45819,10 +45819,10 @@
         <v>1.74</v>
       </c>
       <c r="AP208" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AQ208" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AR208" t="n">
         <v>1.45</v>
@@ -46037,10 +46037,10 @@
         <v>2</v>
       </c>
       <c r="AP209" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AR209" t="n">
         <v>1.29</v>
@@ -46255,10 +46255,10 @@
         <v>1.57</v>
       </c>
       <c r="AP210" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AQ210" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AR210" t="n">
         <v>1.19</v>
@@ -46473,10 +46473,10 @@
         <v>1.7</v>
       </c>
       <c r="AP211" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AR211" t="n">
         <v>1.59</v>
@@ -46552,6 +46552,878 @@
       </c>
       <c r="BP211" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="n">
+        <v>8260244</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="n">
+        <v>45941.70833333334</v>
+      </c>
+      <c r="F212" t="n">
+        <v>6</v>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Brusque</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>1</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>1</v>
+      </c>
+      <c r="L212" t="n">
+        <v>2</v>
+      </c>
+      <c r="M212" t="n">
+        <v>1</v>
+      </c>
+      <c r="N212" t="n">
+        <v>3</v>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>['33', '86']</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="Q212" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="R212" t="n">
+        <v>2</v>
+      </c>
+      <c r="S212" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="T212" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="U212" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V212" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="W212" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X212" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Y212" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z212" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AA212" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="AB212" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AC212" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD212" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE212" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF212" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AG212" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AH212" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI212" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AJ212" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK212" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AL212" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM212" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AN212" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO212" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP212" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AQ212" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR212" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS212" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AT212" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU212" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV212" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW212" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX212" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY212" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ212" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA212" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB212" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC212" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD212" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BE212" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BF212" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="BG212" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BH212" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="BI212" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BJ212" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BK212" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL212" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BM212" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BN212" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BO212" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BP212" t="n">
+        <v>1.52</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="n">
+        <v>8260236</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="n">
+        <v>45941.70833333334</v>
+      </c>
+      <c r="F213" t="n">
+        <v>6</v>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Caxias</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Floresta</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>1</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>1</v>
+      </c>
+      <c r="L213" t="n">
+        <v>1</v>
+      </c>
+      <c r="M213" t="n">
+        <v>1</v>
+      </c>
+      <c r="N213" t="n">
+        <v>2</v>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="Q213" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R213" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S213" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="T213" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U213" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V213" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="W213" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X213" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y213" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Z213" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA213" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AB213" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AC213" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD213" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AE213" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AF213" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AG213" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AH213" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI213" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AJ213" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK213" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL213" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM213" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AN213" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO213" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AP213" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ213" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AR213" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AS213" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AT213" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AU213" t="n">
+        <v>5</v>
+      </c>
+      <c r="AV213" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW213" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX213" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY213" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ213" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA213" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB213" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC213" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD213" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BE213" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BF213" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BG213" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH213" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="BI213" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ213" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="BK213" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="BL213" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM213" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BN213" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO213" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BP213" t="n">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>8260239</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>45941.70833333334</v>
+      </c>
+      <c r="F214" t="n">
+        <v>6</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Guarani</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>1</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>1</v>
+      </c>
+      <c r="L214" t="n">
+        <v>2</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="n">
+        <v>2</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>['7', '75']</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="R214" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S214" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T214" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U214" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V214" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="W214" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X214" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AT214" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU214" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW214" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY214" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ214" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA214" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB214" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC214" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD214" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BE214" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF214" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BG214" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BH214" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI214" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BJ214" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BK214" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BL214" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM214" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BN214" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO214" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP214" t="n">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>8260241</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>45941.70833333334</v>
+      </c>
+      <c r="F215" t="n">
+        <v>6</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>1</v>
+      </c>
+      <c r="K215" t="n">
+        <v>1</v>
+      </c>
+      <c r="L215" t="n">
+        <v>1</v>
+      </c>
+      <c r="M215" t="n">
+        <v>1</v>
+      </c>
+      <c r="N215" t="n">
+        <v>2</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>['46']</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>['17']</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="R215" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="S215" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="T215" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U215" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="V215" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="W215" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X215" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT215" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AU215" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW215" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX215" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY215" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ215" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA215" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB215" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC215" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD215" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BE215" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF215" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BG215" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BH215" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="BI215" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BJ215" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BK215" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BL215" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BM215" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BN215" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BO215" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BP215" t="n">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,7 +1132,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.89</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>1</v>
@@ -5492,7 +5492,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR23" t="n">
         <v>2.61</v>
@@ -10939,7 +10939,7 @@
         <v>0.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ48" t="n">
         <v>0.3</v>
@@ -11596,7 +11596,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ51" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR51" t="n">
         <v>1.68</v>
@@ -13994,7 +13994,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR62" t="n">
         <v>1.45</v>
@@ -14645,7 +14645,7 @@
         <v>1.67</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ65" t="n">
         <v>1.3</v>
@@ -19441,7 +19441,7 @@
         <v>0.5</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ87" t="n">
         <v>1</v>
@@ -21188,7 +21188,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR95" t="n">
         <v>2.52</v>
@@ -23801,7 +23801,7 @@
         <v>1</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.08</v>
@@ -25112,7 +25112,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR113" t="n">
         <v>1.77</v>
@@ -27507,7 +27507,7 @@
         <v>0</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.4</v>
@@ -29687,7 +29687,7 @@
         <v>1</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ134" t="n">
         <v>0.67</v>
@@ -30562,7 +30562,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR138" t="n">
         <v>1.45</v>
@@ -33614,7 +33614,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ152" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR152" t="n">
         <v>1.61</v>
@@ -34483,7 +34483,7 @@
         <v>1.57</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.67</v>
@@ -38843,7 +38843,7 @@
         <v>0.67</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AQ176" t="n">
         <v>0.7</v>
@@ -39936,7 +39936,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ181" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AR181" t="n">
         <v>1.97</v>
@@ -42334,7 +42334,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AR192" t="n">
         <v>1.48</v>
@@ -42552,7 +42552,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AR193" t="n">
         <v>1.58</v>
@@ -42770,7 +42770,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ194" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AR194" t="n">
         <v>1.58</v>
@@ -44075,7 +44075,7 @@
         <v>1.48</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AQ200" t="n">
         <v>1.42</v>
@@ -44293,7 +44293,7 @@
         <v>1.4</v>
       </c>
       <c r="AP201" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AQ201" t="n">
         <v>1.36</v>
@@ -44514,7 +44514,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ202" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AR202" t="n">
         <v>1.56</v>
@@ -44729,7 +44729,7 @@
         <v>1.77</v>
       </c>
       <c r="AP203" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.58</v>
@@ -45383,7 +45383,7 @@
         <v>1.77</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AQ206" t="n">
         <v>1.76</v>
@@ -46040,7 +46040,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AR209" t="n">
         <v>1.35</v>
@@ -46476,7 +46476,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ211" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AR211" t="n">
         <v>1.29</v>
@@ -46694,7 +46694,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ212" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AR212" t="n">
         <v>1.19</v>
@@ -47345,7 +47345,7 @@
         <v>1.48</v>
       </c>
       <c r="AP215" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AQ215" t="n">
         <v>1.46</v>
@@ -47563,7 +47563,7 @@
         <v>1.42</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AQ216" t="n">
         <v>1.36</v>
@@ -47860,6 +47860,224 @@
       </c>
       <c r="BP217" t="n">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>8336511</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>45948.70833333334</v>
+      </c>
+      <c r="F218" t="n">
+        <v>0</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" t="n">
+        <v>0</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R218" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S218" t="n">
+        <v>4</v>
+      </c>
+      <c r="T218" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U218" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V218" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="W218" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X218" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ218" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AR218" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AS218" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AT218" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU218" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW218" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX218" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY218" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ218" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA218" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB218" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC218" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD218" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE218" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF218" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="BG218" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH218" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="BI218" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ218" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BK218" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BL218" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BM218" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BN218" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BO218" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP218" t="n">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -48014,22 +48014,22 @@
         <v>2.99</v>
       </c>
       <c r="AU218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV218" t="n">
         <v>0</v>
       </c>
       <c r="AW218" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AX218" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY218" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AZ218" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BA218" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -42564,31 +42564,31 @@
         <v>3.15</v>
       </c>
       <c r="AU193" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AV193" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AW193" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="AX193" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="AY193" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AZ193" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="BA193" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="BB193" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="BC193" t="n">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="BD193" t="n">
         <v>0</v>
@@ -43430,10 +43430,10 @@
         <v>1.33</v>
       </c>
       <c r="AS197" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AT197" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="AU197" t="n">
         <v>3</v>
@@ -43645,13 +43645,13 @@
         <v>1.44</v>
       </c>
       <c r="AR198" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AS198" t="n">
         <v>1.17</v>
       </c>
       <c r="AT198" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="AU198" t="n">
         <v>4</v>
@@ -44299,13 +44299,13 @@
         <v>1.6</v>
       </c>
       <c r="AR201" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AS201" t="n">
         <v>1.34</v>
       </c>
       <c r="AT201" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="AU201" t="n">
         <v>7</v>
@@ -44520,10 +44520,10 @@
         <v>1.14</v>
       </c>
       <c r="AS202" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AT202" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="AU202" t="n">
         <v>5</v>
@@ -45389,13 +45389,13 @@
         <v>1.44</v>
       </c>
       <c r="AR206" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AS206" t="n">
         <v>1.2</v>
       </c>
       <c r="AT206" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AU206" t="n">
         <v>5</v>
@@ -45610,10 +45610,10 @@
         <v>1.35</v>
       </c>
       <c r="AS207" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AT207" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AU207" t="n">
         <v>7</v>
@@ -46264,10 +46264,10 @@
         <v>1.19</v>
       </c>
       <c r="AS210" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AT210" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="AU210" t="n">
         <v>4</v>
@@ -46479,13 +46479,13 @@
         <v>1.6</v>
       </c>
       <c r="AR211" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AS211" t="n">
         <v>1.38</v>
       </c>
       <c r="AT211" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="AU211" t="n">
         <v>7</v>
@@ -46697,13 +46697,13 @@
         <v>1.48</v>
       </c>
       <c r="AR212" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AS212" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AT212" t="n">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="AU212" t="n">
         <v>4</v>
@@ -47569,13 +47569,13 @@
         <v>1.92</v>
       </c>
       <c r="AR216" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AS216" t="n">
         <v>1.39</v>
       </c>
       <c r="AT216" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="AU216" t="n">
         <v>1</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP216"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ13" t="n">
         <v>0.4</v>
@@ -4184,7 +4184,7 @@
         <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR17" t="n">
         <v>0</v>
@@ -7887,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.7</v>
@@ -9416,7 +9416,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR41" t="n">
         <v>1.51</v>
@@ -12247,7 +12247,7 @@
         <v>1</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ54" t="n">
         <v>1.17</v>
@@ -13776,7 +13776,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR61" t="n">
         <v>2.4</v>
@@ -16828,7 +16828,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR75" t="n">
         <v>0.91</v>
@@ -17915,7 +17915,7 @@
         <v>0.33</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ80" t="n">
         <v>0.89</v>
@@ -18351,7 +18351,7 @@
         <v>1.5</v>
       </c>
       <c r="AP82" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.3</v>
@@ -20534,7 +20534,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR92" t="n">
         <v>1.52</v>
@@ -24455,7 +24455,7 @@
         <v>0.6</v>
       </c>
       <c r="AP110" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ110" t="n">
         <v>0.3</v>
@@ -25766,7 +25766,7 @@
         <v>1.7</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR116" t="n">
         <v>1.53</v>
@@ -27507,7 +27507,7 @@
         <v>1</v>
       </c>
       <c r="AP124" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ124" t="n">
         <v>0.92</v>
@@ -31649,7 +31649,7 @@
         <v>0.83</v>
       </c>
       <c r="AP143" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ143" t="n">
         <v>1.08</v>
@@ -33396,7 +33396,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR151" t="n">
         <v>1.41</v>
@@ -36009,7 +36009,7 @@
         <v>0.13</v>
       </c>
       <c r="AP163" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ163" t="n">
         <v>0.4</v>
@@ -36884,7 +36884,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR167" t="n">
         <v>1.31</v>
@@ -41023,10 +41023,10 @@
         <v>1.63</v>
       </c>
       <c r="AP186" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="AQ186" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AR186" t="n">
         <v>1.42</v>
@@ -42334,7 +42334,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AR192" t="n">
         <v>1.48</v>
@@ -42552,7 +42552,7 @@
         <v>1.48</v>
       </c>
       <c r="AQ193" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AR193" t="n">
         <v>1.58</v>
@@ -43639,7 +43639,7 @@
         <v>1.5</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AQ198" t="n">
         <v>1.44</v>
@@ -43857,7 +43857,7 @@
         <v>1.4</v>
       </c>
       <c r="AP199" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AQ199" t="n">
         <v>1.36</v>
@@ -44078,7 +44078,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AR200" t="n">
         <v>1.56</v>
@@ -44293,7 +44293,7 @@
         <v>1.81</v>
       </c>
       <c r="AP201" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AQ201" t="n">
         <v>1.6</v>
@@ -44947,7 +44947,7 @@
         <v>1.77</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AQ204" t="n">
         <v>1.76</v>
@@ -45604,7 +45604,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AR207" t="n">
         <v>1.35</v>
@@ -46040,7 +46040,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ209" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AR209" t="n">
         <v>1.29</v>
@@ -46258,7 +46258,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ210" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AR210" t="n">
         <v>1.19</v>
@@ -46691,7 +46691,7 @@
         <v>1.5</v>
       </c>
       <c r="AP212" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AQ212" t="n">
         <v>1.48</v>
@@ -46909,7 +46909,7 @@
         <v>1.42</v>
       </c>
       <c r="AP213" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AQ213" t="n">
         <v>1.36</v>
@@ -47563,10 +47563,10 @@
         <v>1.96</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AQ216" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AR216" t="n">
         <v>1.56</v>
@@ -47642,6 +47642,224 @@
       </c>
       <c r="BP216" t="n">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>8336510</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>45955.70833333334</v>
+      </c>
+      <c r="F217" t="n">
+        <v>0</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>2</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" t="n">
+        <v>2</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>['48', '73']</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R217" t="n">
+        <v>2</v>
+      </c>
+      <c r="S217" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T217" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U217" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V217" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="W217" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X217" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AT217" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU217" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV217" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW217" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX217" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY217" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ217" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA217" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB217" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC217" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BE217" t="n">
+        <v>8.050000000000001</v>
+      </c>
+      <c r="BF217" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BG217" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH217" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="BI217" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ217" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK217" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BL217" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM217" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BN217" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BO217" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BP217" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Brazil Serie C_2025.xlsx
@@ -47796,16 +47796,16 @@
         <v>2.91</v>
       </c>
       <c r="AU217" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV217" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW217" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX217" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY217" t="n">
         <v>15</v>
